--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E841FA3B-EF18-46C5-8A2B-F4B8753C72A5}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
+    <sheet name="Página1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -97,36 +106,33 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -136,7 +142,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -146,59 +152,65 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFF5B400"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -388,17 +400,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F244"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,7 +433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -432,13 +447,13 @@
         <v>574.5</v>
       </c>
       <c r="E2" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F2" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -452,13 +467,13 @@
         <v>426.5</v>
       </c>
       <c r="E3" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F3" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -472,13 +487,13 @@
         <v>68.5</v>
       </c>
       <c r="E4" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F4" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -489,16 +504,16 @@
         <v>13</v>
       </c>
       <c r="D5" s="3">
-        <v>352.0</v>
+        <v>352</v>
       </c>
       <c r="E5" s="4">
         <v>1072.5</v>
       </c>
       <c r="F5" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -512,13 +527,13 @@
         <v>195.5</v>
       </c>
       <c r="E6" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F6" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -535,10 +550,10 @@
         <v>427.5</v>
       </c>
       <c r="F7" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -549,16 +564,16 @@
         <v>20</v>
       </c>
       <c r="D8" s="3">
-        <v>116.0</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2">
         <v>427.5</v>
       </c>
       <c r="F8" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -572,13 +587,13 @@
         <v>43.5</v>
       </c>
       <c r="E9" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F9" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -589,16 +604,16 @@
         <v>26</v>
       </c>
       <c r="D10" s="3">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="E10" s="2">
         <v>376.5</v>
       </c>
       <c r="F10" s="5">
-        <v>46204.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -609,16 +624,16 @@
         <v>8</v>
       </c>
       <c r="D11" s="3">
-        <v>861.0</v>
+        <v>861</v>
       </c>
       <c r="E11" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F11" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -632,13 +647,13 @@
         <v>507.5</v>
       </c>
       <c r="E12" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F12" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -652,13 +667,13 @@
         <v>129.5</v>
       </c>
       <c r="E13" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F13" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -675,10 +690,10 @@
         <v>1072.5</v>
       </c>
       <c r="F14" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -692,13 +707,13 @@
         <v>297.5</v>
       </c>
       <c r="E15" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F15" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -709,16 +724,16 @@
         <v>17</v>
       </c>
       <c r="D16" s="3">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="E16" s="2">
         <v>427.5</v>
       </c>
       <c r="F16" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -729,16 +744,16 @@
         <v>20</v>
       </c>
       <c r="D17" s="3">
-        <v>213.0</v>
+        <v>213</v>
       </c>
       <c r="E17" s="2">
         <v>427.5</v>
       </c>
       <c r="F17" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -749,16 +764,16 @@
         <v>23</v>
       </c>
       <c r="D18" s="3">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F18" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -775,10 +790,10 @@
         <v>376.5</v>
       </c>
       <c r="F19" s="5">
-        <v>46205.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -789,16 +804,16 @@
         <v>8</v>
       </c>
       <c r="D20" s="3">
-        <v>927.0</v>
+        <v>927</v>
       </c>
       <c r="E20" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F20" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
@@ -809,16 +824,16 @@
         <v>9</v>
       </c>
       <c r="D21" s="3">
-        <v>680.0</v>
+        <v>680</v>
       </c>
       <c r="E21" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F21" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
@@ -832,13 +847,13 @@
         <v>172.5</v>
       </c>
       <c r="E22" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F22" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
@@ -855,10 +870,10 @@
         <v>1072.5</v>
       </c>
       <c r="F23" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -872,13 +887,13 @@
         <v>304.5</v>
       </c>
       <c r="E24" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F24" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>15</v>
       </c>
@@ -889,16 +904,16 @@
         <v>17</v>
       </c>
       <c r="D25" s="3">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="E25" s="2">
         <v>427.5</v>
       </c>
       <c r="F25" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>18</v>
       </c>
@@ -909,16 +924,16 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>246.0</v>
+        <v>246</v>
       </c>
       <c r="E26" s="2">
         <v>427.5</v>
       </c>
       <c r="F26" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>21</v>
       </c>
@@ -929,16 +944,16 @@
         <v>23</v>
       </c>
       <c r="D27" s="3">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="E27" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F27" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -955,10 +970,10 @@
         <v>376.5</v>
       </c>
       <c r="F28" s="5">
-        <v>46206.0</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
@@ -969,16 +984,16 @@
         <v>8</v>
       </c>
       <c r="D29" s="3">
-        <v>955.0</v>
+        <v>955</v>
       </c>
       <c r="E29" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F29" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
@@ -989,16 +1004,16 @@
         <v>9</v>
       </c>
       <c r="D30" s="3">
-        <v>719.0</v>
+        <v>719</v>
       </c>
       <c r="E30" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F30" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
@@ -1009,16 +1024,16 @@
         <v>10</v>
       </c>
       <c r="D31" s="3">
-        <v>177.0</v>
+        <v>177</v>
       </c>
       <c r="E31" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F31" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -1035,10 +1050,10 @@
         <v>1072.5</v>
       </c>
       <c r="F32" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
@@ -1052,13 +1067,13 @@
         <v>304.5</v>
       </c>
       <c r="E33" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F33" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>15</v>
       </c>
@@ -1069,16 +1084,16 @@
         <v>17</v>
       </c>
       <c r="D34" s="3">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="E34" s="2">
         <v>427.5</v>
       </c>
       <c r="F34" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>18</v>
       </c>
@@ -1089,16 +1104,16 @@
         <v>20</v>
       </c>
       <c r="D35" s="3">
-        <v>254.0</v>
+        <v>254</v>
       </c>
       <c r="E35" s="2">
         <v>427.5</v>
       </c>
       <c r="F35" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>21</v>
       </c>
@@ -1109,16 +1124,16 @@
         <v>23</v>
       </c>
       <c r="D36" s="3">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="E36" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F36" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>24</v>
       </c>
@@ -1135,10 +1150,10 @@
         <v>376.5</v>
       </c>
       <c r="F37" s="5">
-        <v>46207.0</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
@@ -1149,16 +1164,16 @@
         <v>8</v>
       </c>
       <c r="D38" s="3">
-        <v>1019.0</v>
+        <v>1019</v>
       </c>
       <c r="E38" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F38" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1169,16 +1184,16 @@
         <v>9</v>
       </c>
       <c r="D39" s="3">
-        <v>969.0</v>
+        <v>969</v>
       </c>
       <c r="E39" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F39" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
@@ -1189,16 +1204,16 @@
         <v>10</v>
       </c>
       <c r="D40" s="3">
-        <v>187.0</v>
+        <v>187</v>
       </c>
       <c r="E40" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F40" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -1215,10 +1230,10 @@
         <v>1072.5</v>
       </c>
       <c r="F41" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -1232,13 +1247,13 @@
         <v>369.5</v>
       </c>
       <c r="E42" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F42" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>15</v>
       </c>
@@ -1255,10 +1270,10 @@
         <v>427.5</v>
       </c>
       <c r="F43" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>18</v>
       </c>
@@ -1269,16 +1284,16 @@
         <v>20</v>
       </c>
       <c r="D44" s="3">
-        <v>348.0</v>
+        <v>348</v>
       </c>
       <c r="E44" s="2">
         <v>427.5</v>
       </c>
       <c r="F44" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>21</v>
       </c>
@@ -1289,16 +1304,16 @@
         <v>23</v>
       </c>
       <c r="D45" s="3">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F45" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>24</v>
       </c>
@@ -1309,16 +1324,16 @@
         <v>26</v>
       </c>
       <c r="D46" s="3">
-        <v>315.0</v>
+        <v>315</v>
       </c>
       <c r="E46" s="2">
         <v>376.5</v>
       </c>
       <c r="F46" s="5">
-        <v>46209.0</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
@@ -1329,16 +1344,16 @@
         <v>8</v>
       </c>
       <c r="D47" s="3">
-        <v>1088.0</v>
+        <v>1088</v>
       </c>
       <c r="E47" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F47" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
@@ -1349,16 +1364,16 @@
         <v>9</v>
       </c>
       <c r="D48" s="3">
-        <v>1009.0</v>
+        <v>1009</v>
       </c>
       <c r="E48" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F48" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
@@ -1369,16 +1384,16 @@
         <v>10</v>
       </c>
       <c r="D49" s="3">
-        <v>235.0</v>
+        <v>235</v>
       </c>
       <c r="E49" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F49" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -1389,16 +1404,16 @@
         <v>13</v>
       </c>
       <c r="D50" s="3">
-        <v>692.0</v>
+        <v>692</v>
       </c>
       <c r="E50" s="4">
         <v>1072.5</v>
       </c>
       <c r="F50" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
@@ -1409,16 +1424,16 @@
         <v>14</v>
       </c>
       <c r="D51" s="3">
-        <v>444.0</v>
+        <v>444</v>
       </c>
       <c r="E51" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F51" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>15</v>
       </c>
@@ -1429,16 +1444,16 @@
         <v>17</v>
       </c>
       <c r="D52" s="3">
-        <v>203.0</v>
+        <v>203</v>
       </c>
       <c r="E52" s="2">
         <v>427.5</v>
       </c>
       <c r="F52" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>18</v>
       </c>
@@ -1449,16 +1464,16 @@
         <v>20</v>
       </c>
       <c r="D53" s="3">
-        <v>452.0</v>
+        <v>452</v>
       </c>
       <c r="E53" s="2">
         <v>427.5</v>
       </c>
       <c r="F53" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>21</v>
       </c>
@@ -1469,16 +1484,16 @@
         <v>23</v>
       </c>
       <c r="D54" s="3">
-        <v>178.0</v>
+        <v>178</v>
       </c>
       <c r="E54" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F54" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>24</v>
       </c>
@@ -1495,10 +1510,10 @@
         <v>376.5</v>
       </c>
       <c r="F55" s="5">
-        <v>46210.0</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>6</v>
       </c>
@@ -1512,13 +1527,13 @@
         <v>1237.5</v>
       </c>
       <c r="E56" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F56" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1532,13 +1547,13 @@
         <v>1175.5</v>
       </c>
       <c r="E57" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F57" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
@@ -1552,13 +1567,13 @@
         <v>381.5</v>
       </c>
       <c r="E58" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F58" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
@@ -1569,16 +1584,16 @@
         <v>13</v>
       </c>
       <c r="D59" s="3">
-        <v>819.0</v>
+        <v>819</v>
       </c>
       <c r="E59" s="4">
         <v>1072.5</v>
       </c>
       <c r="F59" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>11</v>
       </c>
@@ -1589,16 +1604,16 @@
         <v>14</v>
       </c>
       <c r="D60" s="3">
-        <v>622.0</v>
+        <v>622</v>
       </c>
       <c r="E60" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F60" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>15</v>
       </c>
@@ -1615,10 +1630,10 @@
         <v>427.5</v>
       </c>
       <c r="F61" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>18</v>
       </c>
@@ -1635,10 +1650,10 @@
         <v>427.5</v>
       </c>
       <c r="F62" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>21</v>
       </c>
@@ -1652,13 +1667,13 @@
         <v>262.5</v>
       </c>
       <c r="E63" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F63" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
@@ -1669,16 +1684,16 @@
         <v>26</v>
       </c>
       <c r="D64" s="3">
-        <v>409.0</v>
+        <v>409</v>
       </c>
       <c r="E64" s="2">
         <v>376.5</v>
       </c>
       <c r="F64" s="5">
-        <v>46211.0</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>6</v>
       </c>
@@ -1689,16 +1704,16 @@
         <v>8</v>
       </c>
       <c r="D65" s="3">
-        <v>1358.0</v>
+        <v>1358</v>
       </c>
       <c r="E65" s="4">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F65" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>6</v>
       </c>
@@ -1709,16 +1724,16 @@
         <v>9</v>
       </c>
       <c r="D66" s="3">
-        <v>1311.0</v>
+        <v>1311</v>
       </c>
       <c r="E66" s="2">
-        <v>952.0</v>
+        <v>952</v>
       </c>
       <c r="F66" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -1732,13 +1747,13 @@
         <v>412.5</v>
       </c>
       <c r="E67" s="2">
-        <v>357.0</v>
+        <v>357</v>
       </c>
       <c r="F67" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
@@ -1755,10 +1770,10 @@
         <v>1072.5</v>
       </c>
       <c r="F68" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>11</v>
       </c>
@@ -1772,13 +1787,13 @@
         <v>731.5</v>
       </c>
       <c r="E69" s="2">
-        <v>715.0</v>
+        <v>715</v>
       </c>
       <c r="F69" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>15</v>
       </c>
@@ -1795,10 +1810,10 @@
         <v>427.5</v>
       </c>
       <c r="F70" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>18</v>
       </c>
@@ -1815,10 +1830,10 @@
         <v>427.5</v>
       </c>
       <c r="F71" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>21</v>
       </c>
@@ -1832,13 +1847,13 @@
         <v>408.5</v>
       </c>
       <c r="E72" s="2">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="F72" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>24</v>
       </c>
@@ -1849,16 +1864,16 @@
         <v>26</v>
       </c>
       <c r="D73" s="3">
-        <v>456.0</v>
+        <v>456</v>
       </c>
       <c r="E73" s="2">
         <v>376.5</v>
       </c>
       <c r="F73" s="5">
-        <v>46212.0</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>6</v>
       </c>
@@ -1869,16 +1884,16 @@
         <v>8</v>
       </c>
       <c r="D74" s="3">
-        <v>1535.0</v>
+        <v>1535</v>
       </c>
       <c r="E74" s="4">
-        <v>2142.0</v>
+        <v>2142</v>
       </c>
       <c r="F74" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -1889,16 +1904,16 @@
         <v>9</v>
       </c>
       <c r="D75" s="3">
-        <v>1404.0</v>
+        <v>1404</v>
       </c>
       <c r="E75" s="4">
-        <v>1904.0</v>
+        <v>1904</v>
       </c>
       <c r="F75" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>6</v>
       </c>
@@ -1912,13 +1927,13 @@
         <v>484.5</v>
       </c>
       <c r="E76" s="2">
-        <v>714.0</v>
+        <v>714</v>
       </c>
       <c r="F76" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>11</v>
       </c>
@@ -1929,16 +1944,16 @@
         <v>13</v>
       </c>
       <c r="D77" s="3">
-        <v>1092.0</v>
+        <v>1092</v>
       </c>
       <c r="E77" s="4">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F77" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>11</v>
       </c>
@@ -1952,13 +1967,13 @@
         <v>879.5</v>
       </c>
       <c r="E78" s="4">
-        <v>1430.0</v>
+        <v>1430</v>
       </c>
       <c r="F78" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>15</v>
       </c>
@@ -1969,16 +1984,16 @@
         <v>17</v>
       </c>
       <c r="D79" s="3">
-        <v>446.0</v>
+        <v>446</v>
       </c>
       <c r="E79" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F79" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>18</v>
       </c>
@@ -1989,16 +2004,16 @@
         <v>20</v>
       </c>
       <c r="D80" s="3">
-        <v>712.0</v>
+        <v>712</v>
       </c>
       <c r="E80" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F80" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>21</v>
       </c>
@@ -2009,16 +2024,16 @@
         <v>23</v>
       </c>
       <c r="D81" s="3">
-        <v>455.0</v>
+        <v>455</v>
       </c>
       <c r="E81" s="2">
-        <v>580.0</v>
+        <v>580</v>
       </c>
       <c r="F81" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>24</v>
       </c>
@@ -2032,13 +2047,13 @@
         <v>523.5</v>
       </c>
       <c r="E82" s="2">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="F82" s="5">
-        <v>46213.0</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
@@ -2052,13 +2067,13 @@
         <v>1631.5</v>
       </c>
       <c r="E83" s="4">
-        <v>2142.0</v>
+        <v>2142</v>
       </c>
       <c r="F83" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>6</v>
       </c>
@@ -2069,16 +2084,16 @@
         <v>9</v>
       </c>
       <c r="D84" s="3">
-        <v>1480.0</v>
+        <v>1480</v>
       </c>
       <c r="E84" s="4">
-        <v>1904.0</v>
+        <v>1904</v>
       </c>
       <c r="F84" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>6</v>
       </c>
@@ -2092,13 +2107,13 @@
         <v>484.5</v>
       </c>
       <c r="E85" s="2">
-        <v>714.0</v>
+        <v>714</v>
       </c>
       <c r="F85" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>11</v>
       </c>
@@ -2112,13 +2127,13 @@
         <v>1130.5</v>
       </c>
       <c r="E86" s="4">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F86" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>11</v>
       </c>
@@ -2129,16 +2144,16 @@
         <v>14</v>
       </c>
       <c r="D87" s="3">
-        <v>884.0</v>
+        <v>884</v>
       </c>
       <c r="E87" s="4">
-        <v>1430.0</v>
+        <v>1430</v>
       </c>
       <c r="F87" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>15</v>
       </c>
@@ -2149,16 +2164,16 @@
         <v>17</v>
       </c>
       <c r="D88" s="3">
-        <v>446.0</v>
+        <v>446</v>
       </c>
       <c r="E88" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F88" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>18</v>
       </c>
@@ -2172,13 +2187,13 @@
         <v>712.5</v>
       </c>
       <c r="E89" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F89" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>21</v>
       </c>
@@ -2189,16 +2204,16 @@
         <v>23</v>
       </c>
       <c r="D90" s="3">
-        <v>455.0</v>
+        <v>455</v>
       </c>
       <c r="E90" s="2">
-        <v>580.0</v>
+        <v>580</v>
       </c>
       <c r="F90" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>24</v>
       </c>
@@ -2212,13 +2227,13 @@
         <v>523.5</v>
       </c>
       <c r="E91" s="2">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="F91" s="5">
-        <v>46214.0</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>6</v>
       </c>
@@ -2232,13 +2247,13 @@
         <v>1752.5</v>
       </c>
       <c r="E92" s="4">
-        <v>2142.0</v>
+        <v>2142</v>
       </c>
       <c r="F92" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>6</v>
       </c>
@@ -2252,13 +2267,13 @@
         <v>1638.5</v>
       </c>
       <c r="E93" s="4">
-        <v>1904.0</v>
+        <v>1904</v>
       </c>
       <c r="F93" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>6</v>
       </c>
@@ -2272,13 +2287,13 @@
         <v>493.5</v>
       </c>
       <c r="E94" s="2">
-        <v>714.0</v>
+        <v>714</v>
       </c>
       <c r="F94" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>11</v>
       </c>
@@ -2292,13 +2307,13 @@
         <v>1280.5</v>
       </c>
       <c r="E95" s="4">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F95" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -2309,16 +2324,16 @@
         <v>14</v>
       </c>
       <c r="D96" s="3">
-        <v>990.0</v>
+        <v>990</v>
       </c>
       <c r="E96" s="4">
-        <v>1430.0</v>
+        <v>1430</v>
       </c>
       <c r="F96" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>15</v>
       </c>
@@ -2329,16 +2344,16 @@
         <v>17</v>
       </c>
       <c r="D97" s="3">
-        <v>481.0</v>
+        <v>481</v>
       </c>
       <c r="E97" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F97" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>18</v>
       </c>
@@ -2349,16 +2364,16 @@
         <v>20</v>
       </c>
       <c r="D98" s="3">
-        <v>786.0</v>
+        <v>786</v>
       </c>
       <c r="E98" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F98" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>21</v>
       </c>
@@ -2369,16 +2384,16 @@
         <v>23</v>
       </c>
       <c r="D99" s="3">
-        <v>494.0</v>
+        <v>494</v>
       </c>
       <c r="E99" s="2">
-        <v>580.0</v>
+        <v>580</v>
       </c>
       <c r="F99" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>24</v>
       </c>
@@ -2392,13 +2407,13 @@
         <v>653.5</v>
       </c>
       <c r="E100" s="2">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="F100" s="5">
-        <v>46216.0</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>6</v>
       </c>
@@ -2409,16 +2424,16 @@
         <v>8</v>
       </c>
       <c r="D101" s="3">
-        <v>1835.0</v>
+        <v>1835</v>
       </c>
       <c r="E101" s="4">
-        <v>2142.0</v>
+        <v>2142</v>
       </c>
       <c r="F101" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>6</v>
       </c>
@@ -2429,16 +2444,16 @@
         <v>9</v>
       </c>
       <c r="D102" s="3">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="E102" s="4">
-        <v>1904.0</v>
+        <v>1904</v>
       </c>
       <c r="F102" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>6</v>
       </c>
@@ -2452,13 +2467,13 @@
         <v>538.5</v>
       </c>
       <c r="E103" s="2">
-        <v>714.0</v>
+        <v>714</v>
       </c>
       <c r="F103" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -2472,13 +2487,13 @@
         <v>1400.5</v>
       </c>
       <c r="E104" s="4">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F104" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>11</v>
       </c>
@@ -2492,13 +2507,13 @@
         <v>1120.5</v>
       </c>
       <c r="E105" s="4">
-        <v>1430.0</v>
+        <v>1430</v>
       </c>
       <c r="F105" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>15</v>
       </c>
@@ -2509,16 +2524,16 @@
         <v>17</v>
       </c>
       <c r="D106" s="3">
-        <v>606.0</v>
+        <v>606</v>
       </c>
       <c r="E106" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F106" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>18</v>
       </c>
@@ -2532,13 +2547,13 @@
         <v>894.5</v>
       </c>
       <c r="E107" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F107" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>21</v>
       </c>
@@ -2549,16 +2564,16 @@
         <v>23</v>
       </c>
       <c r="D108" s="3">
-        <v>509.0</v>
+        <v>509</v>
       </c>
       <c r="E108" s="2">
-        <v>580.0</v>
+        <v>580</v>
       </c>
       <c r="F108" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>24</v>
       </c>
@@ -2569,16 +2584,16 @@
         <v>26</v>
       </c>
       <c r="D109" s="3">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="E109" s="2">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="F109" s="5">
-        <v>46217.0</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>6</v>
       </c>
@@ -2589,16 +2604,16 @@
         <v>8</v>
       </c>
       <c r="D110" s="3">
-        <v>1972.0</v>
+        <v>1972</v>
       </c>
       <c r="E110" s="4">
-        <v>2142.0</v>
+        <v>2142</v>
       </c>
       <c r="F110" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>6</v>
       </c>
@@ -2612,13 +2627,13 @@
         <v>2133.5</v>
       </c>
       <c r="E111" s="4">
-        <v>1904.0</v>
+        <v>1904</v>
       </c>
       <c r="F111" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>6</v>
       </c>
@@ -2629,16 +2644,16 @@
         <v>10</v>
       </c>
       <c r="D112" s="3">
-        <v>588.0</v>
+        <v>588</v>
       </c>
       <c r="E112" s="2">
-        <v>714.0</v>
+        <v>714</v>
       </c>
       <c r="F112" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="113">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>11</v>
       </c>
@@ -2652,13 +2667,13 @@
         <v>1473.5</v>
       </c>
       <c r="E113" s="4">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F113" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>11</v>
       </c>
@@ -2669,16 +2684,16 @@
         <v>14</v>
       </c>
       <c r="D114" s="3">
-        <v>1236.0</v>
+        <v>1236</v>
       </c>
       <c r="E114" s="4">
-        <v>1430.0</v>
+        <v>1430</v>
       </c>
       <c r="F114" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="115">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>15</v>
       </c>
@@ -2689,16 +2704,16 @@
         <v>17</v>
       </c>
       <c r="D115" s="3">
-        <v>676.0</v>
+        <v>676</v>
       </c>
       <c r="E115" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F115" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>18</v>
       </c>
@@ -2712,13 +2727,13 @@
         <v>938.5</v>
       </c>
       <c r="E116" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F116" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>21</v>
       </c>
@@ -2732,13 +2747,13 @@
         <v>561.5</v>
       </c>
       <c r="E117" s="2">
-        <v>580.0</v>
+        <v>580</v>
       </c>
       <c r="F117" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>24</v>
       </c>
@@ -2749,16 +2764,16 @@
         <v>26</v>
       </c>
       <c r="D118" s="3">
-        <v>904.0</v>
+        <v>904</v>
       </c>
       <c r="E118" s="2">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="F118" s="5">
-        <v>46218.0</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>6</v>
       </c>
@@ -2772,13 +2787,13 @@
         <v>2136.5</v>
       </c>
       <c r="E119" s="4">
-        <v>2142.0</v>
+        <v>2142</v>
       </c>
       <c r="F119" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>6</v>
       </c>
@@ -2792,13 +2807,13 @@
         <v>2318.5</v>
       </c>
       <c r="E120" s="4">
-        <v>1904.0</v>
+        <v>1904</v>
       </c>
       <c r="F120" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="121">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>6</v>
       </c>
@@ -2809,16 +2824,16 @@
         <v>10</v>
       </c>
       <c r="D121" s="3">
-        <v>618.0</v>
+        <v>618</v>
       </c>
       <c r="E121" s="2">
-        <v>714.0</v>
+        <v>714</v>
       </c>
       <c r="F121" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>11</v>
       </c>
@@ -2829,16 +2844,16 @@
         <v>13</v>
       </c>
       <c r="D122" s="3">
-        <v>1632.0</v>
+        <v>1632</v>
       </c>
       <c r="E122" s="4">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F122" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="123">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>11</v>
       </c>
@@ -2852,13 +2867,13 @@
         <v>1307.5</v>
       </c>
       <c r="E123" s="4">
-        <v>1430.0</v>
+        <v>1430</v>
       </c>
       <c r="F123" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>15</v>
       </c>
@@ -2869,16 +2884,16 @@
         <v>17</v>
       </c>
       <c r="D124" s="3">
-        <v>756.0</v>
+        <v>756</v>
       </c>
       <c r="E124" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F124" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>18</v>
       </c>
@@ -2892,13 +2907,13 @@
         <v>1005.5</v>
       </c>
       <c r="E125" s="2">
-        <v>855.0</v>
+        <v>855</v>
       </c>
       <c r="F125" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>21</v>
       </c>
@@ -2909,16 +2924,16 @@
         <v>23</v>
       </c>
       <c r="D126" s="3">
-        <v>614.0</v>
+        <v>614</v>
       </c>
       <c r="E126" s="2">
-        <v>580.0</v>
+        <v>580</v>
       </c>
       <c r="F126" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>24</v>
       </c>
@@ -2929,16 +2944,16 @@
         <v>26</v>
       </c>
       <c r="D127" s="3">
-        <v>988.0</v>
+        <v>988</v>
       </c>
       <c r="E127" s="2">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="F127" s="5">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="128">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>6</v>
       </c>
@@ -2952,13 +2967,13 @@
         <v>2406.5</v>
       </c>
       <c r="E128" s="6">
-        <v>3213.0</v>
+        <v>3213</v>
       </c>
       <c r="F128" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>6</v>
       </c>
@@ -2972,13 +2987,13 @@
         <v>2412.5</v>
       </c>
       <c r="E129" s="6">
-        <v>2856.0</v>
+        <v>2856</v>
       </c>
       <c r="F129" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="130">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>6</v>
       </c>
@@ -2992,13 +3007,13 @@
         <v>618.5</v>
       </c>
       <c r="E130" s="6">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F130" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="131">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>11</v>
       </c>
@@ -3015,10 +3030,10 @@
         <v>3217.5</v>
       </c>
       <c r="F131" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="132">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>11</v>
       </c>
@@ -3029,16 +3044,16 @@
         <v>14</v>
       </c>
       <c r="D132" s="3">
-        <v>1397.0</v>
+        <v>1397</v>
       </c>
       <c r="E132" s="6">
-        <v>2145.0</v>
+        <v>2145</v>
       </c>
       <c r="F132" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="133">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>15</v>
       </c>
@@ -3049,16 +3064,16 @@
         <v>17</v>
       </c>
       <c r="D133" s="3">
-        <v>806.0</v>
+        <v>806</v>
       </c>
       <c r="E133" s="6">
         <v>1282.5</v>
       </c>
       <c r="F133" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>18</v>
       </c>
@@ -3075,10 +3090,10 @@
         <v>1282.5</v>
       </c>
       <c r="F134" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="135">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>21</v>
       </c>
@@ -3089,16 +3104,16 @@
         <v>23</v>
       </c>
       <c r="D135" s="3">
-        <v>667.0</v>
+        <v>667</v>
       </c>
       <c r="E135" s="6">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="F135" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="136">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>24</v>
       </c>
@@ -3109,16 +3124,16 @@
         <v>26</v>
       </c>
       <c r="D136" s="3">
-        <v>1141.0</v>
+        <v>1141</v>
       </c>
       <c r="E136" s="6">
         <v>1128.75</v>
       </c>
       <c r="F136" s="5">
-        <v>46220.0</v>
-      </c>
-    </row>
-    <row r="137">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>6</v>
       </c>
@@ -3129,16 +3144,16 @@
         <v>8</v>
       </c>
       <c r="D137" s="3">
-        <v>2530.0</v>
+        <v>2530</v>
       </c>
       <c r="E137" s="6">
-        <v>3213.0</v>
+        <v>3213</v>
       </c>
       <c r="F137" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="138">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>6</v>
       </c>
@@ -3149,16 +3164,16 @@
         <v>9</v>
       </c>
       <c r="D138" s="3">
-        <v>2503.0</v>
+        <v>2503</v>
       </c>
       <c r="E138" s="6">
-        <v>2856.0</v>
+        <v>2856</v>
       </c>
       <c r="F138" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="139">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -3169,16 +3184,16 @@
         <v>10</v>
       </c>
       <c r="D139" s="3">
-        <v>629.0</v>
+        <v>629</v>
       </c>
       <c r="E139" s="6">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F139" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="140">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>11</v>
       </c>
@@ -3189,16 +3204,16 @@
         <v>13</v>
       </c>
       <c r="D140" s="3">
-        <v>1871.0</v>
+        <v>1871</v>
       </c>
       <c r="E140" s="6">
         <v>3217.5</v>
       </c>
       <c r="F140" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="141">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>11</v>
       </c>
@@ -3209,16 +3224,16 @@
         <v>14</v>
       </c>
       <c r="D141" s="3">
-        <v>1484.0</v>
+        <v>1484</v>
       </c>
       <c r="E141" s="6">
-        <v>2145.0</v>
+        <v>2145</v>
       </c>
       <c r="F141" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="142">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>15</v>
       </c>
@@ -3229,16 +3244,16 @@
         <v>17</v>
       </c>
       <c r="D142" s="3">
-        <v>814.0</v>
+        <v>814</v>
       </c>
       <c r="E142" s="6">
         <v>1282.5</v>
       </c>
       <c r="F142" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>18</v>
       </c>
@@ -3255,10 +3270,10 @@
         <v>1282.5</v>
       </c>
       <c r="F143" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="144">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>21</v>
       </c>
@@ -3269,16 +3284,16 @@
         <v>23</v>
       </c>
       <c r="D144" s="3">
-        <v>677.0</v>
+        <v>677</v>
       </c>
       <c r="E144" s="6">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="F144" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="145">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>24</v>
       </c>
@@ -3289,16 +3304,16 @@
         <v>26</v>
       </c>
       <c r="D145" s="3">
-        <v>1158.0</v>
+        <v>1158</v>
       </c>
       <c r="E145" s="6">
         <v>1128.75</v>
       </c>
       <c r="F145" s="5">
-        <v>46221.0</v>
-      </c>
-    </row>
-    <row r="146">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>6</v>
       </c>
@@ -3312,13 +3327,13 @@
         <v>2734.5</v>
       </c>
       <c r="E146" s="6">
-        <v>3213.0</v>
+        <v>3213</v>
       </c>
       <c r="F146" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="147">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -3329,16 +3344,16 @@
         <v>9</v>
       </c>
       <c r="D147" s="3">
-        <v>2626.0</v>
+        <v>2626</v>
       </c>
       <c r="E147" s="6">
-        <v>2856.0</v>
+        <v>2856</v>
       </c>
       <c r="F147" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="148">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>6</v>
       </c>
@@ -3349,16 +3364,16 @@
         <v>10</v>
       </c>
       <c r="D148" s="3">
-        <v>660.0</v>
+        <v>660</v>
       </c>
       <c r="E148" s="6">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F148" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="149">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>11</v>
       </c>
@@ -3375,10 +3390,10 @@
         <v>3217.5</v>
       </c>
       <c r="F149" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="150">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>11</v>
       </c>
@@ -3392,13 +3407,13 @@
         <v>1632.5</v>
       </c>
       <c r="E150" s="6">
-        <v>2145.0</v>
+        <v>2145</v>
       </c>
       <c r="F150" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="151">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>15</v>
       </c>
@@ -3409,16 +3424,16 @@
         <v>17</v>
       </c>
       <c r="D151" s="3">
-        <v>831.0</v>
+        <v>831</v>
       </c>
       <c r="E151" s="6">
         <v>1282.5</v>
       </c>
       <c r="F151" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="152">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>18</v>
       </c>
@@ -3429,16 +3444,16 @@
         <v>20</v>
       </c>
       <c r="D152" s="3">
-        <v>1144.0</v>
+        <v>1144</v>
       </c>
       <c r="E152" s="6">
         <v>1282.5</v>
       </c>
       <c r="F152" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="153">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>21</v>
       </c>
@@ -3452,13 +3467,13 @@
         <v>751.5</v>
       </c>
       <c r="E153" s="6">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="F153" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="154">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>24</v>
       </c>
@@ -3469,16 +3484,16 @@
         <v>26</v>
       </c>
       <c r="D154" s="3">
-        <v>1185.0</v>
+        <v>1185</v>
       </c>
       <c r="E154" s="6">
         <v>1128.75</v>
       </c>
       <c r="F154" s="5">
-        <v>46223.0</v>
-      </c>
-    </row>
-    <row r="155">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -3488,15 +3503,17 @@
       <c r="C155" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D155" s="7"/>
+      <c r="D155" s="3">
+        <v>2890</v>
+      </c>
       <c r="E155" s="6">
-        <v>3213.0</v>
+        <v>3213</v>
       </c>
       <c r="F155" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="156">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>6</v>
       </c>
@@ -3506,15 +3523,17 @@
       <c r="C156" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D156" s="7"/>
+      <c r="D156" s="3">
+        <v>2760</v>
+      </c>
       <c r="E156" s="6">
-        <v>2856.0</v>
+        <v>2856</v>
       </c>
       <c r="F156" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="157">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>6</v>
       </c>
@@ -3524,15 +3543,17 @@
       <c r="C157" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D157" s="7"/>
+      <c r="D157" s="3">
+        <v>709</v>
+      </c>
       <c r="E157" s="6">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F157" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="158">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>11</v>
       </c>
@@ -3542,15 +3563,17 @@
       <c r="C158" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D158" s="7"/>
+      <c r="D158" s="3">
+        <v>2006</v>
+      </c>
       <c r="E158" s="6">
         <v>3217.5</v>
       </c>
       <c r="F158" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="159">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>11</v>
       </c>
@@ -3560,15 +3583,17 @@
       <c r="C159" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D159" s="7"/>
+      <c r="D159" s="3">
+        <v>1707</v>
+      </c>
       <c r="E159" s="6">
-        <v>2145.0</v>
+        <v>2145</v>
       </c>
       <c r="F159" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="160">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>15</v>
       </c>
@@ -3578,15 +3603,17 @@
       <c r="C160" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D160" s="7"/>
+      <c r="D160" s="3">
+        <v>908</v>
+      </c>
       <c r="E160" s="6">
         <v>1282.5</v>
       </c>
       <c r="F160" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="161">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>18</v>
       </c>
@@ -3596,15 +3623,17 @@
       <c r="C161" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D161" s="7"/>
+      <c r="D161" s="3">
+        <v>1300.5</v>
+      </c>
       <c r="E161" s="6">
         <v>1282.5</v>
       </c>
       <c r="F161" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="162">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>21</v>
       </c>
@@ -3614,15 +3643,17 @@
       <c r="C162" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D162" s="7"/>
+      <c r="D162" s="3">
+        <v>767</v>
+      </c>
       <c r="E162" s="6">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="F162" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="163">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>24</v>
       </c>
@@ -3632,15 +3663,17 @@
       <c r="C163" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D163" s="7"/>
+      <c r="D163" s="3">
+        <v>1250.5</v>
+      </c>
       <c r="E163" s="6">
         <v>1128.75</v>
       </c>
       <c r="F163" s="5">
-        <v>46224.0</v>
-      </c>
-    </row>
-    <row r="164">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>6</v>
       </c>
@@ -3650,15 +3683,17 @@
       <c r="C164" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D164" s="7"/>
+      <c r="D164" s="3">
+        <v>966.5</v>
+      </c>
       <c r="E164" s="6">
-        <v>3213.0</v>
+        <v>3213</v>
       </c>
       <c r="F164" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="165">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>6</v>
       </c>
@@ -3668,15 +3703,15 @@
       <c r="C165" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D165" s="7"/>
+      <c r="D165" s="3"/>
       <c r="E165" s="6">
-        <v>2856.0</v>
+        <v>2856</v>
       </c>
       <c r="F165" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="166">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>6</v>
       </c>
@@ -3686,15 +3721,15 @@
       <c r="C166" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D166" s="7"/>
+      <c r="D166" s="3"/>
       <c r="E166" s="6">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F166" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="167">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>11</v>
       </c>
@@ -3704,15 +3739,15 @@
       <c r="C167" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D167" s="7"/>
+      <c r="D167" s="3"/>
       <c r="E167" s="6">
         <v>3217.5</v>
       </c>
       <c r="F167" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="168">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>11</v>
       </c>
@@ -3722,15 +3757,15 @@
       <c r="C168" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D168" s="7"/>
+      <c r="D168" s="3"/>
       <c r="E168" s="6">
-        <v>2145.0</v>
+        <v>2145</v>
       </c>
       <c r="F168" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="169">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>15</v>
       </c>
@@ -3740,15 +3775,15 @@
       <c r="C169" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D169" s="7"/>
+      <c r="D169" s="3"/>
       <c r="E169" s="6">
         <v>1282.5</v>
       </c>
       <c r="F169" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="170">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>18</v>
       </c>
@@ -3758,15 +3793,15 @@
       <c r="C170" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D170" s="7"/>
+      <c r="D170" s="3"/>
       <c r="E170" s="6">
         <v>1282.5</v>
       </c>
       <c r="F170" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="171">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>21</v>
       </c>
@@ -3776,15 +3811,15 @@
       <c r="C171" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D171" s="7"/>
+      <c r="D171" s="3"/>
       <c r="E171" s="6">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="F171" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="172">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>24</v>
       </c>
@@ -3794,15 +3829,15 @@
       <c r="C172" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D172" s="7"/>
+      <c r="D172" s="3"/>
       <c r="E172" s="6">
         <v>1128.75</v>
       </c>
       <c r="F172" s="5">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="173">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>6</v>
       </c>
@@ -3812,15 +3847,15 @@
       <c r="C173" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D173" s="7"/>
+      <c r="D173" s="3"/>
       <c r="E173" s="6">
-        <v>3213.0</v>
+        <v>3213</v>
       </c>
       <c r="F173" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="174">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>6</v>
       </c>
@@ -3830,15 +3865,15 @@
       <c r="C174" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D174" s="7"/>
+      <c r="D174" s="3"/>
       <c r="E174" s="6">
-        <v>2856.0</v>
+        <v>2856</v>
       </c>
       <c r="F174" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="175">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>6</v>
       </c>
@@ -3848,15 +3883,15 @@
       <c r="C175" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D175" s="7"/>
+      <c r="D175" s="3"/>
       <c r="E175" s="6">
-        <v>1071.0</v>
+        <v>1071</v>
       </c>
       <c r="F175" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="176">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>11</v>
       </c>
@@ -3866,15 +3901,15 @@
       <c r="C176" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D176" s="7"/>
+      <c r="D176" s="3"/>
       <c r="E176" s="6">
         <v>3217.5</v>
       </c>
       <c r="F176" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="177">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>11</v>
       </c>
@@ -3884,15 +3919,15 @@
       <c r="C177" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D177" s="7"/>
+      <c r="D177" s="3"/>
       <c r="E177" s="6">
-        <v>2145.0</v>
+        <v>2145</v>
       </c>
       <c r="F177" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="178">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>15</v>
       </c>
@@ -3902,15 +3937,15 @@
       <c r="C178" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D178" s="7"/>
+      <c r="D178" s="3"/>
       <c r="E178" s="6">
         <v>1282.5</v>
       </c>
       <c r="F178" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="179">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>18</v>
       </c>
@@ -3920,15 +3955,15 @@
       <c r="C179" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D179" s="7"/>
+      <c r="D179" s="3"/>
       <c r="E179" s="6">
         <v>1282.5</v>
       </c>
       <c r="F179" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="180">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>21</v>
       </c>
@@ -3938,15 +3973,15 @@
       <c r="C180" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D180" s="7"/>
+      <c r="D180" s="3"/>
       <c r="E180" s="6">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="F180" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="181">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>24</v>
       </c>
@@ -3956,15 +3991,15 @@
       <c r="C181" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D181" s="7"/>
+      <c r="D181" s="3"/>
       <c r="E181" s="6">
         <v>1128.75</v>
       </c>
       <c r="F181" s="5">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="182">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>6</v>
       </c>
@@ -3974,15 +4009,15 @@
       <c r="C182" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D182" s="7"/>
+      <c r="D182" s="3"/>
       <c r="E182" s="6">
-        <v>4284.0</v>
+        <v>4284</v>
       </c>
       <c r="F182" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="183">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>6</v>
       </c>
@@ -3992,15 +4027,15 @@
       <c r="C183" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D183" s="7"/>
+      <c r="D183" s="3"/>
       <c r="E183" s="6">
-        <v>3808.0</v>
+        <v>3808</v>
       </c>
       <c r="F183" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="184">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>6</v>
       </c>
@@ -4010,15 +4045,15 @@
       <c r="C184" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D184" s="7"/>
+      <c r="D184" s="3"/>
       <c r="E184" s="6">
-        <v>1428.0</v>
+        <v>1428</v>
       </c>
       <c r="F184" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="185">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>11</v>
       </c>
@@ -4028,15 +4063,15 @@
       <c r="C185" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D185" s="7"/>
+      <c r="D185" s="3"/>
       <c r="E185" s="6">
-        <v>4290.0</v>
+        <v>4290</v>
       </c>
       <c r="F185" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="186">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>11</v>
       </c>
@@ -4046,15 +4081,15 @@
       <c r="C186" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D186" s="7"/>
+      <c r="D186" s="3"/>
       <c r="E186" s="6">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="F186" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="187">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>15</v>
       </c>
@@ -4064,15 +4099,15 @@
       <c r="C187" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D187" s="7"/>
+      <c r="D187" s="3"/>
       <c r="E187" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F187" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="188">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>18</v>
       </c>
@@ -4082,15 +4117,15 @@
       <c r="C188" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D188" s="7"/>
+      <c r="D188" s="3"/>
       <c r="E188" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F188" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="189">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>21</v>
       </c>
@@ -4100,15 +4135,15 @@
       <c r="C189" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D189" s="7"/>
+      <c r="D189" s="3"/>
       <c r="E189" s="6">
-        <v>1160.0</v>
+        <v>1160</v>
       </c>
       <c r="F189" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="190">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>24</v>
       </c>
@@ -4118,15 +4153,15 @@
       <c r="C190" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D190" s="7"/>
+      <c r="D190" s="3"/>
       <c r="E190" s="6">
-        <v>1505.0</v>
+        <v>1505</v>
       </c>
       <c r="F190" s="5">
-        <v>46227.0</v>
-      </c>
-    </row>
-    <row r="191">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>6</v>
       </c>
@@ -4136,15 +4171,15 @@
       <c r="C191" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D191" s="7"/>
+      <c r="D191" s="3"/>
       <c r="E191" s="6">
-        <v>4284.0</v>
+        <v>4284</v>
       </c>
       <c r="F191" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="192">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>6</v>
       </c>
@@ -4154,15 +4189,15 @@
       <c r="C192" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D192" s="7"/>
+      <c r="D192" s="3"/>
       <c r="E192" s="6">
-        <v>3808.0</v>
+        <v>3808</v>
       </c>
       <c r="F192" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="193">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>6</v>
       </c>
@@ -4172,15 +4207,15 @@
       <c r="C193" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D193" s="7"/>
+      <c r="D193" s="3"/>
       <c r="E193" s="6">
-        <v>1428.0</v>
+        <v>1428</v>
       </c>
       <c r="F193" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="194">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>11</v>
       </c>
@@ -4190,15 +4225,15 @@
       <c r="C194" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D194" s="7"/>
+      <c r="D194" s="3"/>
       <c r="E194" s="6">
-        <v>4290.0</v>
+        <v>4290</v>
       </c>
       <c r="F194" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="195">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>11</v>
       </c>
@@ -4208,15 +4243,15 @@
       <c r="C195" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D195" s="7"/>
+      <c r="D195" s="3"/>
       <c r="E195" s="6">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="F195" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="196">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>15</v>
       </c>
@@ -4226,15 +4261,15 @@
       <c r="C196" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D196" s="7"/>
+      <c r="D196" s="3"/>
       <c r="E196" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F196" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="197">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>18</v>
       </c>
@@ -4244,15 +4279,15 @@
       <c r="C197" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D197" s="7"/>
+      <c r="D197" s="3"/>
       <c r="E197" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F197" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="198">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>21</v>
       </c>
@@ -4262,15 +4297,15 @@
       <c r="C198" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D198" s="7"/>
+      <c r="D198" s="3"/>
       <c r="E198" s="6">
-        <v>1160.0</v>
+        <v>1160</v>
       </c>
       <c r="F198" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="199">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>24</v>
       </c>
@@ -4280,15 +4315,15 @@
       <c r="C199" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D199" s="7"/>
+      <c r="D199" s="3"/>
       <c r="E199" s="6">
-        <v>1505.0</v>
+        <v>1505</v>
       </c>
       <c r="F199" s="5">
-        <v>46228.0</v>
-      </c>
-    </row>
-    <row r="200">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>6</v>
       </c>
@@ -4298,15 +4333,15 @@
       <c r="C200" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D200" s="7"/>
+      <c r="D200" s="3"/>
       <c r="E200" s="6">
-        <v>4284.0</v>
+        <v>4284</v>
       </c>
       <c r="F200" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="201">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>6</v>
       </c>
@@ -4316,15 +4351,15 @@
       <c r="C201" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D201" s="7"/>
+      <c r="D201" s="3"/>
       <c r="E201" s="6">
-        <v>3808.0</v>
+        <v>3808</v>
       </c>
       <c r="F201" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="202">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>6</v>
       </c>
@@ -4334,15 +4369,15 @@
       <c r="C202" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D202" s="7"/>
+      <c r="D202" s="3"/>
       <c r="E202" s="6">
-        <v>1428.0</v>
+        <v>1428</v>
       </c>
       <c r="F202" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="203">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>11</v>
       </c>
@@ -4352,15 +4387,15 @@
       <c r="C203" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D203" s="7"/>
+      <c r="D203" s="3"/>
       <c r="E203" s="6">
-        <v>4290.0</v>
+        <v>4290</v>
       </c>
       <c r="F203" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="204">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>11</v>
       </c>
@@ -4370,15 +4405,15 @@
       <c r="C204" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D204" s="7"/>
+      <c r="D204" s="3"/>
       <c r="E204" s="6">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="F204" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="205">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>15</v>
       </c>
@@ -4388,15 +4423,15 @@
       <c r="C205" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D205" s="7"/>
+      <c r="D205" s="3"/>
       <c r="E205" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F205" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="206">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>18</v>
       </c>
@@ -4406,15 +4441,15 @@
       <c r="C206" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D206" s="7"/>
+      <c r="D206" s="3"/>
       <c r="E206" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F206" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="207">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>21</v>
       </c>
@@ -4424,15 +4459,15 @@
       <c r="C207" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D207" s="7"/>
+      <c r="D207" s="3"/>
       <c r="E207" s="6">
-        <v>1160.0</v>
+        <v>1160</v>
       </c>
       <c r="F207" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="208">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>24</v>
       </c>
@@ -4442,15 +4477,15 @@
       <c r="C208" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D208" s="7"/>
+      <c r="D208" s="3"/>
       <c r="E208" s="6">
-        <v>1505.0</v>
+        <v>1505</v>
       </c>
       <c r="F208" s="5">
-        <v>46230.0</v>
-      </c>
-    </row>
-    <row r="209">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>6</v>
       </c>
@@ -4460,15 +4495,15 @@
       <c r="C209" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D209" s="7"/>
+      <c r="D209" s="3"/>
       <c r="E209" s="6">
-        <v>4284.0</v>
+        <v>4284</v>
       </c>
       <c r="F209" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="210">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>6</v>
       </c>
@@ -4478,15 +4513,15 @@
       <c r="C210" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D210" s="7"/>
+      <c r="D210" s="3"/>
       <c r="E210" s="6">
-        <v>3808.0</v>
+        <v>3808</v>
       </c>
       <c r="F210" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="211">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>6</v>
       </c>
@@ -4496,15 +4531,15 @@
       <c r="C211" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D211" s="7"/>
+      <c r="D211" s="3"/>
       <c r="E211" s="6">
-        <v>1428.0</v>
+        <v>1428</v>
       </c>
       <c r="F211" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="212">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>11</v>
       </c>
@@ -4514,15 +4549,15 @@
       <c r="C212" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D212" s="7"/>
+      <c r="D212" s="3"/>
       <c r="E212" s="6">
-        <v>4290.0</v>
+        <v>4290</v>
       </c>
       <c r="F212" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="213">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>11</v>
       </c>
@@ -4532,15 +4567,15 @@
       <c r="C213" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D213" s="7"/>
+      <c r="D213" s="3"/>
       <c r="E213" s="6">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="F213" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="214">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>15</v>
       </c>
@@ -4550,15 +4585,15 @@
       <c r="C214" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D214" s="7"/>
+      <c r="D214" s="3"/>
       <c r="E214" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F214" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="215">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>18</v>
       </c>
@@ -4568,15 +4603,15 @@
       <c r="C215" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D215" s="7"/>
+      <c r="D215" s="3"/>
       <c r="E215" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F215" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="216">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>21</v>
       </c>
@@ -4586,15 +4621,15 @@
       <c r="C216" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D216" s="7"/>
+      <c r="D216" s="3"/>
       <c r="E216" s="6">
-        <v>1160.0</v>
+        <v>1160</v>
       </c>
       <c r="F216" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="217">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>24</v>
       </c>
@@ -4604,15 +4639,15 @@
       <c r="C217" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D217" s="7"/>
+      <c r="D217" s="3"/>
       <c r="E217" s="6">
-        <v>1505.0</v>
+        <v>1505</v>
       </c>
       <c r="F217" s="5">
-        <v>46231.0</v>
-      </c>
-    </row>
-    <row r="218">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>6</v>
       </c>
@@ -4622,15 +4657,15 @@
       <c r="C218" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D218" s="7"/>
+      <c r="D218" s="3"/>
       <c r="E218" s="6">
-        <v>4284.0</v>
+        <v>4284</v>
       </c>
       <c r="F218" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="219">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>6</v>
       </c>
@@ -4640,15 +4675,15 @@
       <c r="C219" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D219" s="7"/>
+      <c r="D219" s="3"/>
       <c r="E219" s="6">
-        <v>3808.0</v>
+        <v>3808</v>
       </c>
       <c r="F219" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="220">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>6</v>
       </c>
@@ -4658,15 +4693,15 @@
       <c r="C220" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D220" s="7"/>
+      <c r="D220" s="3"/>
       <c r="E220" s="6">
-        <v>1428.0</v>
+        <v>1428</v>
       </c>
       <c r="F220" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="221">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>11</v>
       </c>
@@ -4676,15 +4711,15 @@
       <c r="C221" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D221" s="7"/>
+      <c r="D221" s="3"/>
       <c r="E221" s="6">
-        <v>4290.0</v>
+        <v>4290</v>
       </c>
       <c r="F221" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="222">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>11</v>
       </c>
@@ -4694,15 +4729,15 @@
       <c r="C222" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D222" s="7"/>
+      <c r="D222" s="3"/>
       <c r="E222" s="6">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="F222" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="223">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>15</v>
       </c>
@@ -4712,15 +4747,15 @@
       <c r="C223" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D223" s="7"/>
+      <c r="D223" s="3"/>
       <c r="E223" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F223" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="224">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>18</v>
       </c>
@@ -4730,15 +4765,15 @@
       <c r="C224" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D224" s="7"/>
+      <c r="D224" s="3"/>
       <c r="E224" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F224" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="225">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>21</v>
       </c>
@@ -4748,15 +4783,15 @@
       <c r="C225" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D225" s="7"/>
+      <c r="D225" s="3"/>
       <c r="E225" s="6">
-        <v>1160.0</v>
+        <v>1160</v>
       </c>
       <c r="F225" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>24</v>
       </c>
@@ -4766,15 +4801,15 @@
       <c r="C226" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D226" s="7"/>
+      <c r="D226" s="3"/>
       <c r="E226" s="6">
-        <v>1505.0</v>
+        <v>1505</v>
       </c>
       <c r="F226" s="5">
-        <v>46232.0</v>
-      </c>
-    </row>
-    <row r="227">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>6</v>
       </c>
@@ -4784,15 +4819,15 @@
       <c r="C227" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D227" s="7"/>
+      <c r="D227" s="3"/>
       <c r="E227" s="6">
-        <v>4284.0</v>
+        <v>4284</v>
       </c>
       <c r="F227" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="228">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>6</v>
       </c>
@@ -4802,15 +4837,15 @@
       <c r="C228" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D228" s="7"/>
+      <c r="D228" s="3"/>
       <c r="E228" s="6">
-        <v>3808.0</v>
+        <v>3808</v>
       </c>
       <c r="F228" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="229">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>6</v>
       </c>
@@ -4820,15 +4855,15 @@
       <c r="C229" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D229" s="7"/>
+      <c r="D229" s="3"/>
       <c r="E229" s="6">
-        <v>1428.0</v>
+        <v>1428</v>
       </c>
       <c r="F229" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="230">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>11</v>
       </c>
@@ -4838,15 +4873,15 @@
       <c r="C230" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D230" s="7"/>
+      <c r="D230" s="3"/>
       <c r="E230" s="6">
-        <v>4290.0</v>
+        <v>4290</v>
       </c>
       <c r="F230" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="231">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>11</v>
       </c>
@@ -4856,15 +4891,15 @@
       <c r="C231" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D231" s="7"/>
+      <c r="D231" s="3"/>
       <c r="E231" s="6">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="F231" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="232">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>15</v>
       </c>
@@ -4874,15 +4909,15 @@
       <c r="C232" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D232" s="7"/>
+      <c r="D232" s="3"/>
       <c r="E232" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F232" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="233">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>18</v>
       </c>
@@ -4892,15 +4927,15 @@
       <c r="C233" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D233" s="7"/>
+      <c r="D233" s="3"/>
       <c r="E233" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F233" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="234">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>21</v>
       </c>
@@ -4910,15 +4945,15 @@
       <c r="C234" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D234" s="7"/>
+      <c r="D234" s="3"/>
       <c r="E234" s="6">
-        <v>1160.0</v>
+        <v>1160</v>
       </c>
       <c r="F234" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="235">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>24</v>
       </c>
@@ -4928,15 +4963,15 @@
       <c r="C235" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D235" s="7"/>
+      <c r="D235" s="3"/>
       <c r="E235" s="6">
-        <v>1505.0</v>
+        <v>1505</v>
       </c>
       <c r="F235" s="5">
-        <v>46233.0</v>
-      </c>
-    </row>
-    <row r="236">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>6</v>
       </c>
@@ -4946,15 +4981,15 @@
       <c r="C236" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D236" s="7"/>
+      <c r="D236" s="3"/>
       <c r="E236" s="6">
-        <v>4284.0</v>
+        <v>4284</v>
       </c>
       <c r="F236" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="237">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>6</v>
       </c>
@@ -4964,15 +4999,15 @@
       <c r="C237" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D237" s="7"/>
+      <c r="D237" s="3"/>
       <c r="E237" s="6">
-        <v>3808.0</v>
+        <v>3808</v>
       </c>
       <c r="F237" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="238">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>6</v>
       </c>
@@ -4982,15 +5017,15 @@
       <c r="C238" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D238" s="7"/>
+      <c r="D238" s="3"/>
       <c r="E238" s="6">
-        <v>1428.0</v>
+        <v>1428</v>
       </c>
       <c r="F238" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="239">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>11</v>
       </c>
@@ -5000,15 +5035,15 @@
       <c r="C239" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D239" s="7"/>
+      <c r="D239" s="3"/>
       <c r="E239" s="6">
-        <v>4290.0</v>
+        <v>4290</v>
       </c>
       <c r="F239" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="240">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>11</v>
       </c>
@@ -5018,15 +5053,15 @@
       <c r="C240" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D240" s="7"/>
+      <c r="D240" s="3"/>
       <c r="E240" s="6">
-        <v>2860.0</v>
+        <v>2860</v>
       </c>
       <c r="F240" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="241">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>15</v>
       </c>
@@ -5036,15 +5071,15 @@
       <c r="C241" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D241" s="7"/>
+      <c r="D241" s="3"/>
       <c r="E241" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F241" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="242">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>18</v>
       </c>
@@ -5054,15 +5089,15 @@
       <c r="C242" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D242" s="7"/>
+      <c r="D242" s="3"/>
       <c r="E242" s="6">
-        <v>1710.0</v>
+        <v>1710</v>
       </c>
       <c r="F242" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="243">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>21</v>
       </c>
@@ -5072,15 +5107,15 @@
       <c r="C243" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D243" s="7"/>
+      <c r="D243" s="3"/>
       <c r="E243" s="6">
-        <v>1160.0</v>
+        <v>1160</v>
       </c>
       <c r="F243" s="5">
-        <v>46234.0</v>
-      </c>
-    </row>
-    <row r="244">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>24</v>
       </c>
@@ -5090,15 +5125,15 @@
       <c r="C244" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D244" s="7"/>
+      <c r="D244" s="3"/>
       <c r="E244" s="6">
-        <v>1505.0</v>
+        <v>1505</v>
       </c>
       <c r="F244" s="5">
-        <v>46234.0</v>
+        <v>46234</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E841FA3B-EF18-46C5-8A2B-F4B8753C72A5}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2746B70-D403-468D-A6FF-67C7BC8E24E6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3644,7 +3644,7 @@
         <v>23</v>
       </c>
       <c r="D162" s="3">
-        <v>767</v>
+        <v>767.5</v>
       </c>
       <c r="E162" s="6">
         <v>870</v>
@@ -3683,9 +3683,7 @@
       <c r="C164" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D164" s="3">
-        <v>966.5</v>
-      </c>
+      <c r="D164" s="3"/>
       <c r="E164" s="6">
         <v>3213</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2746B70-D403-468D-A6FF-67C7BC8E24E6}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36381623-FB46-47FE-9EFC-19A144E5B535}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="28">
   <si>
     <t>Cidade</t>
   </si>
@@ -102,6 +102,9 @@
   <si>
     <t>Junior</t>
   </si>
+  <si>
+    <t xml:space="preserve">Meta 100% </t>
+  </si>
 </sst>
 </file>
 
@@ -172,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -190,6 +193,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -410,10 +416,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:L244"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,8 +446,14 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -452,8 +472,20 @@
       <c r="F2" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -472,8 +504,21 @@
       <c r="F3" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="6">
+        <v>4284</v>
+      </c>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -492,8 +537,21 @@
       <c r="F4" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6">
+        <v>3808</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -512,8 +570,21 @@
       <c r="F5" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1428</v>
+      </c>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -532,8 +603,21 @@
       <c r="F6" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="6">
+        <v>4290</v>
+      </c>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -552,8 +636,21 @@
       <c r="F7" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="6">
+        <v>2860</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -572,8 +669,21 @@
       <c r="F8" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1710</v>
+      </c>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -592,8 +702,21 @@
       <c r="F9" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1710</v>
+      </c>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -612,8 +735,21 @@
       <c r="F10" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1160</v>
+      </c>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -632,8 +768,21 @@
       <c r="F11" s="5">
         <v>46205</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1505</v>
+      </c>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -652,8 +801,13 @@
       <c r="F12" s="5">
         <v>46205</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -673,7 +827,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -693,7 +847,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -713,7 +867,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -5132,6 +5286,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:K1"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36381623-FB46-47FE-9EFC-19A144E5B535}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82DFF625-BADB-4A41-927C-13F353F24B7F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Página1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="30">
   <si>
     <t>Cidade</t>
   </si>
@@ -105,6 +105,12 @@
   <si>
     <t xml:space="preserve">Meta 100% </t>
   </si>
+  <si>
+    <t xml:space="preserve">Checkpoint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data limite </t>
+  </si>
 </sst>
 </file>
 
@@ -175,27 +181,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -416,4874 +437,5152 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L244"/>
+  <dimension ref="A1:N244"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="4"/>
+    <col min="2" max="2" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="12.5703125" style="4"/>
+    <col min="7" max="7" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="12.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="M1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="6">
         <v>574.5</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="7">
         <v>1071</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="8">
         <v>46204</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="M2" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="N2" s="12">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="6">
         <v>426.5</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="5">
         <v>952</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="8">
         <v>46204</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="9">
         <v>4284</v>
       </c>
-      <c r="L3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="L3" s="7"/>
+      <c r="M3" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="N3" s="12">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="6">
         <v>68.5</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="5">
         <v>357</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="8">
         <v>46204</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="9">
         <v>3808</v>
       </c>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="L4" s="5"/>
+      <c r="M4" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="N4" s="12">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="6">
         <v>352</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="8">
         <v>46204</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="9">
         <v>1428</v>
       </c>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="L5" s="5"/>
+      <c r="M5" s="11">
+        <v>1</v>
+      </c>
+      <c r="N5" s="12">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="6">
         <v>195.5</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="5">
         <v>715</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="8">
         <v>46204</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="G6" s="1"/>
+      <c r="H6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="9">
         <v>4290</v>
       </c>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="6">
         <v>46.5</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="5">
         <v>427.5</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="8">
         <v>46204</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="G7" s="1"/>
+      <c r="H7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="9">
         <v>2860</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="6">
         <v>116</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="5">
         <v>427.5</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="8">
         <v>46204</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="1"/>
+      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="9">
         <v>1710</v>
       </c>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="6">
         <v>43.5</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="5">
         <v>290</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="8">
         <v>46204</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="G9" s="1"/>
+      <c r="H9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="9">
         <v>1710</v>
       </c>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="6">
         <v>92</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="5">
         <v>376.5</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="8">
         <v>46204</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="G10" s="1"/>
+      <c r="H10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="9">
         <v>1160</v>
       </c>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="6">
         <v>861</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="7">
         <v>1071</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="8">
         <v>46205</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="G11" s="1"/>
+      <c r="H11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="9">
         <v>1505</v>
       </c>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="6">
         <v>507.5</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="5">
         <v>952</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="8">
         <v>46205</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="G12" s="1"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="6">
         <v>129.5</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="5">
         <v>357</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="8">
         <v>46205</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="6">
         <v>451.5</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="8">
         <v>46205</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="6">
         <v>297.5</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="5">
         <v>715</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="8">
         <v>46205</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="6">
         <v>142</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="5">
         <v>427.5</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="8">
         <v>46205</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="6">
         <v>213</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="5">
         <v>427.5</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="8">
         <v>46205</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="6">
         <v>58</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="5">
         <v>290</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="8">
         <v>46205</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="6">
         <v>186.5</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="5">
         <v>376.5</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="8">
         <v>46205</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="6">
         <v>927</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="7">
         <v>1071</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="6">
         <v>680</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="5">
         <v>952</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="6">
         <v>172.5</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="5">
         <v>357</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="6">
         <v>451.5</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="6">
         <v>304.5</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="5">
         <v>715</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="6">
         <v>142</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="5">
         <v>427.5</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="6">
         <v>246</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="5">
         <v>427.5</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="6">
         <v>56</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="5">
         <v>290</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="6">
         <v>214.5</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="5">
         <v>376.5</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="8">
         <v>46206</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="6">
         <v>955</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="7">
         <v>1071</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="6">
         <v>719</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="5">
         <v>952</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="6">
         <v>177</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="5">
         <v>357</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="6">
         <v>472.5</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="6">
         <v>304.5</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="5">
         <v>715</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="6">
         <v>150</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="5">
         <v>427.5</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="6">
         <v>254</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="5">
         <v>427.5</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="6">
         <v>68</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="5">
         <v>290</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="6">
         <v>231.5</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="5">
         <v>376.5</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="8">
         <v>46207</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="6">
         <v>1019</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="7">
         <v>1071</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="6">
         <v>969</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="5">
         <v>952</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="6">
         <v>187</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="5">
         <v>357</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="6">
         <v>613.5</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="6">
         <v>369.5</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="5">
         <v>715</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="6">
         <v>152.5</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="5">
         <v>427.5</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="6">
         <v>348</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="5">
         <v>427.5</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="6">
         <v>84</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="5">
         <v>290</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="6">
         <v>315</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="5">
         <v>376.5</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="8">
         <v>46209</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="6">
         <v>1088</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="7">
         <v>1071</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="6">
         <v>1009</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="5">
         <v>952</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="6">
         <v>235</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="5">
         <v>357</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="6">
         <v>692</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="6">
         <v>444</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="5">
         <v>715</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="6">
         <v>203</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="5">
         <v>427.5</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="6">
         <v>452</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="5">
         <v>427.5</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="6">
         <v>178</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="5">
         <v>290</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="6">
         <v>351.5</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="5">
         <v>376.5</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="8">
         <v>46210</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="6">
         <v>1237.5</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="7">
         <v>1071</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="6">
         <v>1175.5</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="5">
         <v>952</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="6">
         <v>381.5</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="5">
         <v>357</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="6">
         <v>819</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="6">
         <v>622</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="5">
         <v>715</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="6">
         <v>243.5</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="5">
         <v>427.5</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="6">
         <v>508.5</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="5">
         <v>427.5</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="6">
         <v>262.5</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="5">
         <v>290</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="6">
         <v>409</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="5">
         <v>376.5</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="8">
         <v>46211</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="6">
         <v>1358</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="7">
         <v>1071</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="6">
         <v>1311</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="5">
         <v>952</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F66" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="6">
         <v>412.5</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="5">
         <v>357</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F67" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+      <c r="G67" s="1"/>
+    </row>
+    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="6">
         <v>946.5</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="7">
         <v>1072.5</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="6">
         <v>731.5</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="5">
         <v>715</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="G69" s="1"/>
+    </row>
+    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A70" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="6">
         <v>309.5</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="5">
         <v>427.5</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+      <c r="G70" s="1"/>
+    </row>
+    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A71" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="6">
         <v>641.5</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="5">
         <v>427.5</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
+      <c r="G71" s="1"/>
+    </row>
+    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="6">
         <v>408.5</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="5">
         <v>290</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
+      <c r="G72" s="1"/>
+    </row>
+    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="6">
         <v>456</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="5">
         <v>376.5</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="8">
         <v>46212</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="G73" s="1"/>
+    </row>
+    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="6">
         <v>1535</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="7">
         <v>2142</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="G74" s="1"/>
+    </row>
+    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="6">
         <v>1404</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E75" s="7">
         <v>1904</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F75" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="G75" s="1"/>
+    </row>
+    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="6">
         <v>484.5</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="5">
         <v>714</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77" s="6">
         <v>1092</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E77" s="7">
         <v>2154</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
+      <c r="G77" s="1"/>
+    </row>
+    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="6">
         <v>879.5</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E78" s="7">
         <v>1430</v>
       </c>
-      <c r="F78" s="5">
+      <c r="F78" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
+      <c r="G78" s="1"/>
+    </row>
+    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79" s="6">
         <v>446</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="5">
         <v>855</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
+      <c r="G79" s="1"/>
+    </row>
+    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80" s="6">
         <v>712</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="5">
         <v>855</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+      <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A81" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="6">
         <v>455</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="5">
         <v>580</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A82" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="6">
         <v>523.5</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="5">
         <v>752</v>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="8">
         <v>46213</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="2" t="s">
+      <c r="G82" s="1"/>
+    </row>
+    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="6">
         <v>1631.5</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E83" s="7">
         <v>2142</v>
       </c>
-      <c r="F83" s="5">
+      <c r="F83" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="G83" s="1"/>
+    </row>
+    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="6">
         <v>1480</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E84" s="7">
         <v>1904</v>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="2" t="s">
+      <c r="G84" s="1"/>
+    </row>
+    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85" s="6">
         <v>484.5</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="5">
         <v>714</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
+      <c r="G85" s="1"/>
+    </row>
+    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="6">
         <v>1130.5</v>
       </c>
-      <c r="E86" s="4">
+      <c r="E86" s="7">
         <v>2154</v>
       </c>
-      <c r="F86" s="5">
+      <c r="F86" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
+      <c r="G86" s="1"/>
+    </row>
+    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="6">
         <v>884</v>
       </c>
-      <c r="E87" s="4">
+      <c r="E87" s="7">
         <v>1430</v>
       </c>
-      <c r="F87" s="5">
+      <c r="F87" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+      <c r="G87" s="1"/>
+    </row>
+    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A88" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88" s="6">
         <v>446</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="5">
         <v>855</v>
       </c>
-      <c r="F88" s="5">
+      <c r="F88" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+      <c r="G88" s="1"/>
+    </row>
+    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A89" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="6">
         <v>712.5</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="5">
         <v>855</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
+      <c r="G89" s="1"/>
+    </row>
+    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="6">
         <v>455</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="5">
         <v>580</v>
       </c>
-      <c r="F90" s="5">
+      <c r="F90" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
+      <c r="G90" s="1"/>
+    </row>
+    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A91" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="6">
         <v>523.5</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="5">
         <v>752</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="8">
         <v>46214</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="G91" s="1"/>
+    </row>
+    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A92" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="6">
         <v>1752.5</v>
       </c>
-      <c r="E92" s="4">
+      <c r="E92" s="7">
         <v>2142</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="2" t="s">
+      <c r="G92" s="1"/>
+    </row>
+    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D93" s="6">
         <v>1638.5</v>
       </c>
-      <c r="E93" s="4">
+      <c r="E93" s="7">
         <v>1904</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="G93" s="1"/>
+    </row>
+    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="6">
         <v>493.5</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="5">
         <v>714</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
+      <c r="G94" s="1"/>
+    </row>
+    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A95" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D95" s="6">
         <v>1280.5</v>
       </c>
-      <c r="E95" s="4">
+      <c r="E95" s="7">
         <v>2154</v>
       </c>
-      <c r="F95" s="5">
+      <c r="F95" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
+      <c r="G95" s="1"/>
+    </row>
+    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="6">
         <v>990</v>
       </c>
-      <c r="E96" s="4">
+      <c r="E96" s="7">
         <v>1430</v>
       </c>
-      <c r="F96" s="5">
+      <c r="F96" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+      <c r="G96" s="1"/>
+    </row>
+    <row r="97" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A97" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D97" s="6">
         <v>481</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="5">
         <v>855</v>
       </c>
-      <c r="F97" s="5">
+      <c r="F97" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
+      <c r="G97" s="1"/>
+    </row>
+    <row r="98" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A98" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="6">
         <v>786</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="5">
         <v>855</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+      <c r="G98" s="1"/>
+    </row>
+    <row r="99" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A99" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="6">
         <v>494</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="5">
         <v>580</v>
       </c>
-      <c r="F99" s="5">
+      <c r="F99" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+      <c r="G99" s="1"/>
+    </row>
+    <row r="100" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="6">
         <v>653.5</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="5">
         <v>752</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="8">
         <v>46216</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C101" s="2" t="s">
+      <c r="G100" s="1"/>
+    </row>
+    <row r="101" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="6">
         <v>1835</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E101" s="7">
         <v>2142</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="G101" s="1"/>
+    </row>
+    <row r="102" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="6">
         <v>1945</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E102" s="7">
         <v>1904</v>
       </c>
-      <c r="F102" s="5">
+      <c r="F102" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C103" s="2" t="s">
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D103" s="6">
         <v>538.5</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="5">
         <v>714</v>
       </c>
-      <c r="F103" s="5">
+      <c r="F103" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
+      <c r="G103" s="1"/>
+    </row>
+    <row r="104" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="6">
         <v>1400.5</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="7">
         <v>2154</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D105" s="6">
         <v>1120.5</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="7">
         <v>1430</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
+      <c r="G105" s="1"/>
+    </row>
+    <row r="106" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D106" s="6">
         <v>606</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="5">
         <v>855</v>
       </c>
-      <c r="F106" s="5">
+      <c r="F106" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D107" s="6">
         <v>894.5</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="5">
         <v>855</v>
       </c>
-      <c r="F107" s="5">
+      <c r="F107" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D108" s="6">
         <v>509</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="5">
         <v>580</v>
       </c>
-      <c r="F108" s="5">
+      <c r="F108" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="6">
         <v>752</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="5">
         <v>752</v>
       </c>
-      <c r="F109" s="5">
+      <c r="F109" s="8">
         <v>46217</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" s="2" t="s">
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="6">
         <v>1972</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="7">
         <v>2142</v>
       </c>
-      <c r="F110" s="5">
+      <c r="F110" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" s="2" t="s">
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A111" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D111" s="6">
         <v>2133.5</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="7">
         <v>1904</v>
       </c>
-      <c r="F111" s="5">
+      <c r="F111" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C112" s="2" t="s">
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A112" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112" s="6">
         <v>588</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="5">
         <v>714</v>
       </c>
-      <c r="F112" s="5">
+      <c r="F112" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D113" s="6">
         <v>1473.5</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E113" s="7">
         <v>2154</v>
       </c>
-      <c r="F113" s="5">
+      <c r="F113" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
+      <c r="G113" s="1"/>
+    </row>
+    <row r="114" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A114" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D114" s="6">
         <v>1236</v>
       </c>
-      <c r="E114" s="4">
+      <c r="E114" s="7">
         <v>1430</v>
       </c>
-      <c r="F114" s="5">
+      <c r="F114" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
+      <c r="G114" s="1"/>
+    </row>
+    <row r="115" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A115" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D115" s="6">
         <v>676</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115" s="5">
         <v>855</v>
       </c>
-      <c r="F115" s="5">
+      <c r="F115" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A116" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D116" s="6">
         <v>938.5</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="5">
         <v>855</v>
       </c>
-      <c r="F116" s="5">
+      <c r="F116" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A117" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117" s="6">
         <v>561.5</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="5">
         <v>580</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A118" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D118" s="6">
         <v>904</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E118" s="5">
         <v>752</v>
       </c>
-      <c r="F118" s="5">
+      <c r="F118" s="8">
         <v>46218</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C119" s="2" t="s">
+      <c r="G118" s="1"/>
+    </row>
+    <row r="119" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A119" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119" s="6">
         <v>2136.5</v>
       </c>
-      <c r="E119" s="4">
+      <c r="E119" s="7">
         <v>2142</v>
       </c>
-      <c r="F119" s="5">
+      <c r="F119" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C120" s="2" t="s">
+      <c r="G119" s="1"/>
+    </row>
+    <row r="120" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A120" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120" s="6">
         <v>2318.5</v>
       </c>
-      <c r="E120" s="4">
+      <c r="E120" s="7">
         <v>1904</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C121" s="2" t="s">
+      <c r="G120" s="1"/>
+    </row>
+    <row r="121" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A121" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D121" s="3">
+      <c r="D121" s="6">
         <v>618</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="5">
         <v>714</v>
       </c>
-      <c r="F121" s="5">
+      <c r="F121" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
+      <c r="G121" s="1"/>
+    </row>
+    <row r="122" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A122" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D122" s="3">
+      <c r="D122" s="6">
         <v>1632</v>
       </c>
-      <c r="E122" s="4">
+      <c r="E122" s="7">
         <v>2154</v>
       </c>
-      <c r="F122" s="5">
+      <c r="F122" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
+      <c r="G122" s="1"/>
+    </row>
+    <row r="123" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A123" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D123" s="3">
+      <c r="D123" s="6">
         <v>1307.5</v>
       </c>
-      <c r="E123" s="4">
+      <c r="E123" s="7">
         <v>1430</v>
       </c>
-      <c r="F123" s="5">
+      <c r="F123" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
+      <c r="G123" s="1"/>
+    </row>
+    <row r="124" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A124" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124" s="6">
         <v>756</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="5">
         <v>855</v>
       </c>
-      <c r="F124" s="5">
+      <c r="F124" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
+      <c r="G124" s="1"/>
+    </row>
+    <row r="125" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A125" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125" s="6">
         <v>1005.5</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="5">
         <v>855</v>
       </c>
-      <c r="F125" s="5">
+      <c r="F125" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
+      <c r="G125" s="1"/>
+    </row>
+    <row r="126" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A126" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126" s="6">
         <v>614</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="5">
         <v>580</v>
       </c>
-      <c r="F126" s="5">
+      <c r="F126" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
+      <c r="G126" s="1"/>
+    </row>
+    <row r="127" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A127" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D127" s="3">
+      <c r="D127" s="6">
         <v>988</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E127" s="5">
         <v>752</v>
       </c>
-      <c r="F127" s="5">
+      <c r="F127" s="8">
         <v>46219</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="2" t="s">
+      <c r="G127" s="1"/>
+    </row>
+    <row r="128" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A128" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D128" s="3">
+      <c r="D128" s="6">
         <v>2406.5</v>
       </c>
-      <c r="E128" s="6">
+      <c r="E128" s="9">
         <v>3213</v>
       </c>
-      <c r="F128" s="5">
+      <c r="F128" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C129" s="2" t="s">
+      <c r="G128" s="1"/>
+    </row>
+    <row r="129" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A129" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D129" s="3">
+      <c r="D129" s="6">
         <v>2412.5</v>
       </c>
-      <c r="E129" s="6">
+      <c r="E129" s="9">
         <v>2856</v>
       </c>
-      <c r="F129" s="5">
+      <c r="F129" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C130" s="2" t="s">
+      <c r="G129" s="1"/>
+    </row>
+    <row r="130" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A130" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130" s="6">
         <v>618.5</v>
       </c>
-      <c r="E130" s="6">
+      <c r="E130" s="9">
         <v>1071</v>
       </c>
-      <c r="F130" s="5">
+      <c r="F130" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
+      <c r="G130" s="1"/>
+    </row>
+    <row r="131" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A131" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D131" s="3">
+      <c r="D131" s="6">
         <v>1786.5</v>
       </c>
-      <c r="E131" s="6">
+      <c r="E131" s="9">
         <v>3217.5</v>
       </c>
-      <c r="F131" s="5">
+      <c r="F131" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A132" s="2" t="s">
+      <c r="G131" s="1"/>
+    </row>
+    <row r="132" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A132" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D132" s="3">
+      <c r="D132" s="6">
         <v>1397</v>
       </c>
-      <c r="E132" s="6">
+      <c r="E132" s="9">
         <v>2145</v>
       </c>
-      <c r="F132" s="5">
+      <c r="F132" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A133" s="2" t="s">
+      <c r="G132" s="1"/>
+    </row>
+    <row r="133" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A133" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133" s="6">
         <v>806</v>
       </c>
-      <c r="E133" s="6">
+      <c r="E133" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F133" s="5">
+      <c r="F133" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
+      <c r="G133" s="1"/>
+    </row>
+    <row r="134" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A134" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134" s="6">
         <v>1077.5</v>
       </c>
-      <c r="E134" s="6">
+      <c r="E134" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F134" s="5">
+      <c r="F134" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
+      <c r="G134" s="1"/>
+    </row>
+    <row r="135" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A135" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135" s="6">
         <v>667</v>
       </c>
-      <c r="E135" s="6">
+      <c r="E135" s="9">
         <v>870</v>
       </c>
-      <c r="F135" s="5">
+      <c r="F135" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
+      <c r="G135" s="1"/>
+    </row>
+    <row r="136" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A136" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136" s="6">
         <v>1141</v>
       </c>
-      <c r="E136" s="6">
+      <c r="E136" s="9">
         <v>1128.75</v>
       </c>
-      <c r="F136" s="5">
+      <c r="F136" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C137" s="2" t="s">
+      <c r="G136" s="1"/>
+    </row>
+    <row r="137" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A137" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D137" s="6">
         <v>2530</v>
       </c>
-      <c r="E137" s="6">
+      <c r="E137" s="9">
         <v>3213</v>
       </c>
-      <c r="F137" s="5">
+      <c r="F137" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C138" s="2" t="s">
+      <c r="G137" s="1"/>
+    </row>
+    <row r="138" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D138" s="6">
         <v>2503</v>
       </c>
-      <c r="E138" s="6">
+      <c r="E138" s="9">
         <v>2856</v>
       </c>
-      <c r="F138" s="5">
+      <c r="F138" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C139" s="2" t="s">
+      <c r="G138" s="1"/>
+    </row>
+    <row r="139" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D139" s="3">
+      <c r="D139" s="6">
         <v>629</v>
       </c>
-      <c r="E139" s="6">
+      <c r="E139" s="9">
         <v>1071</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
+      <c r="G139" s="1"/>
+    </row>
+    <row r="140" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A140" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D140" s="3">
+      <c r="D140" s="6">
         <v>1871</v>
       </c>
-      <c r="E140" s="6">
+      <c r="E140" s="9">
         <v>3217.5</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
+      <c r="G140" s="1"/>
+    </row>
+    <row r="141" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A141" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D141" s="3">
+      <c r="D141" s="6">
         <v>1484</v>
       </c>
-      <c r="E141" s="6">
+      <c r="E141" s="9">
         <v>2145</v>
       </c>
-      <c r="F141" s="5">
+      <c r="F141" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
+      <c r="G141" s="1"/>
+    </row>
+    <row r="142" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A142" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D142" s="3">
+      <c r="D142" s="6">
         <v>814</v>
       </c>
-      <c r="E142" s="6">
+      <c r="E142" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F142" s="5">
+      <c r="F142" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A143" s="2" t="s">
+      <c r="G142" s="1"/>
+    </row>
+    <row r="143" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A143" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D143" s="3">
+      <c r="D143" s="6">
         <v>1077.5</v>
       </c>
-      <c r="E143" s="6">
+      <c r="E143" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
+      <c r="G143" s="1"/>
+    </row>
+    <row r="144" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A144" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D144" s="3">
+      <c r="D144" s="6">
         <v>677</v>
       </c>
-      <c r="E144" s="6">
+      <c r="E144" s="9">
         <v>870</v>
       </c>
-      <c r="F144" s="5">
+      <c r="F144" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A145" s="2" t="s">
+      <c r="G144" s="1"/>
+    </row>
+    <row r="145" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A145" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D145" s="3">
+      <c r="D145" s="6">
         <v>1158</v>
       </c>
-      <c r="E145" s="6">
+      <c r="E145" s="9">
         <v>1128.75</v>
       </c>
-      <c r="F145" s="5">
+      <c r="F145" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A146" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C146" s="2" t="s">
+      <c r="G145" s="1"/>
+    </row>
+    <row r="146" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A146" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D146" s="3">
+      <c r="D146" s="6">
         <v>2734.5</v>
       </c>
-      <c r="E146" s="6">
+      <c r="E146" s="9">
         <v>3213</v>
       </c>
-      <c r="F146" s="5">
+      <c r="F146" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" s="2" t="s">
+      <c r="G146" s="1"/>
+    </row>
+    <row r="147" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A147" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D147" s="3">
+      <c r="D147" s="6">
         <v>2626</v>
       </c>
-      <c r="E147" s="6">
+      <c r="E147" s="9">
         <v>2856</v>
       </c>
-      <c r="F147" s="5">
+      <c r="F147" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="2" t="s">
+      <c r="G147" s="1"/>
+    </row>
+    <row r="148" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A148" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D148" s="3">
+      <c r="D148" s="6">
         <v>660</v>
       </c>
-      <c r="E148" s="6">
+      <c r="E148" s="9">
         <v>1071</v>
       </c>
-      <c r="F148" s="5">
+      <c r="F148" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
+      <c r="G148" s="1"/>
+    </row>
+    <row r="149" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A149" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D149" s="3">
+      <c r="D149" s="6">
         <v>1956.5</v>
       </c>
-      <c r="E149" s="6">
+      <c r="E149" s="9">
         <v>3217.5</v>
       </c>
-      <c r="F149" s="5">
+      <c r="F149" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
+      <c r="G149" s="1"/>
+    </row>
+    <row r="150" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A150" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D150" s="3">
+      <c r="D150" s="6">
         <v>1632.5</v>
       </c>
-      <c r="E150" s="6">
+      <c r="E150" s="9">
         <v>2145</v>
       </c>
-      <c r="F150" s="5">
+      <c r="F150" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A151" s="2" t="s">
+      <c r="G150" s="1"/>
+    </row>
+    <row r="151" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A151" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D151" s="3">
+      <c r="D151" s="6">
         <v>831</v>
       </c>
-      <c r="E151" s="6">
+      <c r="E151" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F151" s="5">
+      <c r="F151" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
+      <c r="G151" s="1"/>
+    </row>
+    <row r="152" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A152" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D152" s="3">
+      <c r="D152" s="6">
         <v>1144</v>
       </c>
-      <c r="E152" s="6">
+      <c r="E152" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F152" s="5">
+      <c r="F152" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A153" s="2" t="s">
+      <c r="G152" s="1"/>
+    </row>
+    <row r="153" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A153" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B153" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D153" s="3">
+      <c r="D153" s="6">
         <v>751.5</v>
       </c>
-      <c r="E153" s="6">
+      <c r="E153" s="9">
         <v>870</v>
       </c>
-      <c r="F153" s="5">
+      <c r="F153" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
+      <c r="G153" s="1"/>
+    </row>
+    <row r="154" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A154" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D154" s="3">
+      <c r="D154" s="6">
         <v>1185</v>
       </c>
-      <c r="E154" s="6">
+      <c r="E154" s="9">
         <v>1128.75</v>
       </c>
-      <c r="F154" s="5">
+      <c r="F154" s="8">
         <v>46223</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A155" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="G154" s="1"/>
+    </row>
+    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A155" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D155" s="3">
+      <c r="D155" s="6">
         <v>2890</v>
       </c>
-      <c r="E155" s="6">
+      <c r="E155" s="9">
         <v>3213</v>
       </c>
-      <c r="F155" s="5">
+      <c r="F155" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C156" s="2" t="s">
+      <c r="G155" s="1"/>
+    </row>
+    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A156" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D156" s="3">
+      <c r="D156" s="6">
         <v>2760</v>
       </c>
-      <c r="E156" s="6">
+      <c r="E156" s="9">
         <v>2856</v>
       </c>
-      <c r="F156" s="5">
+      <c r="F156" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A157" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C157" s="2" t="s">
+      <c r="G156" s="1"/>
+    </row>
+    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A157" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D157" s="3">
+      <c r="D157" s="6">
         <v>709</v>
       </c>
-      <c r="E157" s="6">
+      <c r="E157" s="9">
         <v>1071</v>
       </c>
-      <c r="F157" s="5">
+      <c r="F157" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A158" s="2" t="s">
+      <c r="G157" s="1"/>
+    </row>
+    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A158" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D158" s="3">
+      <c r="D158" s="6">
         <v>2006</v>
       </c>
-      <c r="E158" s="6">
+      <c r="E158" s="9">
         <v>3217.5</v>
       </c>
-      <c r="F158" s="5">
+      <c r="F158" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
+      <c r="G158" s="1"/>
+    </row>
+    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A159" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D159" s="3">
+      <c r="D159" s="6">
         <v>1707</v>
       </c>
-      <c r="E159" s="6">
+      <c r="E159" s="9">
         <v>2145</v>
       </c>
-      <c r="F159" s="5">
+      <c r="F159" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A160" s="2" t="s">
+      <c r="G159" s="1"/>
+    </row>
+    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A160" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B160" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D160" s="3">
+      <c r="D160" s="6">
         <v>908</v>
       </c>
-      <c r="E160" s="6">
+      <c r="E160" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F160" s="5">
+      <c r="F160" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A161" s="2" t="s">
+      <c r="G160" s="1"/>
+    </row>
+    <row r="161" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A161" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D161" s="3">
+      <c r="D161" s="6">
         <v>1300.5</v>
       </c>
-      <c r="E161" s="6">
+      <c r="E161" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F161" s="5">
+      <c r="F161" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A162" s="2" t="s">
+      <c r="G161" s="1"/>
+    </row>
+    <row r="162" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A162" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B162" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D162" s="3">
+      <c r="D162" s="6">
         <v>767.5</v>
       </c>
-      <c r="E162" s="6">
+      <c r="E162" s="9">
         <v>870</v>
       </c>
-      <c r="F162" s="5">
+      <c r="F162" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A163" s="2" t="s">
+      <c r="G162" s="1"/>
+    </row>
+    <row r="163" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A163" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D163" s="3">
+      <c r="D163" s="6">
         <v>1250.5</v>
       </c>
-      <c r="E163" s="6">
+      <c r="E163" s="9">
         <v>1128.75</v>
       </c>
-      <c r="F163" s="5">
+      <c r="F163" s="8">
         <v>46224</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" s="2" t="s">
+      <c r="G163" s="1"/>
+    </row>
+    <row r="164" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A164" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D164" s="3"/>
-      <c r="E164" s="6">
+      <c r="D164" s="6"/>
+      <c r="E164" s="9">
         <v>3213</v>
       </c>
-      <c r="F164" s="5">
+      <c r="F164" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A165" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" s="2" t="s">
+      <c r="G164" s="1"/>
+    </row>
+    <row r="165" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A165" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D165" s="3"/>
-      <c r="E165" s="6">
+      <c r="D165" s="6"/>
+      <c r="E165" s="9">
         <v>2856</v>
       </c>
-      <c r="F165" s="5">
+      <c r="F165" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A166" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" s="2" t="s">
+      <c r="G165" s="1"/>
+    </row>
+    <row r="166" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A166" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D166" s="3"/>
-      <c r="E166" s="6">
+      <c r="D166" s="6"/>
+      <c r="E166" s="9">
         <v>1071</v>
       </c>
-      <c r="F166" s="5">
+      <c r="F166" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A167" s="2" t="s">
+      <c r="G166" s="1"/>
+    </row>
+    <row r="167" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A167" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D167" s="3"/>
-      <c r="E167" s="6">
+      <c r="D167" s="6"/>
+      <c r="E167" s="9">
         <v>3217.5</v>
       </c>
-      <c r="F167" s="5">
+      <c r="F167" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A168" s="2" t="s">
+      <c r="G167" s="1"/>
+    </row>
+    <row r="168" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A168" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D168" s="3"/>
-      <c r="E168" s="6">
+      <c r="D168" s="6"/>
+      <c r="E168" s="9">
         <v>2145</v>
       </c>
-      <c r="F168" s="5">
+      <c r="F168" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A169" s="2" t="s">
+      <c r="G168" s="1"/>
+    </row>
+    <row r="169" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A169" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C169" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D169" s="3"/>
-      <c r="E169" s="6">
+      <c r="D169" s="6"/>
+      <c r="E169" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F169" s="5">
+      <c r="F169" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
+      <c r="G169" s="1"/>
+    </row>
+    <row r="170" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A170" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="C170" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D170" s="3"/>
-      <c r="E170" s="6">
+      <c r="D170" s="6"/>
+      <c r="E170" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F170" s="5">
+      <c r="F170" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A171" s="2" t="s">
+      <c r="G170" s="1"/>
+    </row>
+    <row r="171" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A171" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="C171" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D171" s="3"/>
-      <c r="E171" s="6">
+      <c r="D171" s="6"/>
+      <c r="E171" s="9">
         <v>870</v>
       </c>
-      <c r="F171" s="5">
+      <c r="F171" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
+      <c r="G171" s="1"/>
+    </row>
+    <row r="172" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A172" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="C172" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D172" s="3"/>
-      <c r="E172" s="6">
+      <c r="D172" s="6"/>
+      <c r="E172" s="9">
         <v>1128.75</v>
       </c>
-      <c r="F172" s="5">
+      <c r="F172" s="8">
         <v>46225</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A173" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C173" s="2" t="s">
+      <c r="G172" s="1"/>
+    </row>
+    <row r="173" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A173" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D173" s="3"/>
-      <c r="E173" s="6">
+      <c r="D173" s="6"/>
+      <c r="E173" s="9">
         <v>3213</v>
       </c>
-      <c r="F173" s="5">
+      <c r="F173" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" s="2" t="s">
+      <c r="G173" s="1"/>
+    </row>
+    <row r="174" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A174" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D174" s="3"/>
-      <c r="E174" s="6">
+      <c r="D174" s="6"/>
+      <c r="E174" s="9">
         <v>2856</v>
       </c>
-      <c r="F174" s="5">
+      <c r="F174" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="G174" s="1"/>
+    </row>
+    <row r="175" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A175" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D175" s="3"/>
-      <c r="E175" s="6">
+      <c r="D175" s="6"/>
+      <c r="E175" s="9">
         <v>1071</v>
       </c>
-      <c r="F175" s="5">
+      <c r="F175" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A176" s="2" t="s">
+      <c r="G175" s="1"/>
+    </row>
+    <row r="176" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A176" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="B176" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C176" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D176" s="3"/>
-      <c r="E176" s="6">
+      <c r="D176" s="6"/>
+      <c r="E176" s="9">
         <v>3217.5</v>
       </c>
-      <c r="F176" s="5">
+      <c r="F176" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
+      <c r="G176" s="1"/>
+    </row>
+    <row r="177" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A177" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B177" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C177" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D177" s="3"/>
-      <c r="E177" s="6">
+      <c r="D177" s="6"/>
+      <c r="E177" s="9">
         <v>2145</v>
       </c>
-      <c r="F177" s="5">
+      <c r="F177" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A178" s="2" t="s">
+      <c r="G177" s="1"/>
+    </row>
+    <row r="178" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A178" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B178" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="C178" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D178" s="3"/>
-      <c r="E178" s="6">
+      <c r="D178" s="6"/>
+      <c r="E178" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F178" s="5">
+      <c r="F178" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A179" s="2" t="s">
+      <c r="G178" s="1"/>
+    </row>
+    <row r="179" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A179" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B179" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="C179" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D179" s="3"/>
-      <c r="E179" s="6">
+      <c r="D179" s="6"/>
+      <c r="E179" s="9">
         <v>1282.5</v>
       </c>
-      <c r="F179" s="5">
+      <c r="F179" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
+      <c r="G179" s="1"/>
+    </row>
+    <row r="180" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A180" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B180" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C180" s="2" t="s">
+      <c r="C180" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D180" s="3"/>
-      <c r="E180" s="6">
+      <c r="D180" s="6"/>
+      <c r="E180" s="9">
         <v>870</v>
       </c>
-      <c r="F180" s="5">
+      <c r="F180" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
+      <c r="G180" s="1"/>
+    </row>
+    <row r="181" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A181" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B181" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C181" s="2" t="s">
+      <c r="C181" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D181" s="3"/>
-      <c r="E181" s="6">
+      <c r="D181" s="6"/>
+      <c r="E181" s="9">
         <v>1128.75</v>
       </c>
-      <c r="F181" s="5">
+      <c r="F181" s="8">
         <v>46226</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C182" s="2" t="s">
+      <c r="G181" s="1"/>
+    </row>
+    <row r="182" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A182" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D182" s="3"/>
-      <c r="E182" s="6">
+      <c r="D182" s="6"/>
+      <c r="E182" s="9">
         <v>4284</v>
       </c>
-      <c r="F182" s="5">
+      <c r="F182" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C183" s="2" t="s">
+      <c r="G182" s="1"/>
+    </row>
+    <row r="183" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A183" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D183" s="3"/>
-      <c r="E183" s="6">
+      <c r="D183" s="6"/>
+      <c r="E183" s="9">
         <v>3808</v>
       </c>
-      <c r="F183" s="5">
+      <c r="F183" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C184" s="2" t="s">
+      <c r="G183" s="1"/>
+    </row>
+    <row r="184" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A184" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D184" s="3"/>
-      <c r="E184" s="6">
+      <c r="D184" s="6"/>
+      <c r="E184" s="9">
         <v>1428</v>
       </c>
-      <c r="F184" s="5">
+      <c r="F184" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A185" s="2" t="s">
+      <c r="G184" s="1"/>
+    </row>
+    <row r="185" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A185" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B185" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C185" s="2" t="s">
+      <c r="C185" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D185" s="3"/>
-      <c r="E185" s="6">
+      <c r="D185" s="6"/>
+      <c r="E185" s="9">
         <v>4290</v>
       </c>
-      <c r="F185" s="5">
+      <c r="F185" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
+      <c r="G185" s="1"/>
+    </row>
+    <row r="186" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A186" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="B186" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="C186" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D186" s="3"/>
-      <c r="E186" s="6">
+      <c r="D186" s="6"/>
+      <c r="E186" s="9">
         <v>2860</v>
       </c>
-      <c r="F186" s="5">
+      <c r="F186" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
+      <c r="G186" s="1"/>
+    </row>
+    <row r="187" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A187" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C187" s="2" t="s">
+      <c r="C187" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D187" s="3"/>
-      <c r="E187" s="6">
+      <c r="D187" s="6"/>
+      <c r="E187" s="9">
         <v>1710</v>
       </c>
-      <c r="F187" s="5">
+      <c r="F187" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
+      <c r="G187" s="1"/>
+    </row>
+    <row r="188" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A188" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B188" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C188" s="2" t="s">
+      <c r="C188" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D188" s="3"/>
-      <c r="E188" s="6">
+      <c r="D188" s="6"/>
+      <c r="E188" s="9">
         <v>1710</v>
       </c>
-      <c r="F188" s="5">
+      <c r="F188" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
+      <c r="G188" s="1"/>
+    </row>
+    <row r="189" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A189" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C189" s="2" t="s">
+      <c r="C189" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D189" s="3"/>
-      <c r="E189" s="6">
+      <c r="D189" s="6"/>
+      <c r="E189" s="9">
         <v>1160</v>
       </c>
-      <c r="F189" s="5">
+      <c r="F189" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A190" s="2" t="s">
+      <c r="G189" s="1"/>
+    </row>
+    <row r="190" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A190" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="C190" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D190" s="3"/>
-      <c r="E190" s="6">
+      <c r="D190" s="6"/>
+      <c r="E190" s="9">
         <v>1505</v>
       </c>
-      <c r="F190" s="5">
+      <c r="F190" s="8">
         <v>46227</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C191" s="2" t="s">
+      <c r="G190" s="1"/>
+    </row>
+    <row r="191" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A191" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D191" s="3"/>
-      <c r="E191" s="6">
+      <c r="D191" s="6"/>
+      <c r="E191" s="9">
         <v>4284</v>
       </c>
-      <c r="F191" s="5">
+      <c r="F191" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C192" s="2" t="s">
+      <c r="G191" s="1"/>
+    </row>
+    <row r="192" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A192" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D192" s="3"/>
-      <c r="E192" s="6">
+      <c r="D192" s="6"/>
+      <c r="E192" s="9">
         <v>3808</v>
       </c>
-      <c r="F192" s="5">
+      <c r="F192" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A193" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C193" s="2" t="s">
+      <c r="G192" s="1"/>
+    </row>
+    <row r="193" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A193" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D193" s="3"/>
-      <c r="E193" s="6">
+      <c r="D193" s="6"/>
+      <c r="E193" s="9">
         <v>1428</v>
       </c>
-      <c r="F193" s="5">
+      <c r="F193" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
+      <c r="G193" s="1"/>
+    </row>
+    <row r="194" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A194" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B194" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="C194" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D194" s="3"/>
-      <c r="E194" s="6">
+      <c r="D194" s="6"/>
+      <c r="E194" s="9">
         <v>4290</v>
       </c>
-      <c r="F194" s="5">
+      <c r="F194" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A195" s="2" t="s">
+      <c r="G194" s="1"/>
+    </row>
+    <row r="195" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A195" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B195" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C195" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D195" s="3"/>
-      <c r="E195" s="6">
+      <c r="D195" s="6"/>
+      <c r="E195" s="9">
         <v>2860</v>
       </c>
-      <c r="F195" s="5">
+      <c r="F195" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
+      <c r="G195" s="1"/>
+    </row>
+    <row r="196" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A196" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="B196" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="C196" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D196" s="3"/>
-      <c r="E196" s="6">
+      <c r="D196" s="6"/>
+      <c r="E196" s="9">
         <v>1710</v>
       </c>
-      <c r="F196" s="5">
+      <c r="F196" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
+      <c r="G196" s="1"/>
+    </row>
+    <row r="197" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A197" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="B197" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C197" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D197" s="3"/>
-      <c r="E197" s="6">
+      <c r="D197" s="6"/>
+      <c r="E197" s="9">
         <v>1710</v>
       </c>
-      <c r="F197" s="5">
+      <c r="F197" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A198" s="2" t="s">
+      <c r="G197" s="1"/>
+    </row>
+    <row r="198" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A198" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B198" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C198" s="2" t="s">
+      <c r="C198" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D198" s="3"/>
-      <c r="E198" s="6">
+      <c r="D198" s="6"/>
+      <c r="E198" s="9">
         <v>1160</v>
       </c>
-      <c r="F198" s="5">
+      <c r="F198" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A199" s="2" t="s">
+      <c r="G198" s="1"/>
+    </row>
+    <row r="199" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A199" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B199" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C199" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D199" s="3"/>
-      <c r="E199" s="6">
+      <c r="D199" s="6"/>
+      <c r="E199" s="9">
         <v>1505</v>
       </c>
-      <c r="F199" s="5">
+      <c r="F199" s="8">
         <v>46228</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A200" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C200" s="2" t="s">
+      <c r="G199" s="1"/>
+    </row>
+    <row r="200" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A200" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D200" s="3"/>
-      <c r="E200" s="6">
+      <c r="D200" s="6"/>
+      <c r="E200" s="9">
         <v>4284</v>
       </c>
-      <c r="F200" s="5">
+      <c r="F200" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A201" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C201" s="2" t="s">
+      <c r="G200" s="1"/>
+    </row>
+    <row r="201" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A201" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D201" s="3"/>
-      <c r="E201" s="6">
+      <c r="D201" s="6"/>
+      <c r="E201" s="9">
         <v>3808</v>
       </c>
-      <c r="F201" s="5">
+      <c r="F201" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A202" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C202" s="2" t="s">
+      <c r="G201" s="1"/>
+    </row>
+    <row r="202" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A202" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D202" s="3"/>
-      <c r="E202" s="6">
+      <c r="D202" s="6"/>
+      <c r="E202" s="9">
         <v>1428</v>
       </c>
-      <c r="F202" s="5">
+      <c r="F202" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A203" s="2" t="s">
+      <c r="G202" s="1"/>
+    </row>
+    <row r="203" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A203" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B203" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="C203" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D203" s="3"/>
-      <c r="E203" s="6">
+      <c r="D203" s="6"/>
+      <c r="E203" s="9">
         <v>4290</v>
       </c>
-      <c r="F203" s="5">
+      <c r="F203" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
+      <c r="G203" s="1"/>
+    </row>
+    <row r="204" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A204" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="B204" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="C204" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D204" s="3"/>
-      <c r="E204" s="6">
+      <c r="D204" s="6"/>
+      <c r="E204" s="9">
         <v>2860</v>
       </c>
-      <c r="F204" s="5">
+      <c r="F204" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A205" s="2" t="s">
+      <c r="G204" s="1"/>
+    </row>
+    <row r="205" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A205" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B205" s="2" t="s">
+      <c r="B205" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C205" s="2" t="s">
+      <c r="C205" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D205" s="3"/>
-      <c r="E205" s="6">
+      <c r="D205" s="6"/>
+      <c r="E205" s="9">
         <v>1710</v>
       </c>
-      <c r="F205" s="5">
+      <c r="F205" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A206" s="2" t="s">
+      <c r="G205" s="1"/>
+    </row>
+    <row r="206" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A206" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="B206" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C206" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D206" s="3"/>
-      <c r="E206" s="6">
+      <c r="D206" s="6"/>
+      <c r="E206" s="9">
         <v>1710</v>
       </c>
-      <c r="F206" s="5">
+      <c r="F206" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A207" s="2" t="s">
+      <c r="G206" s="1"/>
+    </row>
+    <row r="207" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A207" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B207" s="2" t="s">
+      <c r="B207" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="C207" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D207" s="3"/>
-      <c r="E207" s="6">
+      <c r="D207" s="6"/>
+      <c r="E207" s="9">
         <v>1160</v>
       </c>
-      <c r="F207" s="5">
+      <c r="F207" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
+      <c r="G207" s="1"/>
+    </row>
+    <row r="208" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A208" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B208" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C208" s="2" t="s">
+      <c r="C208" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D208" s="3"/>
-      <c r="E208" s="6">
+      <c r="D208" s="6"/>
+      <c r="E208" s="9">
         <v>1505</v>
       </c>
-      <c r="F208" s="5">
+      <c r="F208" s="8">
         <v>46230</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A209" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C209" s="2" t="s">
+      <c r="G208" s="1"/>
+    </row>
+    <row r="209" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A209" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C209" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D209" s="3"/>
-      <c r="E209" s="6">
+      <c r="D209" s="6"/>
+      <c r="E209" s="9">
         <v>4284</v>
       </c>
-      <c r="F209" s="5">
+      <c r="F209" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A210" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C210" s="2" t="s">
+      <c r="G209" s="1"/>
+    </row>
+    <row r="210" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A210" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C210" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D210" s="3"/>
-      <c r="E210" s="6">
+      <c r="D210" s="6"/>
+      <c r="E210" s="9">
         <v>3808</v>
       </c>
-      <c r="F210" s="5">
+      <c r="F210" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A211" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C211" s="2" t="s">
+      <c r="G210" s="1"/>
+    </row>
+    <row r="211" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A211" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C211" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D211" s="3"/>
-      <c r="E211" s="6">
+      <c r="D211" s="6"/>
+      <c r="E211" s="9">
         <v>1428</v>
       </c>
-      <c r="F211" s="5">
+      <c r="F211" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A212" s="2" t="s">
+      <c r="G211" s="1"/>
+    </row>
+    <row r="212" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A212" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B212" s="2" t="s">
+      <c r="B212" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="C212" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D212" s="3"/>
-      <c r="E212" s="6">
+      <c r="D212" s="6"/>
+      <c r="E212" s="9">
         <v>4290</v>
       </c>
-      <c r="F212" s="5">
+      <c r="F212" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A213" s="2" t="s">
+      <c r="G212" s="1"/>
+    </row>
+    <row r="213" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A213" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B213" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="C213" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="6">
+      <c r="D213" s="6"/>
+      <c r="E213" s="9">
         <v>2860</v>
       </c>
-      <c r="F213" s="5">
+      <c r="F213" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A214" s="2" t="s">
+      <c r="G213" s="1"/>
+    </row>
+    <row r="214" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A214" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B214" s="2" t="s">
+      <c r="B214" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="C214" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D214" s="3"/>
-      <c r="E214" s="6">
+      <c r="D214" s="6"/>
+      <c r="E214" s="9">
         <v>1710</v>
       </c>
-      <c r="F214" s="5">
+      <c r="F214" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
+      <c r="G214" s="1"/>
+    </row>
+    <row r="215" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A215" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B215" s="2" t="s">
+      <c r="B215" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C215" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D215" s="3"/>
-      <c r="E215" s="6">
+      <c r="D215" s="6"/>
+      <c r="E215" s="9">
         <v>1710</v>
       </c>
-      <c r="F215" s="5">
+      <c r="F215" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
+      <c r="G215" s="1"/>
+    </row>
+    <row r="216" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A216" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="B216" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C216" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D216" s="3"/>
-      <c r="E216" s="6">
+      <c r="D216" s="6"/>
+      <c r="E216" s="9">
         <v>1160</v>
       </c>
-      <c r="F216" s="5">
+      <c r="F216" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A217" s="2" t="s">
+      <c r="G216" s="1"/>
+    </row>
+    <row r="217" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A217" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B217" s="2" t="s">
+      <c r="B217" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C217" s="2" t="s">
+      <c r="C217" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D217" s="3"/>
-      <c r="E217" s="6">
+      <c r="D217" s="6"/>
+      <c r="E217" s="9">
         <v>1505</v>
       </c>
-      <c r="F217" s="5">
+      <c r="F217" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C218" s="2" t="s">
+      <c r="G217" s="1"/>
+    </row>
+    <row r="218" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A218" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C218" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D218" s="3"/>
-      <c r="E218" s="6">
+      <c r="D218" s="6"/>
+      <c r="E218" s="9">
         <v>4284</v>
       </c>
-      <c r="F218" s="5">
+      <c r="F218" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A219" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C219" s="2" t="s">
+      <c r="G218" s="1"/>
+    </row>
+    <row r="219" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A219" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C219" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D219" s="3"/>
-      <c r="E219" s="6">
+      <c r="D219" s="6"/>
+      <c r="E219" s="9">
         <v>3808</v>
       </c>
-      <c r="F219" s="5">
+      <c r="F219" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C220" s="2" t="s">
+      <c r="G219" s="1"/>
+    </row>
+    <row r="220" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A220" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D220" s="3"/>
-      <c r="E220" s="6">
+      <c r="D220" s="6"/>
+      <c r="E220" s="9">
         <v>1428</v>
       </c>
-      <c r="F220" s="5">
+      <c r="F220" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A221" s="2" t="s">
+      <c r="G220" s="1"/>
+    </row>
+    <row r="221" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A221" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C221" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D221" s="3"/>
-      <c r="E221" s="6">
+      <c r="D221" s="6"/>
+      <c r="E221" s="9">
         <v>4290</v>
       </c>
-      <c r="F221" s="5">
+      <c r="F221" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
+      <c r="G221" s="1"/>
+    </row>
+    <row r="222" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A222" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C222" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D222" s="3"/>
-      <c r="E222" s="6">
+      <c r="D222" s="6"/>
+      <c r="E222" s="9">
         <v>2860</v>
       </c>
-      <c r="F222" s="5">
+      <c r="F222" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
+      <c r="G222" s="1"/>
+    </row>
+    <row r="223" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A223" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C223" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D223" s="3"/>
-      <c r="E223" s="6">
+      <c r="D223" s="6"/>
+      <c r="E223" s="9">
         <v>1710</v>
       </c>
-      <c r="F223" s="5">
+      <c r="F223" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
+      <c r="G223" s="1"/>
+    </row>
+    <row r="224" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A224" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="C224" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D224" s="3"/>
-      <c r="E224" s="6">
+      <c r="D224" s="6"/>
+      <c r="E224" s="9">
         <v>1710</v>
       </c>
-      <c r="F224" s="5">
+      <c r="F224" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
+      <c r="G224" s="1"/>
+    </row>
+    <row r="225" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A225" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B225" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="C225" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D225" s="3"/>
-      <c r="E225" s="6">
+      <c r="D225" s="6"/>
+      <c r="E225" s="9">
         <v>1160</v>
       </c>
-      <c r="F225" s="5">
+      <c r="F225" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
+      <c r="G225" s="1"/>
+    </row>
+    <row r="226" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A226" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="C226" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D226" s="3"/>
-      <c r="E226" s="6">
+      <c r="D226" s="6"/>
+      <c r="E226" s="9">
         <v>1505</v>
       </c>
-      <c r="F226" s="5">
+      <c r="F226" s="8">
         <v>46232</v>
       </c>
-    </row>
-    <row r="227" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C227" s="2" t="s">
+      <c r="G226" s="1"/>
+    </row>
+    <row r="227" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A227" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D227" s="3"/>
-      <c r="E227" s="6">
+      <c r="D227" s="6"/>
+      <c r="E227" s="9">
         <v>4284</v>
       </c>
-      <c r="F227" s="5">
+      <c r="F227" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="228" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C228" s="2" t="s">
+      <c r="G227" s="1"/>
+    </row>
+    <row r="228" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A228" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D228" s="3"/>
-      <c r="E228" s="6">
+      <c r="D228" s="6"/>
+      <c r="E228" s="9">
         <v>3808</v>
       </c>
-      <c r="F228" s="5">
+      <c r="F228" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="229" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C229" s="2" t="s">
+      <c r="G228" s="1"/>
+    </row>
+    <row r="229" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A229" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D229" s="3"/>
-      <c r="E229" s="6">
+      <c r="D229" s="6"/>
+      <c r="E229" s="9">
         <v>1428</v>
       </c>
-      <c r="F229" s="5">
+      <c r="F229" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="230" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
+      <c r="G229" s="1"/>
+    </row>
+    <row r="230" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A230" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B230" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C230" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D230" s="3"/>
-      <c r="E230" s="6">
+      <c r="D230" s="6"/>
+      <c r="E230" s="9">
         <v>4290</v>
       </c>
-      <c r="F230" s="5">
+      <c r="F230" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="231" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
+      <c r="G230" s="1"/>
+    </row>
+    <row r="231" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A231" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="B231" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C231" s="2" t="s">
+      <c r="C231" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D231" s="3"/>
-      <c r="E231" s="6">
+      <c r="D231" s="6"/>
+      <c r="E231" s="9">
         <v>2860</v>
       </c>
-      <c r="F231" s="5">
+      <c r="F231" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="232" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A232" s="2" t="s">
+      <c r="G231" s="1"/>
+    </row>
+    <row r="232" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A232" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B232" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C232" s="2" t="s">
+      <c r="C232" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D232" s="3"/>
-      <c r="E232" s="6">
+      <c r="D232" s="6"/>
+      <c r="E232" s="9">
         <v>1710</v>
       </c>
-      <c r="F232" s="5">
+      <c r="F232" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="233" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A233" s="2" t="s">
+      <c r="G232" s="1"/>
+    </row>
+    <row r="233" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A233" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B233" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C233" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D233" s="3"/>
-      <c r="E233" s="6">
+      <c r="D233" s="6"/>
+      <c r="E233" s="9">
         <v>1710</v>
       </c>
-      <c r="F233" s="5">
+      <c r="F233" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="234" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A234" s="2" t="s">
+      <c r="G233" s="1"/>
+    </row>
+    <row r="234" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A234" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B234" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="C234" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D234" s="3"/>
-      <c r="E234" s="6">
+      <c r="D234" s="6"/>
+      <c r="E234" s="9">
         <v>1160</v>
       </c>
-      <c r="F234" s="5">
+      <c r="F234" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="235" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A235" s="2" t="s">
+      <c r="G234" s="1"/>
+    </row>
+    <row r="235" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A235" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B235" s="2" t="s">
+      <c r="B235" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C235" s="2" t="s">
+      <c r="C235" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D235" s="3"/>
-      <c r="E235" s="6">
+      <c r="D235" s="6"/>
+      <c r="E235" s="9">
         <v>1505</v>
       </c>
-      <c r="F235" s="5">
+      <c r="F235" s="8">
         <v>46233</v>
       </c>
-    </row>
-    <row r="236" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A236" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C236" s="2" t="s">
+      <c r="G235" s="1"/>
+    </row>
+    <row r="236" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A236" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C236" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D236" s="3"/>
-      <c r="E236" s="6">
+      <c r="D236" s="6"/>
+      <c r="E236" s="9">
         <v>4284</v>
       </c>
-      <c r="F236" s="5">
+      <c r="F236" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="237" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A237" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C237" s="2" t="s">
+      <c r="G236" s="1"/>
+    </row>
+    <row r="237" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A237" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C237" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D237" s="3"/>
-      <c r="E237" s="6">
+      <c r="D237" s="6"/>
+      <c r="E237" s="9">
         <v>3808</v>
       </c>
-      <c r="F237" s="5">
+      <c r="F237" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="238" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A238" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C238" s="2" t="s">
+      <c r="G237" s="1"/>
+    </row>
+    <row r="238" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A238" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C238" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D238" s="3"/>
-      <c r="E238" s="6">
+      <c r="D238" s="6"/>
+      <c r="E238" s="9">
         <v>1428</v>
       </c>
-      <c r="F238" s="5">
+      <c r="F238" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="239" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A239" s="2" t="s">
+      <c r="G238" s="1"/>
+    </row>
+    <row r="239" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A239" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="B239" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C239" s="2" t="s">
+      <c r="C239" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D239" s="3"/>
-      <c r="E239" s="6">
+      <c r="D239" s="6"/>
+      <c r="E239" s="9">
         <v>4290</v>
       </c>
-      <c r="F239" s="5">
+      <c r="F239" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="240" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
+      <c r="G239" s="1"/>
+    </row>
+    <row r="240" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A240" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B240" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C240" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D240" s="3"/>
-      <c r="E240" s="6">
+      <c r="D240" s="6"/>
+      <c r="E240" s="9">
         <v>2860</v>
       </c>
-      <c r="F240" s="5">
+      <c r="F240" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="241" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A241" s="2" t="s">
+      <c r="G240" s="1"/>
+    </row>
+    <row r="241" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A241" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B241" s="2" t="s">
+      <c r="B241" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="C241" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D241" s="3"/>
-      <c r="E241" s="6">
+      <c r="D241" s="6"/>
+      <c r="E241" s="9">
         <v>1710</v>
       </c>
-      <c r="F241" s="5">
+      <c r="F241" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="242" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A242" s="2" t="s">
+      <c r="G241" s="1"/>
+    </row>
+    <row r="242" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A242" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B242" s="2" t="s">
+      <c r="B242" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C242" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D242" s="3"/>
-      <c r="E242" s="6">
+      <c r="D242" s="6"/>
+      <c r="E242" s="9">
         <v>1710</v>
       </c>
-      <c r="F242" s="5">
+      <c r="F242" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="243" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
+      <c r="G242" s="1"/>
+    </row>
+    <row r="243" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A243" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B243" s="2" t="s">
+      <c r="B243" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="C243" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D243" s="3"/>
-      <c r="E243" s="6">
+      <c r="D243" s="6"/>
+      <c r="E243" s="9">
         <v>1160</v>
       </c>
-      <c r="F243" s="5">
+      <c r="F243" s="8">
         <v>46234</v>
       </c>
-    </row>
-    <row r="244" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
+      <c r="G243" s="1"/>
+    </row>
+    <row r="244" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A244" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B244" s="2" t="s">
+      <c r="B244" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C244" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D244" s="3"/>
-      <c r="E244" s="6">
+      <c r="D244" s="6"/>
+      <c r="E244" s="9">
         <v>1505</v>
       </c>
-      <c r="F244" s="5">
+      <c r="F244" s="8">
         <v>46234</v>
       </c>
+      <c r="G244" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82DFF625-BADB-4A41-927C-13F353F24B7F}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{111D56E7-BAE6-4CDD-B415-3BE9E361BCEF}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,14 +210,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,12 +472,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1"/>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
       <c r="M1" s="3" t="s">
         <v>28</v>
       </c>
@@ -517,10 +517,10 @@
       <c r="K2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>0.25</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="11">
         <v>46212</v>
       </c>
     </row>
@@ -557,10 +557,10 @@
         <v>4284</v>
       </c>
       <c r="L3" s="7"/>
-      <c r="M3" s="11">
+      <c r="M3" s="10">
         <v>0.5</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="11">
         <v>46219</v>
       </c>
     </row>
@@ -597,10 +597,10 @@
         <v>3808</v>
       </c>
       <c r="L4" s="5"/>
-      <c r="M4" s="11">
+      <c r="M4" s="10">
         <v>0.75</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>46226</v>
       </c>
     </row>
@@ -637,10 +637,10 @@
         <v>1428</v>
       </c>
       <c r="L5" s="5"/>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>1</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="11">
         <v>46234</v>
       </c>
     </row>
@@ -4055,7 +4055,9 @@
       <c r="C164" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D164" s="6"/>
+      <c r="D164" s="6">
+        <v>2904.5</v>
+      </c>
       <c r="E164" s="9">
         <v>3213</v>
       </c>
@@ -4074,7 +4076,9 @@
       <c r="C165" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D165" s="6"/>
+      <c r="D165" s="6">
+        <v>2868</v>
+      </c>
       <c r="E165" s="9">
         <v>2856</v>
       </c>
@@ -4093,7 +4097,9 @@
       <c r="C166" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D166" s="6"/>
+      <c r="D166" s="6">
+        <v>709.5</v>
+      </c>
       <c r="E166" s="9">
         <v>1071</v>
       </c>
@@ -4112,7 +4118,9 @@
       <c r="C167" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D167" s="6"/>
+      <c r="D167" s="6">
+        <v>2019.5</v>
+      </c>
       <c r="E167" s="9">
         <v>3217.5</v>
       </c>
@@ -4131,7 +4139,9 @@
       <c r="C168" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D168" s="6"/>
+      <c r="D168" s="6">
+        <v>1707</v>
+      </c>
       <c r="E168" s="9">
         <v>2145</v>
       </c>
@@ -4150,7 +4160,9 @@
       <c r="C169" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D169" s="6"/>
+      <c r="D169" s="6">
+        <v>950.5</v>
+      </c>
       <c r="E169" s="9">
         <v>1282.5</v>
       </c>
@@ -4169,7 +4181,9 @@
       <c r="C170" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D170" s="6"/>
+      <c r="D170" s="6">
+        <v>1321.5</v>
+      </c>
       <c r="E170" s="9">
         <v>1282.5</v>
       </c>
@@ -4188,7 +4202,9 @@
       <c r="C171" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D171" s="6"/>
+      <c r="D171" s="6">
+        <v>772.5</v>
+      </c>
       <c r="E171" s="9">
         <v>870</v>
       </c>
@@ -4207,7 +4223,9 @@
       <c r="C172" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D172" s="6"/>
+      <c r="D172" s="6">
+        <v>1242.5</v>
+      </c>
       <c r="E172" s="9">
         <v>1128.75</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{111D56E7-BAE6-4CDD-B415-3BE9E361BCEF}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D886E26-21AC-4772-BCC0-CA1EF5593713}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4244,7 +4244,9 @@
       <c r="C173" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D173" s="6"/>
+      <c r="D173" s="6">
+        <v>3050.5</v>
+      </c>
       <c r="E173" s="9">
         <v>3213</v>
       </c>
@@ -4263,7 +4265,9 @@
       <c r="C174" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D174" s="6"/>
+      <c r="D174" s="6">
+        <v>3092</v>
+      </c>
       <c r="E174" s="9">
         <v>2856</v>
       </c>
@@ -4282,7 +4286,9 @@
       <c r="C175" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D175" s="6"/>
+      <c r="D175" s="6">
+        <v>718.5</v>
+      </c>
       <c r="E175" s="9">
         <v>1071</v>
       </c>
@@ -4301,7 +4307,9 @@
       <c r="C176" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D176" s="6"/>
+      <c r="D176" s="6">
+        <v>2100.5</v>
+      </c>
       <c r="E176" s="9">
         <v>3217.5</v>
       </c>
@@ -4320,7 +4328,9 @@
       <c r="C177" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D177" s="6"/>
+      <c r="D177" s="6">
+        <v>1786</v>
+      </c>
       <c r="E177" s="9">
         <v>2145</v>
       </c>
@@ -4339,7 +4349,9 @@
       <c r="C178" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D178" s="6"/>
+      <c r="D178" s="6">
+        <v>981</v>
+      </c>
       <c r="E178" s="9">
         <v>1282.5</v>
       </c>
@@ -4358,7 +4370,9 @@
       <c r="C179" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D179" s="6"/>
+      <c r="D179" s="6">
+        <v>1326.5</v>
+      </c>
       <c r="E179" s="9">
         <v>1282.5</v>
       </c>
@@ -4377,7 +4391,9 @@
       <c r="C180" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D180" s="6"/>
+      <c r="D180" s="6">
+        <v>776.5</v>
+      </c>
       <c r="E180" s="9">
         <v>870</v>
       </c>
@@ -4396,7 +4412,9 @@
       <c r="C181" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D181" s="6"/>
+      <c r="D181" s="6">
+        <v>1272</v>
+      </c>
       <c r="E181" s="9">
         <v>1128.75</v>
       </c>
@@ -4415,7 +4433,9 @@
       <c r="C182" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D182" s="6"/>
+      <c r="D182" s="6">
+        <v>3190.5</v>
+      </c>
       <c r="E182" s="9">
         <v>4284</v>
       </c>
@@ -4434,7 +4454,9 @@
       <c r="C183" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D183" s="6"/>
+      <c r="D183" s="6">
+        <v>3171</v>
+      </c>
       <c r="E183" s="9">
         <v>3808</v>
       </c>
@@ -4453,7 +4475,9 @@
       <c r="C184" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D184" s="6"/>
+      <c r="D184" s="6">
+        <v>753</v>
+      </c>
       <c r="E184" s="9">
         <v>1428</v>
       </c>
@@ -4472,7 +4496,9 @@
       <c r="C185" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D185" s="6"/>
+      <c r="D185" s="6">
+        <v>2208.5</v>
+      </c>
       <c r="E185" s="9">
         <v>4290</v>
       </c>
@@ -4491,7 +4517,9 @@
       <c r="C186" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D186" s="6"/>
+      <c r="D186" s="6">
+        <v>1846</v>
+      </c>
       <c r="E186" s="9">
         <v>2860</v>
       </c>
@@ -4510,7 +4538,9 @@
       <c r="C187" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D187" s="6"/>
+      <c r="D187" s="6">
+        <v>1088</v>
+      </c>
       <c r="E187" s="9">
         <v>1710</v>
       </c>
@@ -4529,7 +4559,9 @@
       <c r="C188" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D188" s="6"/>
+      <c r="D188" s="6">
+        <v>1326.5</v>
+      </c>
       <c r="E188" s="9">
         <v>1710</v>
       </c>
@@ -4548,7 +4580,9 @@
       <c r="C189" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D189" s="6"/>
+      <c r="D189" s="6">
+        <v>810</v>
+      </c>
       <c r="E189" s="9">
         <v>1160</v>
       </c>
@@ -4567,7 +4601,9 @@
       <c r="C190" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D190" s="6"/>
+      <c r="D190" s="6">
+        <v>1305</v>
+      </c>
       <c r="E190" s="9">
         <v>1505</v>
       </c>
@@ -4586,7 +4622,9 @@
       <c r="C191" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D191" s="6"/>
+      <c r="D191" s="6">
+        <v>3197</v>
+      </c>
       <c r="E191" s="9">
         <v>4284</v>
       </c>
@@ -4605,7 +4643,9 @@
       <c r="C192" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D192" s="6"/>
+      <c r="D192" s="6">
+        <v>3181</v>
+      </c>
       <c r="E192" s="9">
         <v>3808</v>
       </c>
@@ -4624,7 +4664,9 @@
       <c r="C193" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D193" s="6"/>
+      <c r="D193" s="6">
+        <v>804</v>
+      </c>
       <c r="E193" s="9">
         <v>1428</v>
       </c>
@@ -4643,7 +4685,9 @@
       <c r="C194" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D194" s="6"/>
+      <c r="D194" s="6">
+        <v>2250</v>
+      </c>
       <c r="E194" s="9">
         <v>4290</v>
       </c>
@@ -4662,7 +4706,9 @@
       <c r="C195" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D195" s="6"/>
+      <c r="D195" s="6">
+        <v>1892</v>
+      </c>
       <c r="E195" s="9">
         <v>2860</v>
       </c>
@@ -4681,7 +4727,9 @@
       <c r="C196" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D196" s="6"/>
+      <c r="D196" s="6">
+        <v>1088</v>
+      </c>
       <c r="E196" s="9">
         <v>1710</v>
       </c>
@@ -4700,7 +4748,9 @@
       <c r="C197" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D197" s="6"/>
+      <c r="D197" s="6">
+        <v>1326.5</v>
+      </c>
       <c r="E197" s="9">
         <v>1710</v>
       </c>
@@ -4719,7 +4769,9 @@
       <c r="C198" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D198" s="6"/>
+      <c r="D198" s="6">
+        <v>810</v>
+      </c>
       <c r="E198" s="9">
         <v>1160</v>
       </c>
@@ -4738,7 +4790,9 @@
       <c r="C199" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D199" s="6"/>
+      <c r="D199" s="6">
+        <v>1305</v>
+      </c>
       <c r="E199" s="9">
         <v>1505</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D886E26-21AC-4772-BCC0-CA1EF5593713}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB44BA14-AA80-4E84-8248-8F1E5FA95B64}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4811,7 +4811,9 @@
       <c r="C200" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D200" s="6"/>
+      <c r="D200" s="6">
+        <v>3247</v>
+      </c>
       <c r="E200" s="9">
         <v>4284</v>
       </c>
@@ -4830,7 +4832,9 @@
       <c r="C201" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D201" s="6"/>
+      <c r="D201" s="6">
+        <v>3350</v>
+      </c>
       <c r="E201" s="9">
         <v>3808</v>
       </c>
@@ -4849,7 +4853,9 @@
       <c r="C202" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D202" s="6"/>
+      <c r="D202" s="6">
+        <v>1004.5</v>
+      </c>
       <c r="E202" s="9">
         <v>1428</v>
       </c>
@@ -4868,7 +4874,9 @@
       <c r="C203" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D203" s="6"/>
+      <c r="D203" s="6">
+        <v>2456.5</v>
+      </c>
       <c r="E203" s="9">
         <v>4290</v>
       </c>
@@ -4887,7 +4895,9 @@
       <c r="C204" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D204" s="6"/>
+      <c r="D204" s="6">
+        <v>2078</v>
+      </c>
       <c r="E204" s="9">
         <v>2860</v>
       </c>
@@ -4906,7 +4916,9 @@
       <c r="C205" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D205" s="6"/>
+      <c r="D205" s="6">
+        <v>1181.5</v>
+      </c>
       <c r="E205" s="9">
         <v>1710</v>
       </c>
@@ -4925,7 +4937,9 @@
       <c r="C206" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D206" s="6"/>
+      <c r="D206" s="6">
+        <v>1340</v>
+      </c>
       <c r="E206" s="9">
         <v>1710</v>
       </c>
@@ -4944,7 +4958,9 @@
       <c r="C207" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D207" s="6"/>
+      <c r="D207" s="6">
+        <v>817</v>
+      </c>
       <c r="E207" s="9">
         <v>1160</v>
       </c>
@@ -4963,7 +4979,9 @@
       <c r="C208" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D208" s="6"/>
+      <c r="D208" s="6">
+        <v>1345</v>
+      </c>
       <c r="E208" s="9">
         <v>1505</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metro cúbicos  Vendedores/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metas e Produzido/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB44BA14-AA80-4E84-8248-8F1E5FA95B64}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B59EEF-1525-4D00-B967-DFD28E8ACEC9}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5000,7 +5000,9 @@
       <c r="C209" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D209" s="6"/>
+      <c r="D209" s="6">
+        <v>3638</v>
+      </c>
       <c r="E209" s="9">
         <v>4284</v>
       </c>
@@ -5019,7 +5021,9 @@
       <c r="C210" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D210" s="6"/>
+      <c r="D210" s="6">
+        <v>3432.5</v>
+      </c>
       <c r="E210" s="9">
         <v>3808</v>
       </c>
@@ -5038,7 +5042,9 @@
       <c r="C211" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D211" s="6"/>
+      <c r="D211" s="6">
+        <v>1097.5</v>
+      </c>
       <c r="E211" s="9">
         <v>1428</v>
       </c>
@@ -5057,7 +5063,9 @@
       <c r="C212" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D212" s="6"/>
+      <c r="D212" s="6">
+        <v>2633.5</v>
+      </c>
       <c r="E212" s="9">
         <v>4290</v>
       </c>
@@ -5076,7 +5084,9 @@
       <c r="C213" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D213" s="6"/>
+      <c r="D213" s="6">
+        <v>2120.5</v>
+      </c>
       <c r="E213" s="9">
         <v>2860</v>
       </c>
@@ -5095,7 +5105,9 @@
       <c r="C214" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D214" s="6"/>
+      <c r="D214" s="6">
+        <v>1274.5</v>
+      </c>
       <c r="E214" s="9">
         <v>1710</v>
       </c>
@@ -5114,7 +5126,9 @@
       <c r="C215" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D215" s="6"/>
+      <c r="D215" s="6">
+        <v>1391</v>
+      </c>
       <c r="E215" s="9">
         <v>1710</v>
       </c>
@@ -5133,7 +5147,9 @@
       <c r="C216" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D216" s="6"/>
+      <c r="D216" s="6">
+        <v>862</v>
+      </c>
       <c r="E216" s="9">
         <v>1160</v>
       </c>
@@ -5152,7 +5168,9 @@
       <c r="C217" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D217" s="6"/>
+      <c r="D217" s="6">
+        <v>1492</v>
+      </c>
       <c r="E217" s="9">
         <v>1505</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metas e Produzido/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B59EEF-1525-4D00-B967-DFD28E8ACEC9}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C315292-B193-419F-94A6-0862DF07FCC5}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5189,7 +5189,9 @@
       <c r="C218" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D218" s="6"/>
+      <c r="D218" s="6">
+        <v>3721.5</v>
+      </c>
       <c r="E218" s="9">
         <v>4284</v>
       </c>
@@ -5208,7 +5210,9 @@
       <c r="C219" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D219" s="6"/>
+      <c r="D219" s="6">
+        <v>3667.5</v>
+      </c>
       <c r="E219" s="9">
         <v>3808</v>
       </c>
@@ -5227,7 +5231,9 @@
       <c r="C220" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D220" s="6"/>
+      <c r="D220" s="6">
+        <v>1204.5</v>
+      </c>
       <c r="E220" s="9">
         <v>1428</v>
       </c>
@@ -5246,7 +5252,9 @@
       <c r="C221" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D221" s="6"/>
+      <c r="D221" s="6">
+        <v>2748</v>
+      </c>
       <c r="E221" s="9">
         <v>4290</v>
       </c>
@@ -5265,7 +5273,9 @@
       <c r="C222" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D222" s="6"/>
+      <c r="D222" s="6">
+        <v>2259.5</v>
+      </c>
       <c r="E222" s="9">
         <v>2860</v>
       </c>
@@ -5284,7 +5294,9 @@
       <c r="C223" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D223" s="6"/>
+      <c r="D223" s="6">
+        <v>1320.5</v>
+      </c>
       <c r="E223" s="9">
         <v>1710</v>
       </c>
@@ -5303,7 +5315,9 @@
       <c r="C224" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D224" s="6"/>
+      <c r="D224" s="6">
+        <v>1455</v>
+      </c>
       <c r="E224" s="9">
         <v>1710</v>
       </c>
@@ -5322,7 +5336,9 @@
       <c r="C225" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D225" s="6"/>
+      <c r="D225" s="6">
+        <v>924</v>
+      </c>
       <c r="E225" s="9">
         <v>1160</v>
       </c>
@@ -5341,7 +5357,9 @@
       <c r="C226" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D226" s="6"/>
+      <c r="D226" s="6">
+        <v>1513.5</v>
+      </c>
       <c r="E226" s="9">
         <v>1505</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metas e Produzido/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C315292-B193-419F-94A6-0862DF07FCC5}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A74A4F-F067-459B-9A22-FDCC34011FC7}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5378,7 +5378,9 @@
       <c r="C227" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D227" s="6"/>
+      <c r="D227" s="6">
+        <v>3823</v>
+      </c>
       <c r="E227" s="9">
         <v>4284</v>
       </c>
@@ -5397,7 +5399,9 @@
       <c r="C228" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D228" s="6"/>
+      <c r="D228" s="6">
+        <v>4063</v>
+      </c>
       <c r="E228" s="9">
         <v>3808</v>
       </c>
@@ -5416,7 +5420,9 @@
       <c r="C229" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D229" s="6"/>
+      <c r="D229" s="6">
+        <v>1266.5</v>
+      </c>
       <c r="E229" s="9">
         <v>1428</v>
       </c>
@@ -5435,7 +5441,9 @@
       <c r="C230" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D230" s="6"/>
+      <c r="D230" s="6">
+        <v>2971.5</v>
+      </c>
       <c r="E230" s="9">
         <v>4290</v>
       </c>
@@ -5454,7 +5462,9 @@
       <c r="C231" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D231" s="6"/>
+      <c r="D231" s="6">
+        <v>2349.5</v>
+      </c>
       <c r="E231" s="9">
         <v>2860</v>
       </c>
@@ -5473,7 +5483,9 @@
       <c r="C232" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D232" s="6"/>
+      <c r="D232" s="6">
+        <v>1456.5</v>
+      </c>
       <c r="E232" s="9">
         <v>1710</v>
       </c>
@@ -5492,7 +5504,9 @@
       <c r="C233" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D233" s="6"/>
+      <c r="D233" s="6">
+        <v>1495.5</v>
+      </c>
       <c r="E233" s="9">
         <v>1710</v>
       </c>
@@ -5511,7 +5525,9 @@
       <c r="C234" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D234" s="6"/>
+      <c r="D234" s="6">
+        <v>940</v>
+      </c>
       <c r="E234" s="9">
         <v>1160</v>
       </c>
@@ -5530,7 +5546,9 @@
       <c r="C235" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D235" s="6"/>
+      <c r="D235" s="6">
+        <v>1565</v>
+      </c>
       <c r="E235" s="9">
         <v>1505</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metas e Produzido/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A74A4F-F067-459B-9A22-FDCC34011FC7}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{379C0BA6-B543-457C-91FF-602B84FB31B7}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5379,7 +5379,7 @@
         <v>8</v>
       </c>
       <c r="D227" s="6">
-        <v>3823</v>
+        <v>3837</v>
       </c>
       <c r="E227" s="9">
         <v>4284</v>
@@ -5400,7 +5400,7 @@
         <v>9</v>
       </c>
       <c r="D228" s="6">
-        <v>4063</v>
+        <v>4080.5</v>
       </c>
       <c r="E228" s="9">
         <v>3808</v>
@@ -5421,7 +5421,7 @@
         <v>10</v>
       </c>
       <c r="D229" s="6">
-        <v>1266.5</v>
+        <v>1271</v>
       </c>
       <c r="E229" s="9">
         <v>1428</v>
@@ -5442,7 +5442,7 @@
         <v>13</v>
       </c>
       <c r="D230" s="6">
-        <v>2971.5</v>
+        <v>2997.5</v>
       </c>
       <c r="E230" s="9">
         <v>4290</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="D231" s="6">
-        <v>2349.5</v>
+        <v>2364.5</v>
       </c>
       <c r="E231" s="9">
         <v>2860</v>
@@ -5484,7 +5484,7 @@
         <v>17</v>
       </c>
       <c r="D232" s="6">
-        <v>1456.5</v>
+        <v>1455.5</v>
       </c>
       <c r="E232" s="9">
         <v>1710</v>
@@ -5526,7 +5526,7 @@
         <v>23</v>
       </c>
       <c r="D234" s="6">
-        <v>940</v>
+        <v>941.5</v>
       </c>
       <c r="E234" s="9">
         <v>1160</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metas e Produzido/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{379C0BA6-B543-457C-91FF-602B84FB31B7}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DD3479-ACC0-4E0F-BF0F-4FE00E214D42}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Página1" sheetId="1" r:id="rId1"/>
@@ -5567,7 +5567,9 @@
       <c r="C236" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D236" s="6"/>
+      <c r="D236" s="6">
+        <v>4117</v>
+      </c>
       <c r="E236" s="9">
         <v>4284</v>
       </c>
@@ -5586,7 +5588,9 @@
       <c r="C237" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D237" s="6"/>
+      <c r="D237" s="6">
+        <v>4178</v>
+      </c>
       <c r="E237" s="9">
         <v>3808</v>
       </c>
@@ -5605,7 +5609,9 @@
       <c r="C238" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D238" s="6"/>
+      <c r="D238" s="6">
+        <v>1336.5</v>
+      </c>
       <c r="E238" s="9">
         <v>1428</v>
       </c>
@@ -5624,7 +5630,9 @@
       <c r="C239" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D239" s="6"/>
+      <c r="D239" s="6">
+        <v>3131.5</v>
+      </c>
       <c r="E239" s="9">
         <v>4290</v>
       </c>
@@ -5643,7 +5651,9 @@
       <c r="C240" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D240" s="6"/>
+      <c r="D240" s="6">
+        <v>2671</v>
+      </c>
       <c r="E240" s="9">
         <v>2860</v>
       </c>
@@ -5662,7 +5672,9 @@
       <c r="C241" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D241" s="6"/>
+      <c r="D241" s="6">
+        <v>1554.5</v>
+      </c>
       <c r="E241" s="9">
         <v>1710</v>
       </c>
@@ -5681,7 +5693,9 @@
       <c r="C242" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D242" s="6"/>
+      <c r="D242" s="6">
+        <v>1564</v>
+      </c>
       <c r="E242" s="9">
         <v>1710</v>
       </c>
@@ -5700,7 +5714,9 @@
       <c r="C243" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D243" s="6"/>
+      <c r="D243" s="6">
+        <v>955</v>
+      </c>
       <c r="E243" s="9">
         <v>1160</v>
       </c>
@@ -5719,7 +5735,9 @@
       <c r="C244" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D244" s="6"/>
+      <c r="D244" s="6">
+        <v>1665</v>
+      </c>
       <c r="E244" s="9">
         <v>1505</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,19 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Metas e Produzido/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DD3479-ACC0-4E0F-BF0F-4FE00E214D42}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="11_2B0445071E4C7C47C5C3C758634824BA6359D217" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D3E026A-F571-4889-8D34-057C27475DA5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Página1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Página1!$A$1:$F$271</definedName>
+  </definedNames>
+  <calcPr calcId="191029" iterate="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="41">
   <si>
     <t>Cidade</t>
   </si>
@@ -103,20 +119,56 @@
     <t>Junior</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta 100% </t>
-  </si>
-  <si>
     <t xml:space="preserve">Checkpoint </t>
   </si>
   <si>
     <t xml:space="preserve">Data limite </t>
+  </si>
+  <si>
+    <t>Meta 100% Julho</t>
+  </si>
+  <si>
+    <t>Meta 100% Agosto</t>
+  </si>
+  <si>
+    <t>Meta 100% Setembro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta 100% Outubro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta 100% Novembro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta 100% Dezembro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julho </t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novembro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dezembro </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -128,22 +180,39 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -181,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -207,14 +276,20 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -437,19 +512,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N244"/>
+  <dimension ref="A1:N487"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="4"/>
     <col min="2" max="2" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="12.5703125" style="4"/>
+    <col min="3" max="5" width="12.5703125" style="4"/>
+    <col min="6" max="6" width="12.5703125" style="8"/>
     <col min="7" max="7" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="12.5703125" style="4"/>
+    <col min="11" max="11" width="10.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="12.5703125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -472,18 +550,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="1"/>
-      <c r="H1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="M1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>29</v>
       </c>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="M1" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -517,11 +593,11 @@
       <c r="K2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="N2" s="11">
-        <v>46212</v>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -537,7 +613,7 @@
       <c r="D3" s="6">
         <v>426.5</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="7">
         <v>952</v>
       </c>
       <c r="F3" s="8">
@@ -553,15 +629,15 @@
       <c r="J3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="9">
-        <v>4284</v>
+      <c r="K3" s="11">
+        <v>4117</v>
       </c>
       <c r="L3" s="7"/>
-      <c r="M3" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="N3" s="11">
-        <v>46219</v>
+      <c r="M3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N3" s="10">
+        <v>46212</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -577,7 +653,7 @@
       <c r="D4" s="6">
         <v>68.5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="7">
         <v>357</v>
       </c>
       <c r="F4" s="8">
@@ -593,15 +669,15 @@
       <c r="J4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="9">
-        <v>3808</v>
+      <c r="K4" s="11">
+        <v>4178</v>
       </c>
       <c r="L4" s="5"/>
-      <c r="M4" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="N4" s="11">
-        <v>46226</v>
+      <c r="M4" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="N4" s="10">
+        <v>46219</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -633,15 +709,15 @@
       <c r="J5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="9">
-        <v>1428</v>
+      <c r="K5" s="11">
+        <v>1336.5</v>
       </c>
       <c r="L5" s="5"/>
-      <c r="M5" s="10">
-        <v>1</v>
-      </c>
-      <c r="N5" s="11">
-        <v>46234</v>
+      <c r="M5" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="N5" s="10">
+        <v>46226</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -657,7 +733,7 @@
       <c r="D6" s="6">
         <v>195.5</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="7">
         <v>715</v>
       </c>
       <c r="F6" s="8">
@@ -673,10 +749,16 @@
       <c r="J6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="9">
-        <v>4290</v>
+      <c r="K6" s="11">
+        <v>3131.5</v>
       </c>
       <c r="L6" s="7"/>
+      <c r="M6" s="9">
+        <v>1</v>
+      </c>
+      <c r="N6" s="10">
+        <v>46234</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -691,7 +773,7 @@
       <c r="D7" s="6">
         <v>46.5</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="7">
         <v>427.5</v>
       </c>
       <c r="F7" s="8">
@@ -707,8 +789,8 @@
       <c r="J7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="9">
-        <v>2860</v>
+      <c r="K7" s="11">
+        <v>2671</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -725,7 +807,7 @@
       <c r="D8" s="6">
         <v>116</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="7">
         <v>427.5</v>
       </c>
       <c r="F8" s="8">
@@ -741,8 +823,8 @@
       <c r="J8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="9">
-        <v>1710</v>
+      <c r="K8" s="11">
+        <v>1554.5</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -759,7 +841,7 @@
       <c r="D9" s="6">
         <v>43.5</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="7">
         <v>290</v>
       </c>
       <c r="F9" s="8">
@@ -775,8 +857,8 @@
       <c r="J9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="9">
-        <v>1710</v>
+      <c r="K9" s="11">
+        <v>1564</v>
       </c>
       <c r="L9" s="5"/>
     </row>
@@ -793,7 +875,7 @@
       <c r="D10" s="6">
         <v>92</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="7">
         <v>376.5</v>
       </c>
       <c r="F10" s="8">
@@ -809,8 +891,8 @@
       <c r="J10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="9">
-        <v>1160</v>
+      <c r="K10" s="11">
+        <v>955</v>
       </c>
       <c r="L10" s="5"/>
     </row>
@@ -843,8 +925,8 @@
       <c r="J11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="9">
-        <v>1505</v>
+      <c r="K11" s="11">
+        <v>1665</v>
       </c>
       <c r="L11" s="5"/>
     </row>
@@ -861,7 +943,7 @@
       <c r="D12" s="6">
         <v>507.5</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="7">
         <v>952</v>
       </c>
       <c r="F12" s="8">
@@ -887,13 +969,23 @@
       <c r="D13" s="6">
         <v>129.5</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="7">
         <v>357</v>
       </c>
       <c r="F13" s="8">
         <v>46205</v>
       </c>
       <c r="G13" s="1"/>
+      <c r="H13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="M13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
@@ -915,6 +1007,24 @@
         <v>46205</v>
       </c>
       <c r="G14" s="1"/>
+      <c r="H14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
@@ -929,13 +1039,31 @@
       <c r="D15" s="6">
         <v>297.5</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="7">
         <v>715</v>
       </c>
       <c r="F15" s="8">
         <v>46205</v>
       </c>
       <c r="G15" s="1"/>
+      <c r="H15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="11">
+        <v>4477.5</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N15" s="10">
+        <v>46213</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
@@ -950,15 +1078,33 @@
       <c r="D16" s="6">
         <v>142</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="7">
         <v>427.5</v>
       </c>
       <c r="F16" s="8">
         <v>46205</v>
       </c>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="11">
+        <v>3980</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="N16" s="10">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -971,15 +1117,33 @@
       <c r="D17" s="6">
         <v>213</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="7">
         <v>427.5</v>
       </c>
       <c r="F17" s="8">
         <v>46205</v>
       </c>
       <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="11">
+        <v>1492.5</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="N17" s="10">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
@@ -992,15 +1156,33 @@
       <c r="D18" s="6">
         <v>58</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="7">
         <v>290</v>
       </c>
       <c r="F18" s="8">
         <v>46205</v>
       </c>
       <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="11">
+        <v>4170</v>
+      </c>
+      <c r="M18" s="9">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
@@ -1013,15 +1195,27 @@
       <c r="D19" s="6">
         <v>186.5</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="7">
         <v>376.5</v>
       </c>
       <c r="F19" s="8">
         <v>46205</v>
       </c>
       <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="11">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -1041,8 +1235,20 @@
         <v>46206</v>
       </c>
       <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="11">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>6</v>
       </c>
@@ -1055,15 +1261,27 @@
       <c r="D21" s="6">
         <v>680</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="7">
         <v>952</v>
       </c>
       <c r="F21" s="8">
         <v>46206</v>
       </c>
       <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="11">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>6</v>
       </c>
@@ -1076,15 +1294,27 @@
       <c r="D22" s="6">
         <v>172.5</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="7">
         <v>357</v>
       </c>
       <c r="F22" s="8">
         <v>46206</v>
       </c>
       <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="11">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1334,20 @@
         <v>46206</v>
       </c>
       <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="11">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>11</v>
       </c>
@@ -1118,7 +1360,7 @@
       <c r="D24" s="6">
         <v>304.5</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="7">
         <v>715</v>
       </c>
       <c r="F24" s="8">
@@ -1126,7 +1368,7 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>15</v>
       </c>
@@ -1139,15 +1381,25 @@
       <c r="D25" s="6">
         <v>142</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="7">
         <v>427.5</v>
       </c>
       <c r="F25" s="8">
         <v>46206</v>
       </c>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H25" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="M25" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" s="14"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>18</v>
       </c>
@@ -1160,15 +1412,33 @@
       <c r="D26" s="6">
         <v>246</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="7">
         <v>427.5</v>
       </c>
       <c r="F26" s="8">
         <v>46206</v>
       </c>
       <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>21</v>
       </c>
@@ -1181,15 +1451,29 @@
       <c r="D27" s="6">
         <v>56</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="7">
         <v>290</v>
       </c>
       <c r="F27" s="8">
         <v>46206</v>
       </c>
       <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="11"/>
+      <c r="M27" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
@@ -1202,15 +1486,29 @@
       <c r="D28" s="6">
         <v>214.5</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="7">
         <v>376.5</v>
       </c>
       <c r="F28" s="8">
         <v>46206</v>
       </c>
       <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="11"/>
+      <c r="M28" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="N28" s="10"/>
+    </row>
+    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>6</v>
       </c>
@@ -1230,8 +1528,22 @@
         <v>46207</v>
       </c>
       <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="M29" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="N29" s="10"/>
+    </row>
+    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>6</v>
       </c>
@@ -1244,15 +1556,29 @@
       <c r="D30" s="6">
         <v>719</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="7">
         <v>952</v>
       </c>
       <c r="F30" s="8">
         <v>46207</v>
       </c>
       <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="M30" s="9">
+        <v>1</v>
+      </c>
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>6</v>
       </c>
@@ -1265,15 +1591,25 @@
       <c r="D31" s="6">
         <v>177</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="7">
         <v>357</v>
       </c>
       <c r="F31" s="8">
         <v>46207</v>
       </c>
       <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>11</v>
       </c>
@@ -1293,8 +1629,18 @@
         <v>46207</v>
       </c>
       <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>11</v>
       </c>
@@ -1307,15 +1653,25 @@
       <c r="D33" s="6">
         <v>304.5</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="7">
         <v>715</v>
       </c>
       <c r="F33" s="8">
         <v>46207</v>
       </c>
       <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>15</v>
       </c>
@@ -1328,15 +1684,25 @@
       <c r="D34" s="6">
         <v>150</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="7">
         <v>427.5</v>
       </c>
       <c r="F34" s="8">
         <v>46207</v>
       </c>
       <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="11"/>
+    </row>
+    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>18</v>
       </c>
@@ -1349,15 +1715,25 @@
       <c r="D35" s="6">
         <v>254</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="7">
         <v>427.5</v>
       </c>
       <c r="F35" s="8">
         <v>46207</v>
       </c>
       <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="11"/>
+    </row>
+    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>21</v>
       </c>
@@ -1370,7 +1746,7 @@
       <c r="D36" s="6">
         <v>68</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="7">
         <v>290</v>
       </c>
       <c r="F36" s="8">
@@ -1378,7 +1754,7 @@
       </c>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>24</v>
       </c>
@@ -1391,15 +1767,25 @@
       <c r="D37" s="6">
         <v>231.5</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="7">
         <v>376.5</v>
       </c>
       <c r="F37" s="8">
         <v>46207</v>
       </c>
       <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H37" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="M37" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="N37" s="14"/>
+    </row>
+    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>6</v>
       </c>
@@ -1419,8 +1805,26 @@
         <v>46209</v>
       </c>
       <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H38" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>6</v>
       </c>
@@ -1433,15 +1837,29 @@
       <c r="D39" s="6">
         <v>969</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="7">
         <v>952</v>
       </c>
       <c r="F39" s="8">
         <v>46209</v>
       </c>
       <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K39" s="11"/>
+      <c r="M39" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N39" s="10"/>
+    </row>
+    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>6</v>
       </c>
@@ -1454,15 +1872,29 @@
       <c r="D40" s="6">
         <v>187</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="7">
         <v>357</v>
       </c>
       <c r="F40" s="8">
         <v>46209</v>
       </c>
       <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="11"/>
+      <c r="M40" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="N40" s="10"/>
+    </row>
+    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>11</v>
       </c>
@@ -1482,8 +1914,22 @@
         <v>46209</v>
       </c>
       <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K41" s="11"/>
+      <c r="M41" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="N41" s="10"/>
+    </row>
+    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>11</v>
       </c>
@@ -1496,15 +1942,29 @@
       <c r="D42" s="6">
         <v>369.5</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="7">
         <v>715</v>
       </c>
       <c r="F42" s="8">
         <v>46209</v>
       </c>
       <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="M42" s="9">
+        <v>1</v>
+      </c>
+      <c r="N42" s="10"/>
+    </row>
+    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>15</v>
       </c>
@@ -1517,15 +1977,25 @@
       <c r="D43" s="6">
         <v>152.5</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="7">
         <v>427.5</v>
       </c>
       <c r="F43" s="8">
         <v>46209</v>
       </c>
       <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="11"/>
+    </row>
+    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>18</v>
       </c>
@@ -1538,15 +2008,25 @@
       <c r="D44" s="6">
         <v>348</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="7">
         <v>427.5</v>
       </c>
       <c r="F44" s="8">
         <v>46209</v>
       </c>
       <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="11"/>
+    </row>
+    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>21</v>
       </c>
@@ -1559,15 +2039,25 @@
       <c r="D45" s="6">
         <v>84</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="7">
         <v>290</v>
       </c>
       <c r="F45" s="8">
         <v>46209</v>
       </c>
       <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="11"/>
+    </row>
+    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>24</v>
       </c>
@@ -1580,15 +2070,25 @@
       <c r="D46" s="6">
         <v>315</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="7">
         <v>376.5</v>
       </c>
       <c r="F46" s="8">
         <v>46209</v>
       </c>
       <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="11"/>
+    </row>
+    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>6</v>
       </c>
@@ -1608,8 +2108,18 @@
         <v>46210</v>
       </c>
       <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K47" s="11"/>
+    </row>
+    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>6</v>
       </c>
@@ -1622,7 +2132,7 @@
       <c r="D48" s="6">
         <v>1009</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="7">
         <v>952</v>
       </c>
       <c r="F48" s="8">
@@ -1630,7 +2140,7 @@
       </c>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>6</v>
       </c>
@@ -1643,15 +2153,25 @@
       <c r="D49" s="6">
         <v>235</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="7">
         <v>357</v>
       </c>
       <c r="F49" s="8">
         <v>46210</v>
       </c>
       <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H49" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="M49" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N49" s="14"/>
+    </row>
+    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>11</v>
       </c>
@@ -1671,8 +2191,26 @@
         <v>46210</v>
       </c>
       <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>11</v>
       </c>
@@ -1685,15 +2223,29 @@
       <c r="D51" s="6">
         <v>444</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="7">
         <v>715</v>
       </c>
       <c r="F51" s="8">
         <v>46210</v>
       </c>
       <c r="G51" s="1"/>
-    </row>
-    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K51" s="11"/>
+      <c r="M51" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N51" s="10"/>
+    </row>
+    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>15</v>
       </c>
@@ -1706,15 +2258,29 @@
       <c r="D52" s="6">
         <v>203</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="7">
         <v>427.5</v>
       </c>
       <c r="F52" s="8">
         <v>46210</v>
       </c>
       <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K52" s="11"/>
+      <c r="M52" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="N52" s="10"/>
+    </row>
+    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>18</v>
       </c>
@@ -1727,15 +2293,29 @@
       <c r="D53" s="6">
         <v>452</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="7">
         <v>427.5</v>
       </c>
       <c r="F53" s="8">
         <v>46210</v>
       </c>
       <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K53" s="11"/>
+      <c r="M53" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="N53" s="10"/>
+    </row>
+    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>21</v>
       </c>
@@ -1748,15 +2328,29 @@
       <c r="D54" s="6">
         <v>178</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="7">
         <v>290</v>
       </c>
       <c r="F54" s="8">
         <v>46210</v>
       </c>
       <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H54" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K54" s="11"/>
+      <c r="M54" s="9">
+        <v>1</v>
+      </c>
+      <c r="N54" s="10"/>
+    </row>
+    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>24</v>
       </c>
@@ -1769,15 +2363,25 @@
       <c r="D55" s="6">
         <v>351.5</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="7">
         <v>376.5</v>
       </c>
       <c r="F55" s="8">
         <v>46210</v>
       </c>
       <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K55" s="11"/>
+    </row>
+    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>6</v>
       </c>
@@ -1797,8 +2401,18 @@
         <v>46211</v>
       </c>
       <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" s="11"/>
+    </row>
+    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>6</v>
       </c>
@@ -1811,15 +2425,25 @@
       <c r="D57" s="6">
         <v>1175.5</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="7">
         <v>952</v>
       </c>
       <c r="F57" s="8">
         <v>46211</v>
       </c>
       <c r="G57" s="1"/>
-    </row>
-    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="11"/>
+    </row>
+    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>6</v>
       </c>
@@ -1832,15 +2456,25 @@
       <c r="D58" s="6">
         <v>381.5</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="7">
         <v>357</v>
       </c>
       <c r="F58" s="8">
         <v>46211</v>
       </c>
       <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H58" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" s="11"/>
+    </row>
+    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>11</v>
       </c>
@@ -1860,8 +2494,18 @@
         <v>46211</v>
       </c>
       <c r="G59" s="1"/>
-    </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K59" s="11"/>
+    </row>
+    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>11</v>
       </c>
@@ -1874,7 +2518,7 @@
       <c r="D60" s="6">
         <v>622</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="7">
         <v>715</v>
       </c>
       <c r="F60" s="8">
@@ -1882,7 +2526,7 @@
       </c>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>15</v>
       </c>
@@ -1895,15 +2539,25 @@
       <c r="D61" s="6">
         <v>243.5</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="7">
         <v>427.5</v>
       </c>
       <c r="F61" s="8">
         <v>46211</v>
       </c>
       <c r="G61" s="1"/>
-    </row>
-    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H61" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="M61" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="N61" s="14"/>
+    </row>
+    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>18</v>
       </c>
@@ -1916,15 +2570,33 @@
       <c r="D62" s="6">
         <v>508.5</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="7">
         <v>427.5</v>
       </c>
       <c r="F62" s="8">
         <v>46211</v>
       </c>
       <c r="G62" s="1"/>
-    </row>
-    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H62" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>21</v>
       </c>
@@ -1937,15 +2609,29 @@
       <c r="D63" s="6">
         <v>262.5</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="7">
         <v>290</v>
       </c>
       <c r="F63" s="8">
         <v>46211</v>
       </c>
       <c r="G63" s="1"/>
-    </row>
-    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H63" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K63" s="11"/>
+      <c r="M63" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N63" s="10"/>
+    </row>
+    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>24</v>
       </c>
@@ -1958,15 +2644,29 @@
       <c r="D64" s="6">
         <v>409</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="7">
         <v>376.5</v>
       </c>
       <c r="F64" s="8">
         <v>46211</v>
       </c>
       <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H64" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K64" s="11"/>
+      <c r="M64" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="N64" s="10"/>
+    </row>
+    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>6</v>
       </c>
@@ -1986,8 +2686,22 @@
         <v>46212</v>
       </c>
       <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H65" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K65" s="11"/>
+      <c r="M65" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="N65" s="10"/>
+    </row>
+    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>6</v>
       </c>
@@ -2000,15 +2714,29 @@
       <c r="D66" s="6">
         <v>1311</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="7">
         <v>952</v>
       </c>
       <c r="F66" s="8">
         <v>46212</v>
       </c>
       <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H66" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K66" s="11"/>
+      <c r="M66" s="9">
+        <v>1</v>
+      </c>
+      <c r="N66" s="10"/>
+    </row>
+    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>6</v>
       </c>
@@ -2021,15 +2749,25 @@
       <c r="D67" s="6">
         <v>412.5</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="7">
         <v>357</v>
       </c>
       <c r="F67" s="8">
         <v>46212</v>
       </c>
       <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H67" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K67" s="11"/>
+    </row>
+    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>11</v>
       </c>
@@ -2049,8 +2787,18 @@
         <v>46212</v>
       </c>
       <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H68" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68" s="11"/>
+    </row>
+    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>11</v>
       </c>
@@ -2063,15 +2811,25 @@
       <c r="D69" s="6">
         <v>731.5</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="7">
         <v>715</v>
       </c>
       <c r="F69" s="8">
         <v>46212</v>
       </c>
       <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="11"/>
+    </row>
+    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>15</v>
       </c>
@@ -2084,15 +2842,25 @@
       <c r="D70" s="6">
         <v>309.5</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="7">
         <v>427.5</v>
       </c>
       <c r="F70" s="8">
         <v>46212</v>
       </c>
       <c r="G70" s="1"/>
-    </row>
-    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H70" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" s="11"/>
+    </row>
+    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>18</v>
       </c>
@@ -2105,15 +2873,25 @@
       <c r="D71" s="6">
         <v>641.5</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E71" s="7">
         <v>427.5</v>
       </c>
       <c r="F71" s="8">
         <v>46212</v>
       </c>
       <c r="G71" s="1"/>
-    </row>
-    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="H71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K71" s="11"/>
+    </row>
+    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>21</v>
       </c>
@@ -2126,7 +2904,7 @@
       <c r="D72" s="6">
         <v>408.5</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="7">
         <v>290</v>
       </c>
       <c r="F72" s="8">
@@ -2134,7 +2912,7 @@
       </c>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>24</v>
       </c>
@@ -2147,7 +2925,7 @@
       <c r="D73" s="6">
         <v>456</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="7">
         <v>376.5</v>
       </c>
       <c r="F73" s="8">
@@ -2155,7 +2933,7 @@
       </c>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>6</v>
       </c>
@@ -2176,7 +2954,7 @@
       </c>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>6</v>
       </c>
@@ -2197,7 +2975,7 @@
       </c>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>6</v>
       </c>
@@ -2210,7 +2988,7 @@
       <c r="D76" s="6">
         <v>484.5</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="7">
         <v>714</v>
       </c>
       <c r="F76" s="8">
@@ -2218,7 +2996,7 @@
       </c>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>11</v>
       </c>
@@ -2239,7 +3017,7 @@
       </c>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>11</v>
       </c>
@@ -2260,7 +3038,7 @@
       </c>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>15</v>
       </c>
@@ -2273,7 +3051,7 @@
       <c r="D79" s="6">
         <v>446</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="7">
         <v>855</v>
       </c>
       <c r="F79" s="8">
@@ -2281,7 +3059,7 @@
       </c>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>18</v>
       </c>
@@ -2294,7 +3072,7 @@
       <c r="D80" s="6">
         <v>712</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="7">
         <v>855</v>
       </c>
       <c r="F80" s="8">
@@ -2315,7 +3093,7 @@
       <c r="D81" s="6">
         <v>455</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="7">
         <v>580</v>
       </c>
       <c r="F81" s="8">
@@ -2336,7 +3114,7 @@
       <c r="D82" s="6">
         <v>523.5</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="7">
         <v>752</v>
       </c>
       <c r="F82" s="8">
@@ -2399,7 +3177,7 @@
       <c r="D85" s="6">
         <v>484.5</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="7">
         <v>714</v>
       </c>
       <c r="F85" s="8">
@@ -2462,7 +3240,7 @@
       <c r="D88" s="6">
         <v>446</v>
       </c>
-      <c r="E88" s="5">
+      <c r="E88" s="7">
         <v>855</v>
       </c>
       <c r="F88" s="8">
@@ -2483,7 +3261,7 @@
       <c r="D89" s="6">
         <v>712.5</v>
       </c>
-      <c r="E89" s="5">
+      <c r="E89" s="7">
         <v>855</v>
       </c>
       <c r="F89" s="8">
@@ -2504,7 +3282,7 @@
       <c r="D90" s="6">
         <v>455</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="7">
         <v>580</v>
       </c>
       <c r="F90" s="8">
@@ -2525,7 +3303,7 @@
       <c r="D91" s="6">
         <v>523.5</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E91" s="7">
         <v>752</v>
       </c>
       <c r="F91" s="8">
@@ -2588,7 +3366,7 @@
       <c r="D94" s="6">
         <v>493.5</v>
       </c>
-      <c r="E94" s="5">
+      <c r="E94" s="7">
         <v>714</v>
       </c>
       <c r="F94" s="8">
@@ -2651,7 +3429,7 @@
       <c r="D97" s="6">
         <v>481</v>
       </c>
-      <c r="E97" s="5">
+      <c r="E97" s="7">
         <v>855</v>
       </c>
       <c r="F97" s="8">
@@ -2672,7 +3450,7 @@
       <c r="D98" s="6">
         <v>786</v>
       </c>
-      <c r="E98" s="5">
+      <c r="E98" s="7">
         <v>855</v>
       </c>
       <c r="F98" s="8">
@@ -2693,7 +3471,7 @@
       <c r="D99" s="6">
         <v>494</v>
       </c>
-      <c r="E99" s="5">
+      <c r="E99" s="7">
         <v>580</v>
       </c>
       <c r="F99" s="8">
@@ -2714,7 +3492,7 @@
       <c r="D100" s="6">
         <v>653.5</v>
       </c>
-      <c r="E100" s="5">
+      <c r="E100" s="7">
         <v>752</v>
       </c>
       <c r="F100" s="8">
@@ -2777,7 +3555,7 @@
       <c r="D103" s="6">
         <v>538.5</v>
       </c>
-      <c r="E103" s="5">
+      <c r="E103" s="7">
         <v>714</v>
       </c>
       <c r="F103" s="8">
@@ -2840,7 +3618,7 @@
       <c r="D106" s="6">
         <v>606</v>
       </c>
-      <c r="E106" s="5">
+      <c r="E106" s="7">
         <v>855</v>
       </c>
       <c r="F106" s="8">
@@ -2861,7 +3639,7 @@
       <c r="D107" s="6">
         <v>894.5</v>
       </c>
-      <c r="E107" s="5">
+      <c r="E107" s="7">
         <v>855</v>
       </c>
       <c r="F107" s="8">
@@ -2882,7 +3660,7 @@
       <c r="D108" s="6">
         <v>509</v>
       </c>
-      <c r="E108" s="5">
+      <c r="E108" s="7">
         <v>580</v>
       </c>
       <c r="F108" s="8">
@@ -2903,7 +3681,7 @@
       <c r="D109" s="6">
         <v>752</v>
       </c>
-      <c r="E109" s="5">
+      <c r="E109" s="7">
         <v>752</v>
       </c>
       <c r="F109" s="8">
@@ -2966,7 +3744,7 @@
       <c r="D112" s="6">
         <v>588</v>
       </c>
-      <c r="E112" s="5">
+      <c r="E112" s="7">
         <v>714</v>
       </c>
       <c r="F112" s="8">
@@ -3029,7 +3807,7 @@
       <c r="D115" s="6">
         <v>676</v>
       </c>
-      <c r="E115" s="5">
+      <c r="E115" s="7">
         <v>855</v>
       </c>
       <c r="F115" s="8">
@@ -3050,7 +3828,7 @@
       <c r="D116" s="6">
         <v>938.5</v>
       </c>
-      <c r="E116" s="5">
+      <c r="E116" s="7">
         <v>855</v>
       </c>
       <c r="F116" s="8">
@@ -3071,7 +3849,7 @@
       <c r="D117" s="6">
         <v>561.5</v>
       </c>
-      <c r="E117" s="5">
+      <c r="E117" s="7">
         <v>580</v>
       </c>
       <c r="F117" s="8">
@@ -3092,7 +3870,7 @@
       <c r="D118" s="6">
         <v>904</v>
       </c>
-      <c r="E118" s="5">
+      <c r="E118" s="7">
         <v>752</v>
       </c>
       <c r="F118" s="8">
@@ -3155,7 +3933,7 @@
       <c r="D121" s="6">
         <v>618</v>
       </c>
-      <c r="E121" s="5">
+      <c r="E121" s="7">
         <v>714</v>
       </c>
       <c r="F121" s="8">
@@ -3218,7 +3996,7 @@
       <c r="D124" s="6">
         <v>756</v>
       </c>
-      <c r="E124" s="5">
+      <c r="E124" s="7">
         <v>855</v>
       </c>
       <c r="F124" s="8">
@@ -3239,7 +4017,7 @@
       <c r="D125" s="6">
         <v>1005.5</v>
       </c>
-      <c r="E125" s="5">
+      <c r="E125" s="7">
         <v>855</v>
       </c>
       <c r="F125" s="8">
@@ -3260,7 +4038,7 @@
       <c r="D126" s="6">
         <v>614</v>
       </c>
-      <c r="E126" s="5">
+      <c r="E126" s="7">
         <v>580</v>
       </c>
       <c r="F126" s="8">
@@ -3281,7 +4059,7 @@
       <c r="D127" s="6">
         <v>988</v>
       </c>
-      <c r="E127" s="5">
+      <c r="E127" s="7">
         <v>752</v>
       </c>
       <c r="F127" s="8">
@@ -3302,7 +4080,7 @@
       <c r="D128" s="6">
         <v>2406.5</v>
       </c>
-      <c r="E128" s="9">
+      <c r="E128" s="7">
         <v>3213</v>
       </c>
       <c r="F128" s="8">
@@ -3323,7 +4101,7 @@
       <c r="D129" s="6">
         <v>2412.5</v>
       </c>
-      <c r="E129" s="9">
+      <c r="E129" s="7">
         <v>2856</v>
       </c>
       <c r="F129" s="8">
@@ -3344,7 +4122,7 @@
       <c r="D130" s="6">
         <v>618.5</v>
       </c>
-      <c r="E130" s="9">
+      <c r="E130" s="7">
         <v>1071</v>
       </c>
       <c r="F130" s="8">
@@ -3365,7 +4143,7 @@
       <c r="D131" s="6">
         <v>1786.5</v>
       </c>
-      <c r="E131" s="9">
+      <c r="E131" s="7">
         <v>3217.5</v>
       </c>
       <c r="F131" s="8">
@@ -3386,7 +4164,7 @@
       <c r="D132" s="6">
         <v>1397</v>
       </c>
-      <c r="E132" s="9">
+      <c r="E132" s="7">
         <v>2145</v>
       </c>
       <c r="F132" s="8">
@@ -3407,7 +4185,7 @@
       <c r="D133" s="6">
         <v>806</v>
       </c>
-      <c r="E133" s="9">
+      <c r="E133" s="7">
         <v>1282.5</v>
       </c>
       <c r="F133" s="8">
@@ -3428,7 +4206,7 @@
       <c r="D134" s="6">
         <v>1077.5</v>
       </c>
-      <c r="E134" s="9">
+      <c r="E134" s="7">
         <v>1282.5</v>
       </c>
       <c r="F134" s="8">
@@ -3449,7 +4227,7 @@
       <c r="D135" s="6">
         <v>667</v>
       </c>
-      <c r="E135" s="9">
+      <c r="E135" s="7">
         <v>870</v>
       </c>
       <c r="F135" s="8">
@@ -3470,7 +4248,7 @@
       <c r="D136" s="6">
         <v>1141</v>
       </c>
-      <c r="E136" s="9">
+      <c r="E136" s="7">
         <v>1128.75</v>
       </c>
       <c r="F136" s="8">
@@ -3491,7 +4269,7 @@
       <c r="D137" s="6">
         <v>2530</v>
       </c>
-      <c r="E137" s="9">
+      <c r="E137" s="7">
         <v>3213</v>
       </c>
       <c r="F137" s="8">
@@ -3512,7 +4290,7 @@
       <c r="D138" s="6">
         <v>2503</v>
       </c>
-      <c r="E138" s="9">
+      <c r="E138" s="7">
         <v>2856</v>
       </c>
       <c r="F138" s="8">
@@ -3533,7 +4311,7 @@
       <c r="D139" s="6">
         <v>629</v>
       </c>
-      <c r="E139" s="9">
+      <c r="E139" s="7">
         <v>1071</v>
       </c>
       <c r="F139" s="8">
@@ -3554,7 +4332,7 @@
       <c r="D140" s="6">
         <v>1871</v>
       </c>
-      <c r="E140" s="9">
+      <c r="E140" s="7">
         <v>3217.5</v>
       </c>
       <c r="F140" s="8">
@@ -3575,7 +4353,7 @@
       <c r="D141" s="6">
         <v>1484</v>
       </c>
-      <c r="E141" s="9">
+      <c r="E141" s="7">
         <v>2145</v>
       </c>
       <c r="F141" s="8">
@@ -3596,7 +4374,7 @@
       <c r="D142" s="6">
         <v>814</v>
       </c>
-      <c r="E142" s="9">
+      <c r="E142" s="7">
         <v>1282.5</v>
       </c>
       <c r="F142" s="8">
@@ -3617,7 +4395,7 @@
       <c r="D143" s="6">
         <v>1077.5</v>
       </c>
-      <c r="E143" s="9">
+      <c r="E143" s="7">
         <v>1282.5</v>
       </c>
       <c r="F143" s="8">
@@ -3638,7 +4416,7 @@
       <c r="D144" s="6">
         <v>677</v>
       </c>
-      <c r="E144" s="9">
+      <c r="E144" s="7">
         <v>870</v>
       </c>
       <c r="F144" s="8">
@@ -3659,7 +4437,7 @@
       <c r="D145" s="6">
         <v>1158</v>
       </c>
-      <c r="E145" s="9">
+      <c r="E145" s="7">
         <v>1128.75</v>
       </c>
       <c r="F145" s="8">
@@ -3680,7 +4458,7 @@
       <c r="D146" s="6">
         <v>2734.5</v>
       </c>
-      <c r="E146" s="9">
+      <c r="E146" s="7">
         <v>3213</v>
       </c>
       <c r="F146" s="8">
@@ -3701,7 +4479,7 @@
       <c r="D147" s="6">
         <v>2626</v>
       </c>
-      <c r="E147" s="9">
+      <c r="E147" s="7">
         <v>2856</v>
       </c>
       <c r="F147" s="8">
@@ -3722,7 +4500,7 @@
       <c r="D148" s="6">
         <v>660</v>
       </c>
-      <c r="E148" s="9">
+      <c r="E148" s="7">
         <v>1071</v>
       </c>
       <c r="F148" s="8">
@@ -3743,7 +4521,7 @@
       <c r="D149" s="6">
         <v>1956.5</v>
       </c>
-      <c r="E149" s="9">
+      <c r="E149" s="7">
         <v>3217.5</v>
       </c>
       <c r="F149" s="8">
@@ -3764,7 +4542,7 @@
       <c r="D150" s="6">
         <v>1632.5</v>
       </c>
-      <c r="E150" s="9">
+      <c r="E150" s="7">
         <v>2145</v>
       </c>
       <c r="F150" s="8">
@@ -3785,7 +4563,7 @@
       <c r="D151" s="6">
         <v>831</v>
       </c>
-      <c r="E151" s="9">
+      <c r="E151" s="7">
         <v>1282.5</v>
       </c>
       <c r="F151" s="8">
@@ -3806,7 +4584,7 @@
       <c r="D152" s="6">
         <v>1144</v>
       </c>
-      <c r="E152" s="9">
+      <c r="E152" s="7">
         <v>1282.5</v>
       </c>
       <c r="F152" s="8">
@@ -3827,7 +4605,7 @@
       <c r="D153" s="6">
         <v>751.5</v>
       </c>
-      <c r="E153" s="9">
+      <c r="E153" s="7">
         <v>870</v>
       </c>
       <c r="F153" s="8">
@@ -3848,7 +4626,7 @@
       <c r="D154" s="6">
         <v>1185</v>
       </c>
-      <c r="E154" s="9">
+      <c r="E154" s="7">
         <v>1128.75</v>
       </c>
       <c r="F154" s="8">
@@ -3869,7 +4647,7 @@
       <c r="D155" s="6">
         <v>2890</v>
       </c>
-      <c r="E155" s="9">
+      <c r="E155" s="7">
         <v>3213</v>
       </c>
       <c r="F155" s="8">
@@ -3890,7 +4668,7 @@
       <c r="D156" s="6">
         <v>2760</v>
       </c>
-      <c r="E156" s="9">
+      <c r="E156" s="7">
         <v>2856</v>
       </c>
       <c r="F156" s="8">
@@ -3911,7 +4689,7 @@
       <c r="D157" s="6">
         <v>709</v>
       </c>
-      <c r="E157" s="9">
+      <c r="E157" s="7">
         <v>1071</v>
       </c>
       <c r="F157" s="8">
@@ -3932,7 +4710,7 @@
       <c r="D158" s="6">
         <v>2006</v>
       </c>
-      <c r="E158" s="9">
+      <c r="E158" s="7">
         <v>3217.5</v>
       </c>
       <c r="F158" s="8">
@@ -3953,7 +4731,7 @@
       <c r="D159" s="6">
         <v>1707</v>
       </c>
-      <c r="E159" s="9">
+      <c r="E159" s="7">
         <v>2145</v>
       </c>
       <c r="F159" s="8">
@@ -3974,7 +4752,7 @@
       <c r="D160" s="6">
         <v>908</v>
       </c>
-      <c r="E160" s="9">
+      <c r="E160" s="7">
         <v>1282.5</v>
       </c>
       <c r="F160" s="8">
@@ -3995,7 +4773,7 @@
       <c r="D161" s="6">
         <v>1300.5</v>
       </c>
-      <c r="E161" s="9">
+      <c r="E161" s="7">
         <v>1282.5</v>
       </c>
       <c r="F161" s="8">
@@ -4016,7 +4794,7 @@
       <c r="D162" s="6">
         <v>767.5</v>
       </c>
-      <c r="E162" s="9">
+      <c r="E162" s="7">
         <v>870</v>
       </c>
       <c r="F162" s="8">
@@ -4037,7 +4815,7 @@
       <c r="D163" s="6">
         <v>1250.5</v>
       </c>
-      <c r="E163" s="9">
+      <c r="E163" s="7">
         <v>1128.75</v>
       </c>
       <c r="F163" s="8">
@@ -4058,7 +4836,7 @@
       <c r="D164" s="6">
         <v>2904.5</v>
       </c>
-      <c r="E164" s="9">
+      <c r="E164" s="7">
         <v>3213</v>
       </c>
       <c r="F164" s="8">
@@ -4079,7 +4857,7 @@
       <c r="D165" s="6">
         <v>2868</v>
       </c>
-      <c r="E165" s="9">
+      <c r="E165" s="7">
         <v>2856</v>
       </c>
       <c r="F165" s="8">
@@ -4100,7 +4878,7 @@
       <c r="D166" s="6">
         <v>709.5</v>
       </c>
-      <c r="E166" s="9">
+      <c r="E166" s="7">
         <v>1071</v>
       </c>
       <c r="F166" s="8">
@@ -4121,7 +4899,7 @@
       <c r="D167" s="6">
         <v>2019.5</v>
       </c>
-      <c r="E167" s="9">
+      <c r="E167" s="7">
         <v>3217.5</v>
       </c>
       <c r="F167" s="8">
@@ -4142,7 +4920,7 @@
       <c r="D168" s="6">
         <v>1707</v>
       </c>
-      <c r="E168" s="9">
+      <c r="E168" s="7">
         <v>2145</v>
       </c>
       <c r="F168" s="8">
@@ -4163,7 +4941,7 @@
       <c r="D169" s="6">
         <v>950.5</v>
       </c>
-      <c r="E169" s="9">
+      <c r="E169" s="7">
         <v>1282.5</v>
       </c>
       <c r="F169" s="8">
@@ -4184,7 +4962,7 @@
       <c r="D170" s="6">
         <v>1321.5</v>
       </c>
-      <c r="E170" s="9">
+      <c r="E170" s="7">
         <v>1282.5</v>
       </c>
       <c r="F170" s="8">
@@ -4205,7 +4983,7 @@
       <c r="D171" s="6">
         <v>772.5</v>
       </c>
-      <c r="E171" s="9">
+      <c r="E171" s="7">
         <v>870</v>
       </c>
       <c r="F171" s="8">
@@ -4226,7 +5004,7 @@
       <c r="D172" s="6">
         <v>1242.5</v>
       </c>
-      <c r="E172" s="9">
+      <c r="E172" s="7">
         <v>1128.75</v>
       </c>
       <c r="F172" s="8">
@@ -4247,7 +5025,7 @@
       <c r="D173" s="6">
         <v>3050.5</v>
       </c>
-      <c r="E173" s="9">
+      <c r="E173" s="7">
         <v>3213</v>
       </c>
       <c r="F173" s="8">
@@ -4268,7 +5046,7 @@
       <c r="D174" s="6">
         <v>3092</v>
       </c>
-      <c r="E174" s="9">
+      <c r="E174" s="7">
         <v>2856</v>
       </c>
       <c r="F174" s="8">
@@ -4289,7 +5067,7 @@
       <c r="D175" s="6">
         <v>718.5</v>
       </c>
-      <c r="E175" s="9">
+      <c r="E175" s="7">
         <v>1071</v>
       </c>
       <c r="F175" s="8">
@@ -4310,7 +5088,7 @@
       <c r="D176" s="6">
         <v>2100.5</v>
       </c>
-      <c r="E176" s="9">
+      <c r="E176" s="7">
         <v>3217.5</v>
       </c>
       <c r="F176" s="8">
@@ -4331,7 +5109,7 @@
       <c r="D177" s="6">
         <v>1786</v>
       </c>
-      <c r="E177" s="9">
+      <c r="E177" s="7">
         <v>2145</v>
       </c>
       <c r="F177" s="8">
@@ -4352,7 +5130,7 @@
       <c r="D178" s="6">
         <v>981</v>
       </c>
-      <c r="E178" s="9">
+      <c r="E178" s="7">
         <v>1282.5</v>
       </c>
       <c r="F178" s="8">
@@ -4373,7 +5151,7 @@
       <c r="D179" s="6">
         <v>1326.5</v>
       </c>
-      <c r="E179" s="9">
+      <c r="E179" s="7">
         <v>1282.5</v>
       </c>
       <c r="F179" s="8">
@@ -4394,7 +5172,7 @@
       <c r="D180" s="6">
         <v>776.5</v>
       </c>
-      <c r="E180" s="9">
+      <c r="E180" s="7">
         <v>870</v>
       </c>
       <c r="F180" s="8">
@@ -4415,7 +5193,7 @@
       <c r="D181" s="6">
         <v>1272</v>
       </c>
-      <c r="E181" s="9">
+      <c r="E181" s="7">
         <v>1128.75</v>
       </c>
       <c r="F181" s="8">
@@ -4436,7 +5214,7 @@
       <c r="D182" s="6">
         <v>3190.5</v>
       </c>
-      <c r="E182" s="9">
+      <c r="E182" s="7">
         <v>4284</v>
       </c>
       <c r="F182" s="8">
@@ -4457,7 +5235,7 @@
       <c r="D183" s="6">
         <v>3171</v>
       </c>
-      <c r="E183" s="9">
+      <c r="E183" s="7">
         <v>3808</v>
       </c>
       <c r="F183" s="8">
@@ -4478,7 +5256,7 @@
       <c r="D184" s="6">
         <v>753</v>
       </c>
-      <c r="E184" s="9">
+      <c r="E184" s="7">
         <v>1428</v>
       </c>
       <c r="F184" s="8">
@@ -4499,7 +5277,7 @@
       <c r="D185" s="6">
         <v>2208.5</v>
       </c>
-      <c r="E185" s="9">
+      <c r="E185" s="7">
         <v>4290</v>
       </c>
       <c r="F185" s="8">
@@ -4520,7 +5298,7 @@
       <c r="D186" s="6">
         <v>1846</v>
       </c>
-      <c r="E186" s="9">
+      <c r="E186" s="7">
         <v>2860</v>
       </c>
       <c r="F186" s="8">
@@ -4541,7 +5319,7 @@
       <c r="D187" s="6">
         <v>1088</v>
       </c>
-      <c r="E187" s="9">
+      <c r="E187" s="7">
         <v>1710</v>
       </c>
       <c r="F187" s="8">
@@ -4562,7 +5340,7 @@
       <c r="D188" s="6">
         <v>1326.5</v>
       </c>
-      <c r="E188" s="9">
+      <c r="E188" s="7">
         <v>1710</v>
       </c>
       <c r="F188" s="8">
@@ -4583,7 +5361,7 @@
       <c r="D189" s="6">
         <v>810</v>
       </c>
-      <c r="E189" s="9">
+      <c r="E189" s="7">
         <v>1160</v>
       </c>
       <c r="F189" s="8">
@@ -4604,7 +5382,7 @@
       <c r="D190" s="6">
         <v>1305</v>
       </c>
-      <c r="E190" s="9">
+      <c r="E190" s="7">
         <v>1505</v>
       </c>
       <c r="F190" s="8">
@@ -4625,7 +5403,7 @@
       <c r="D191" s="6">
         <v>3197</v>
       </c>
-      <c r="E191" s="9">
+      <c r="E191" s="7">
         <v>4284</v>
       </c>
       <c r="F191" s="8">
@@ -4646,7 +5424,7 @@
       <c r="D192" s="6">
         <v>3181</v>
       </c>
-      <c r="E192" s="9">
+      <c r="E192" s="7">
         <v>3808</v>
       </c>
       <c r="F192" s="8">
@@ -4667,7 +5445,7 @@
       <c r="D193" s="6">
         <v>804</v>
       </c>
-      <c r="E193" s="9">
+      <c r="E193" s="7">
         <v>1428</v>
       </c>
       <c r="F193" s="8">
@@ -4688,7 +5466,7 @@
       <c r="D194" s="6">
         <v>2250</v>
       </c>
-      <c r="E194" s="9">
+      <c r="E194" s="7">
         <v>4290</v>
       </c>
       <c r="F194" s="8">
@@ -4709,7 +5487,7 @@
       <c r="D195" s="6">
         <v>1892</v>
       </c>
-      <c r="E195" s="9">
+      <c r="E195" s="7">
         <v>2860</v>
       </c>
       <c r="F195" s="8">
@@ -4730,7 +5508,7 @@
       <c r="D196" s="6">
         <v>1088</v>
       </c>
-      <c r="E196" s="9">
+      <c r="E196" s="7">
         <v>1710</v>
       </c>
       <c r="F196" s="8">
@@ -4751,7 +5529,7 @@
       <c r="D197" s="6">
         <v>1326.5</v>
       </c>
-      <c r="E197" s="9">
+      <c r="E197" s="7">
         <v>1710</v>
       </c>
       <c r="F197" s="8">
@@ -4772,7 +5550,7 @@
       <c r="D198" s="6">
         <v>810</v>
       </c>
-      <c r="E198" s="9">
+      <c r="E198" s="7">
         <v>1160</v>
       </c>
       <c r="F198" s="8">
@@ -4793,7 +5571,7 @@
       <c r="D199" s="6">
         <v>1305</v>
       </c>
-      <c r="E199" s="9">
+      <c r="E199" s="7">
         <v>1505</v>
       </c>
       <c r="F199" s="8">
@@ -4814,7 +5592,7 @@
       <c r="D200" s="6">
         <v>3247</v>
       </c>
-      <c r="E200" s="9">
+      <c r="E200" s="7">
         <v>4284</v>
       </c>
       <c r="F200" s="8">
@@ -4835,7 +5613,7 @@
       <c r="D201" s="6">
         <v>3350</v>
       </c>
-      <c r="E201" s="9">
+      <c r="E201" s="7">
         <v>3808</v>
       </c>
       <c r="F201" s="8">
@@ -4856,7 +5634,7 @@
       <c r="D202" s="6">
         <v>1004.5</v>
       </c>
-      <c r="E202" s="9">
+      <c r="E202" s="7">
         <v>1428</v>
       </c>
       <c r="F202" s="8">
@@ -4877,7 +5655,7 @@
       <c r="D203" s="6">
         <v>2456.5</v>
       </c>
-      <c r="E203" s="9">
+      <c r="E203" s="7">
         <v>4290</v>
       </c>
       <c r="F203" s="8">
@@ -4898,7 +5676,7 @@
       <c r="D204" s="6">
         <v>2078</v>
       </c>
-      <c r="E204" s="9">
+      <c r="E204" s="7">
         <v>2860</v>
       </c>
       <c r="F204" s="8">
@@ -4919,7 +5697,7 @@
       <c r="D205" s="6">
         <v>1181.5</v>
       </c>
-      <c r="E205" s="9">
+      <c r="E205" s="7">
         <v>1710</v>
       </c>
       <c r="F205" s="8">
@@ -4940,7 +5718,7 @@
       <c r="D206" s="6">
         <v>1340</v>
       </c>
-      <c r="E206" s="9">
+      <c r="E206" s="7">
         <v>1710</v>
       </c>
       <c r="F206" s="8">
@@ -4961,7 +5739,7 @@
       <c r="D207" s="6">
         <v>817</v>
       </c>
-      <c r="E207" s="9">
+      <c r="E207" s="7">
         <v>1160</v>
       </c>
       <c r="F207" s="8">
@@ -4982,7 +5760,7 @@
       <c r="D208" s="6">
         <v>1345</v>
       </c>
-      <c r="E208" s="9">
+      <c r="E208" s="7">
         <v>1505</v>
       </c>
       <c r="F208" s="8">
@@ -5003,7 +5781,7 @@
       <c r="D209" s="6">
         <v>3638</v>
       </c>
-      <c r="E209" s="9">
+      <c r="E209" s="7">
         <v>4284</v>
       </c>
       <c r="F209" s="8">
@@ -5024,7 +5802,7 @@
       <c r="D210" s="6">
         <v>3432.5</v>
       </c>
-      <c r="E210" s="9">
+      <c r="E210" s="7">
         <v>3808</v>
       </c>
       <c r="F210" s="8">
@@ -5045,7 +5823,7 @@
       <c r="D211" s="6">
         <v>1097.5</v>
       </c>
-      <c r="E211" s="9">
+      <c r="E211" s="7">
         <v>1428</v>
       </c>
       <c r="F211" s="8">
@@ -5066,7 +5844,7 @@
       <c r="D212" s="6">
         <v>2633.5</v>
       </c>
-      <c r="E212" s="9">
+      <c r="E212" s="7">
         <v>4290</v>
       </c>
       <c r="F212" s="8">
@@ -5087,7 +5865,7 @@
       <c r="D213" s="6">
         <v>2120.5</v>
       </c>
-      <c r="E213" s="9">
+      <c r="E213" s="7">
         <v>2860</v>
       </c>
       <c r="F213" s="8">
@@ -5108,7 +5886,7 @@
       <c r="D214" s="6">
         <v>1274.5</v>
       </c>
-      <c r="E214" s="9">
+      <c r="E214" s="7">
         <v>1710</v>
       </c>
       <c r="F214" s="8">
@@ -5129,7 +5907,7 @@
       <c r="D215" s="6">
         <v>1391</v>
       </c>
-      <c r="E215" s="9">
+      <c r="E215" s="7">
         <v>1710</v>
       </c>
       <c r="F215" s="8">
@@ -5150,7 +5928,7 @@
       <c r="D216" s="6">
         <v>862</v>
       </c>
-      <c r="E216" s="9">
+      <c r="E216" s="7">
         <v>1160</v>
       </c>
       <c r="F216" s="8">
@@ -5171,7 +5949,7 @@
       <c r="D217" s="6">
         <v>1492</v>
       </c>
-      <c r="E217" s="9">
+      <c r="E217" s="7">
         <v>1505</v>
       </c>
       <c r="F217" s="8">
@@ -5192,7 +5970,7 @@
       <c r="D218" s="6">
         <v>3721.5</v>
       </c>
-      <c r="E218" s="9">
+      <c r="E218" s="7">
         <v>4284</v>
       </c>
       <c r="F218" s="8">
@@ -5213,7 +5991,7 @@
       <c r="D219" s="6">
         <v>3667.5</v>
       </c>
-      <c r="E219" s="9">
+      <c r="E219" s="7">
         <v>3808</v>
       </c>
       <c r="F219" s="8">
@@ -5234,7 +6012,7 @@
       <c r="D220" s="6">
         <v>1204.5</v>
       </c>
-      <c r="E220" s="9">
+      <c r="E220" s="7">
         <v>1428</v>
       </c>
       <c r="F220" s="8">
@@ -5255,7 +6033,7 @@
       <c r="D221" s="6">
         <v>2748</v>
       </c>
-      <c r="E221" s="9">
+      <c r="E221" s="7">
         <v>4290</v>
       </c>
       <c r="F221" s="8">
@@ -5276,7 +6054,7 @@
       <c r="D222" s="6">
         <v>2259.5</v>
       </c>
-      <c r="E222" s="9">
+      <c r="E222" s="7">
         <v>2860</v>
       </c>
       <c r="F222" s="8">
@@ -5297,7 +6075,7 @@
       <c r="D223" s="6">
         <v>1320.5</v>
       </c>
-      <c r="E223" s="9">
+      <c r="E223" s="7">
         <v>1710</v>
       </c>
       <c r="F223" s="8">
@@ -5318,7 +6096,7 @@
       <c r="D224" s="6">
         <v>1455</v>
       </c>
-      <c r="E224" s="9">
+      <c r="E224" s="7">
         <v>1710</v>
       </c>
       <c r="F224" s="8">
@@ -5339,7 +6117,7 @@
       <c r="D225" s="6">
         <v>924</v>
       </c>
-      <c r="E225" s="9">
+      <c r="E225" s="7">
         <v>1160</v>
       </c>
       <c r="F225" s="8">
@@ -5360,7 +6138,7 @@
       <c r="D226" s="6">
         <v>1513.5</v>
       </c>
-      <c r="E226" s="9">
+      <c r="E226" s="7">
         <v>1505</v>
       </c>
       <c r="F226" s="8">
@@ -5381,7 +6159,7 @@
       <c r="D227" s="6">
         <v>3837</v>
       </c>
-      <c r="E227" s="9">
+      <c r="E227" s="7">
         <v>4284</v>
       </c>
       <c r="F227" s="8">
@@ -5402,7 +6180,7 @@
       <c r="D228" s="6">
         <v>4080.5</v>
       </c>
-      <c r="E228" s="9">
+      <c r="E228" s="7">
         <v>3808</v>
       </c>
       <c r="F228" s="8">
@@ -5423,7 +6201,7 @@
       <c r="D229" s="6">
         <v>1271</v>
       </c>
-      <c r="E229" s="9">
+      <c r="E229" s="7">
         <v>1428</v>
       </c>
       <c r="F229" s="8">
@@ -5444,7 +6222,7 @@
       <c r="D230" s="6">
         <v>2997.5</v>
       </c>
-      <c r="E230" s="9">
+      <c r="E230" s="7">
         <v>4290</v>
       </c>
       <c r="F230" s="8">
@@ -5465,7 +6243,7 @@
       <c r="D231" s="6">
         <v>2364.5</v>
       </c>
-      <c r="E231" s="9">
+      <c r="E231" s="7">
         <v>2860</v>
       </c>
       <c r="F231" s="8">
@@ -5486,7 +6264,7 @@
       <c r="D232" s="6">
         <v>1455.5</v>
       </c>
-      <c r="E232" s="9">
+      <c r="E232" s="7">
         <v>1710</v>
       </c>
       <c r="F232" s="8">
@@ -5507,7 +6285,7 @@
       <c r="D233" s="6">
         <v>1495.5</v>
       </c>
-      <c r="E233" s="9">
+      <c r="E233" s="7">
         <v>1710</v>
       </c>
       <c r="F233" s="8">
@@ -5528,7 +6306,7 @@
       <c r="D234" s="6">
         <v>941.5</v>
       </c>
-      <c r="E234" s="9">
+      <c r="E234" s="7">
         <v>1160</v>
       </c>
       <c r="F234" s="8">
@@ -5549,7 +6327,7 @@
       <c r="D235" s="6">
         <v>1565</v>
       </c>
-      <c r="E235" s="9">
+      <c r="E235" s="7">
         <v>1505</v>
       </c>
       <c r="F235" s="8">
@@ -5570,7 +6348,7 @@
       <c r="D236" s="6">
         <v>4117</v>
       </c>
-      <c r="E236" s="9">
+      <c r="E236" s="7">
         <v>4284</v>
       </c>
       <c r="F236" s="8">
@@ -5591,7 +6369,7 @@
       <c r="D237" s="6">
         <v>4178</v>
       </c>
-      <c r="E237" s="9">
+      <c r="E237" s="7">
         <v>3808</v>
       </c>
       <c r="F237" s="8">
@@ -5612,7 +6390,7 @@
       <c r="D238" s="6">
         <v>1336.5</v>
       </c>
-      <c r="E238" s="9">
+      <c r="E238" s="7">
         <v>1428</v>
       </c>
       <c r="F238" s="8">
@@ -5633,7 +6411,7 @@
       <c r="D239" s="6">
         <v>3131.5</v>
       </c>
-      <c r="E239" s="9">
+      <c r="E239" s="7">
         <v>4290</v>
       </c>
       <c r="F239" s="8">
@@ -5654,7 +6432,7 @@
       <c r="D240" s="6">
         <v>2671</v>
       </c>
-      <c r="E240" s="9">
+      <c r="E240" s="7">
         <v>2860</v>
       </c>
       <c r="F240" s="8">
@@ -5662,7 +6440,7 @@
       </c>
       <c r="G240" s="1"/>
     </row>
-    <row r="241" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A241" s="5" t="s">
         <v>15</v>
       </c>
@@ -5675,7 +6453,7 @@
       <c r="D241" s="6">
         <v>1554.5</v>
       </c>
-      <c r="E241" s="9">
+      <c r="E241" s="7">
         <v>1710</v>
       </c>
       <c r="F241" s="8">
@@ -5683,7 +6461,7 @@
       </c>
       <c r="G241" s="1"/>
     </row>
-    <row r="242" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A242" s="5" t="s">
         <v>18</v>
       </c>
@@ -5696,7 +6474,7 @@
       <c r="D242" s="6">
         <v>1564</v>
       </c>
-      <c r="E242" s="9">
+      <c r="E242" s="7">
         <v>1710</v>
       </c>
       <c r="F242" s="8">
@@ -5704,7 +6482,7 @@
       </c>
       <c r="G242" s="1"/>
     </row>
-    <row r="243" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A243" s="5" t="s">
         <v>21</v>
       </c>
@@ -5717,7 +6495,7 @@
       <c r="D243" s="6">
         <v>955</v>
       </c>
-      <c r="E243" s="9">
+      <c r="E243" s="7">
         <v>1160</v>
       </c>
       <c r="F243" s="8">
@@ -5725,7 +6503,7 @@
       </c>
       <c r="G243" s="1"/>
     </row>
-    <row r="244" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A244" s="5" t="s">
         <v>24</v>
       </c>
@@ -5738,7 +6516,7 @@
       <c r="D244" s="6">
         <v>1665</v>
       </c>
-      <c r="E244" s="9">
+      <c r="E244" s="7">
         <v>1505</v>
       </c>
       <c r="F244" s="8">
@@ -5746,10 +6524,4349 @@
       </c>
       <c r="G244" s="1"/>
     </row>
+    <row r="245" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245" s="6">
+        <v>41.5</v>
+      </c>
+      <c r="E245" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F245" s="8">
+        <v>46235</v>
+      </c>
+      <c r="G245" s="12"/>
+      <c r="K245" s="13"/>
+    </row>
+    <row r="246" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D246" s="6">
+        <v>62</v>
+      </c>
+      <c r="E246" s="7">
+        <v>995</v>
+      </c>
+      <c r="F246" s="8">
+        <v>46235</v>
+      </c>
+      <c r="K246" s="13"/>
+    </row>
+    <row r="247" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D247" s="6">
+        <v>9</v>
+      </c>
+      <c r="E247" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F247" s="8">
+        <v>46235</v>
+      </c>
+      <c r="K247" s="13"/>
+    </row>
+    <row r="248" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D248" s="6">
+        <v>64</v>
+      </c>
+      <c r="E248" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F248" s="8">
+        <v>46235</v>
+      </c>
+      <c r="K248" s="13"/>
+    </row>
+    <row r="249" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D249" s="6">
+        <v>42</v>
+      </c>
+      <c r="E249" s="7">
+        <v>695</v>
+      </c>
+      <c r="F249" s="8">
+        <v>46235</v>
+      </c>
+      <c r="K249" s="13"/>
+    </row>
+    <row r="250" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D250" s="6">
+        <v>38.5</v>
+      </c>
+      <c r="E250" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F250" s="8">
+        <v>46235</v>
+      </c>
+      <c r="K250" s="13"/>
+    </row>
+    <row r="251" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D251" s="6">
+        <v>46</v>
+      </c>
+      <c r="E251" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F251" s="8">
+        <v>46235</v>
+      </c>
+      <c r="K251" s="13"/>
+    </row>
+    <row r="252" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D252" s="6">
+        <v>0</v>
+      </c>
+      <c r="E252" s="7">
+        <v>280</v>
+      </c>
+      <c r="F252" s="8">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D253" s="6">
+        <v>0</v>
+      </c>
+      <c r="E253" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F253" s="8">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D254" s="6">
+        <v>291</v>
+      </c>
+      <c r="E254" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F254" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="6">
+        <v>256</v>
+      </c>
+      <c r="E255" s="7">
+        <v>995</v>
+      </c>
+      <c r="F255" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D256" s="6">
+        <v>18</v>
+      </c>
+      <c r="E256" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F256" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D257" s="6">
+        <v>238.5</v>
+      </c>
+      <c r="E257" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F257" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D258" s="6">
+        <v>102</v>
+      </c>
+      <c r="E258" s="7">
+        <v>695</v>
+      </c>
+      <c r="F258" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D259" s="6">
+        <v>138.5</v>
+      </c>
+      <c r="E259" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F259" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D260" s="6">
+        <v>213.5</v>
+      </c>
+      <c r="E260" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F260" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D261" s="6">
+        <v>25.5</v>
+      </c>
+      <c r="E261" s="7">
+        <v>280</v>
+      </c>
+      <c r="F261" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D262" s="6">
+        <v>58.5</v>
+      </c>
+      <c r="E262" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F262" s="8">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D263" s="6">
+        <v>538</v>
+      </c>
+      <c r="E263" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F263" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D264" s="6">
+        <v>332.5</v>
+      </c>
+      <c r="E264" s="7">
+        <v>995</v>
+      </c>
+      <c r="F264" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D265" s="6">
+        <v>30.5</v>
+      </c>
+      <c r="E265" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F265" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D266" s="6">
+        <v>466</v>
+      </c>
+      <c r="E266" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F266" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D267" s="6">
+        <v>189</v>
+      </c>
+      <c r="E267" s="7">
+        <v>695</v>
+      </c>
+      <c r="F267" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D268" s="6">
+        <v>228.5</v>
+      </c>
+      <c r="E268" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F268" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D269" s="6">
+        <v>305.5</v>
+      </c>
+      <c r="E269" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F269" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D270" s="6">
+        <v>68.5</v>
+      </c>
+      <c r="E270" s="7">
+        <v>280</v>
+      </c>
+      <c r="F270" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D271" s="6">
+        <v>127</v>
+      </c>
+      <c r="E271" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F271" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D272" s="6"/>
+      <c r="E272" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F272" s="8">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D273" s="6"/>
+      <c r="E273" s="7">
+        <v>995</v>
+      </c>
+      <c r="F273" s="8">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D274" s="6"/>
+      <c r="E274" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F274" s="8">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D275" s="6"/>
+      <c r="E275" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F275" s="8">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D276" s="6"/>
+      <c r="E276" s="7">
+        <v>695</v>
+      </c>
+      <c r="F276" s="8">
+        <v>46239</v>
+      </c>
+      <c r="J276" s="13"/>
+    </row>
+    <row r="277" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D277" s="6"/>
+      <c r="E277" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F277" s="8">
+        <v>46239</v>
+      </c>
+      <c r="J277" s="13"/>
+    </row>
+    <row r="278" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D278" s="6"/>
+      <c r="E278" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F278" s="8">
+        <v>46239</v>
+      </c>
+      <c r="J278" s="13"/>
+    </row>
+    <row r="279" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D279" s="6"/>
+      <c r="E279" s="7">
+        <v>280</v>
+      </c>
+      <c r="F279" s="8">
+        <v>46239</v>
+      </c>
+      <c r="J279" s="13"/>
+    </row>
+    <row r="280" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D280" s="6"/>
+      <c r="E280" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F280" s="8">
+        <v>46239</v>
+      </c>
+      <c r="J280" s="13"/>
+    </row>
+    <row r="281" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D281" s="6"/>
+      <c r="E281" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F281" s="8">
+        <v>46240</v>
+      </c>
+      <c r="J281" s="13"/>
+    </row>
+    <row r="282" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D282" s="6"/>
+      <c r="E282" s="7">
+        <v>995</v>
+      </c>
+      <c r="F282" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D283" s="6"/>
+      <c r="E283" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F283" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D284" s="6"/>
+      <c r="E284" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F284" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D285" s="6"/>
+      <c r="E285" s="7">
+        <v>695</v>
+      </c>
+      <c r="F285" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D286" s="6"/>
+      <c r="E286" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F286" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D287" s="6"/>
+      <c r="E287" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F287" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D288" s="6"/>
+      <c r="E288" s="7">
+        <v>280</v>
+      </c>
+      <c r="F288" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D289" s="6"/>
+      <c r="E289" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F289" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D290" s="6"/>
+      <c r="E290" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F290" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D291" s="6"/>
+      <c r="E291" s="7">
+        <v>995</v>
+      </c>
+      <c r="F291" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D292" s="6"/>
+      <c r="E292" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F292" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D293" s="6"/>
+      <c r="E293" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F293" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D294" s="6"/>
+      <c r="E294" s="7">
+        <v>695</v>
+      </c>
+      <c r="F294" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D295" s="6"/>
+      <c r="E295" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F295" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D296" s="6"/>
+      <c r="E296" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F296" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D297" s="6"/>
+      <c r="E297" s="7">
+        <v>280</v>
+      </c>
+      <c r="F297" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D298" s="6"/>
+      <c r="E298" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F298" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D299" s="6"/>
+      <c r="E299" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F299" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D300" s="6"/>
+      <c r="E300" s="7">
+        <v>995</v>
+      </c>
+      <c r="F300" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D301" s="6"/>
+      <c r="E301" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F301" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D302" s="6"/>
+      <c r="E302" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F302" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D303" s="6"/>
+      <c r="E303" s="7">
+        <v>695</v>
+      </c>
+      <c r="F303" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D304" s="6"/>
+      <c r="E304" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F304" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D305" s="6"/>
+      <c r="E305" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F305" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D306" s="6"/>
+      <c r="E306" s="7">
+        <v>280</v>
+      </c>
+      <c r="F306" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D307" s="6"/>
+      <c r="E307" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F307" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D308" s="6"/>
+      <c r="E308" s="7">
+        <v>1119.3800000000001</v>
+      </c>
+      <c r="F308" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D309" s="6"/>
+      <c r="E309" s="7">
+        <v>995</v>
+      </c>
+      <c r="F309" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D310" s="6"/>
+      <c r="E310" s="7">
+        <v>373.13</v>
+      </c>
+      <c r="F310" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D311" s="6"/>
+      <c r="E311" s="7">
+        <v>1042.5</v>
+      </c>
+      <c r="F311" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D312" s="6"/>
+      <c r="E312" s="7">
+        <v>695</v>
+      </c>
+      <c r="F312" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D313" s="6"/>
+      <c r="E313" s="7">
+        <v>427.5</v>
+      </c>
+      <c r="F313" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D314" s="6"/>
+      <c r="E314" s="7">
+        <v>402.5</v>
+      </c>
+      <c r="F314" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D315" s="6"/>
+      <c r="E315" s="7">
+        <v>280</v>
+      </c>
+      <c r="F315" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D316" s="6"/>
+      <c r="E316" s="7">
+        <v>351.25</v>
+      </c>
+      <c r="F316" s="8">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D317" s="6"/>
+      <c r="E317" s="7">
+        <v>2238.75</v>
+      </c>
+      <c r="F317" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D318" s="6"/>
+      <c r="E318" s="7">
+        <v>1990</v>
+      </c>
+      <c r="F318" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D319" s="6"/>
+      <c r="E319" s="7">
+        <v>746.25</v>
+      </c>
+      <c r="F319" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D320" s="6"/>
+      <c r="E320" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F320" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D321" s="6"/>
+      <c r="E321" s="7">
+        <v>1390</v>
+      </c>
+      <c r="F321" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D322" s="6"/>
+      <c r="E322" s="7">
+        <v>855</v>
+      </c>
+      <c r="F322" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D323" s="6"/>
+      <c r="E323" s="7">
+        <v>805</v>
+      </c>
+      <c r="F323" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D324" s="6"/>
+      <c r="E324" s="7">
+        <v>560</v>
+      </c>
+      <c r="F324" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D325" s="6"/>
+      <c r="E325" s="7">
+        <v>702.5</v>
+      </c>
+      <c r="F325" s="8">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D326" s="6"/>
+      <c r="E326" s="7">
+        <v>2238.75</v>
+      </c>
+      <c r="F326" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D327" s="6"/>
+      <c r="E327" s="7">
+        <v>1990</v>
+      </c>
+      <c r="F327" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D328" s="6"/>
+      <c r="E328" s="7">
+        <v>746.25</v>
+      </c>
+      <c r="F328" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D329" s="6"/>
+      <c r="E329" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F329" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D330" s="6"/>
+      <c r="E330" s="7">
+        <v>1390</v>
+      </c>
+      <c r="F330" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D331" s="6"/>
+      <c r="E331" s="7">
+        <v>855</v>
+      </c>
+      <c r="F331" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D332" s="6"/>
+      <c r="E332" s="7">
+        <v>805</v>
+      </c>
+      <c r="F332" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D333" s="6"/>
+      <c r="E333" s="7">
+        <v>560</v>
+      </c>
+      <c r="F333" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C334" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D334" s="6"/>
+      <c r="E334" s="7">
+        <v>702.5</v>
+      </c>
+      <c r="F334" s="8">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D335" s="6"/>
+      <c r="E335" s="7">
+        <v>2238.75</v>
+      </c>
+      <c r="F335" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D336" s="6"/>
+      <c r="E336" s="7">
+        <v>1990</v>
+      </c>
+      <c r="F336" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D337" s="6"/>
+      <c r="E337" s="7">
+        <v>746.25</v>
+      </c>
+      <c r="F337" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D338" s="6"/>
+      <c r="E338" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F338" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C339" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D339" s="6"/>
+      <c r="E339" s="7">
+        <v>1390</v>
+      </c>
+      <c r="F339" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D340" s="6"/>
+      <c r="E340" s="7">
+        <v>855</v>
+      </c>
+      <c r="F340" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D341" s="6"/>
+      <c r="E341" s="7">
+        <v>805</v>
+      </c>
+      <c r="F341" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D342" s="6"/>
+      <c r="E342" s="7">
+        <v>560</v>
+      </c>
+      <c r="F342" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D343" s="6"/>
+      <c r="E343" s="7">
+        <v>702.5</v>
+      </c>
+      <c r="F343" s="8">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D344" s="6"/>
+      <c r="E344" s="7">
+        <v>2238.75</v>
+      </c>
+      <c r="F344" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D345" s="6"/>
+      <c r="E345" s="7">
+        <v>1990</v>
+      </c>
+      <c r="F345" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A346" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D346" s="6"/>
+      <c r="E346" s="7">
+        <v>746.25</v>
+      </c>
+      <c r="F346" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A347" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D347" s="6"/>
+      <c r="E347" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F347" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A348" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D348" s="6"/>
+      <c r="E348" s="7">
+        <v>1390</v>
+      </c>
+      <c r="F348" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D349" s="6"/>
+      <c r="E349" s="7">
+        <v>855</v>
+      </c>
+      <c r="F349" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A350" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D350" s="6"/>
+      <c r="E350" s="7">
+        <v>805</v>
+      </c>
+      <c r="F350" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A351" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D351" s="6"/>
+      <c r="E351" s="7">
+        <v>560</v>
+      </c>
+      <c r="F351" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A352" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D352" s="6"/>
+      <c r="E352" s="7">
+        <v>702.5</v>
+      </c>
+      <c r="F352" s="8">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D353" s="6"/>
+      <c r="E353" s="7">
+        <v>2238.75</v>
+      </c>
+      <c r="F353" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A354" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D354" s="6"/>
+      <c r="E354" s="7">
+        <v>1990</v>
+      </c>
+      <c r="F354" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A355" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D355" s="6"/>
+      <c r="E355" s="7">
+        <v>746.25</v>
+      </c>
+      <c r="F355" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A356" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D356" s="6"/>
+      <c r="E356" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F356" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A357" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D357" s="6"/>
+      <c r="E357" s="7">
+        <v>1390</v>
+      </c>
+      <c r="F357" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A358" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D358" s="6"/>
+      <c r="E358" s="7">
+        <v>855</v>
+      </c>
+      <c r="F358" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A359" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D359" s="6"/>
+      <c r="E359" s="7">
+        <v>805</v>
+      </c>
+      <c r="F359" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A360" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D360" s="6"/>
+      <c r="E360" s="7">
+        <v>560</v>
+      </c>
+      <c r="F360" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A361" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D361" s="6"/>
+      <c r="E361" s="7">
+        <v>702.5</v>
+      </c>
+      <c r="F361" s="8">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A362" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D362" s="6"/>
+      <c r="E362" s="7">
+        <v>2238.75</v>
+      </c>
+      <c r="F362" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A363" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D363" s="6"/>
+      <c r="E363" s="7">
+        <v>1990</v>
+      </c>
+      <c r="F363" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A364" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D364" s="6"/>
+      <c r="E364" s="7">
+        <v>746.25</v>
+      </c>
+      <c r="F364" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A365" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D365" s="6"/>
+      <c r="E365" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F365" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C366" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D366" s="6"/>
+      <c r="E366" s="7">
+        <v>1390</v>
+      </c>
+      <c r="F366" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C367" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D367" s="6"/>
+      <c r="E367" s="7">
+        <v>855</v>
+      </c>
+      <c r="F367" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A368" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C368" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D368" s="6"/>
+      <c r="E368" s="7">
+        <v>805</v>
+      </c>
+      <c r="F368" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A369" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C369" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D369" s="6"/>
+      <c r="E369" s="7">
+        <v>560</v>
+      </c>
+      <c r="F369" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A370" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C370" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D370" s="6"/>
+      <c r="E370" s="7">
+        <v>702.5</v>
+      </c>
+      <c r="F370" s="8">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A371" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C371" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D371" s="6"/>
+      <c r="E371" s="7">
+        <v>3358.125</v>
+      </c>
+      <c r="F371" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A372" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D372" s="6"/>
+      <c r="E372" s="7">
+        <v>2985</v>
+      </c>
+      <c r="F372" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A373" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D373" s="6"/>
+      <c r="E373" s="7">
+        <v>1119.375</v>
+      </c>
+      <c r="F373" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A374" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D374" s="6"/>
+      <c r="E374" s="7">
+        <v>3127.5</v>
+      </c>
+      <c r="F374" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A375" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D375" s="6"/>
+      <c r="E375" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F375" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A376" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D376" s="6"/>
+      <c r="E376" s="7">
+        <v>1282.5</v>
+      </c>
+      <c r="F376" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A377" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D377" s="6"/>
+      <c r="E377" s="7">
+        <v>1207.5</v>
+      </c>
+      <c r="F377" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A378" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C378" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D378" s="6"/>
+      <c r="E378" s="7">
+        <v>840</v>
+      </c>
+      <c r="F378" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A379" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D379" s="6"/>
+      <c r="E379" s="7">
+        <v>1053.75</v>
+      </c>
+      <c r="F379" s="8">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A380" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C380" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D380" s="6"/>
+      <c r="E380" s="7">
+        <v>3358.125</v>
+      </c>
+      <c r="F380" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A381" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D381" s="6"/>
+      <c r="E381" s="7">
+        <v>2985</v>
+      </c>
+      <c r="F381" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A382" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C382" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D382" s="6"/>
+      <c r="E382" s="7">
+        <v>1119.375</v>
+      </c>
+      <c r="F382" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A383" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D383" s="6"/>
+      <c r="E383" s="7">
+        <v>3127.5</v>
+      </c>
+      <c r="F383" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A384" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D384" s="6"/>
+      <c r="E384" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F384" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A385" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D385" s="6"/>
+      <c r="E385" s="7">
+        <v>1282.5</v>
+      </c>
+      <c r="F385" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A386" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C386" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D386" s="6"/>
+      <c r="E386" s="7">
+        <v>1207.5</v>
+      </c>
+      <c r="F386" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A387" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C387" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D387" s="6"/>
+      <c r="E387" s="7">
+        <v>840</v>
+      </c>
+      <c r="F387" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A388" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C388" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D388" s="6"/>
+      <c r="E388" s="7">
+        <v>1053.75</v>
+      </c>
+      <c r="F388" s="8">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A389" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C389" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D389" s="6"/>
+      <c r="E389" s="7">
+        <v>3358.125</v>
+      </c>
+      <c r="F389" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A390" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C390" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D390" s="6"/>
+      <c r="E390" s="7">
+        <v>2985</v>
+      </c>
+      <c r="F390" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A391" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D391" s="6"/>
+      <c r="E391" s="7">
+        <v>1119.375</v>
+      </c>
+      <c r="F391" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A392" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C392" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D392" s="6"/>
+      <c r="E392" s="7">
+        <v>3127.5</v>
+      </c>
+      <c r="F392" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A393" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D393" s="6"/>
+      <c r="E393" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F393" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A394" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C394" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D394" s="6"/>
+      <c r="E394" s="7">
+        <v>1282.5</v>
+      </c>
+      <c r="F394" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A395" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B395" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D395" s="6"/>
+      <c r="E395" s="7">
+        <v>1207.5</v>
+      </c>
+      <c r="F395" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A396" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D396" s="6"/>
+      <c r="E396" s="7">
+        <v>840</v>
+      </c>
+      <c r="F396" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A397" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D397" s="6"/>
+      <c r="E397" s="7">
+        <v>1053.75</v>
+      </c>
+      <c r="F397" s="8">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A398" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D398" s="6"/>
+      <c r="E398" s="7">
+        <v>3358.125</v>
+      </c>
+      <c r="F398" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A399" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D399" s="6"/>
+      <c r="E399" s="7">
+        <v>2985</v>
+      </c>
+      <c r="F399" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A400" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D400" s="6"/>
+      <c r="E400" s="7">
+        <v>1119.375</v>
+      </c>
+      <c r="F400" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A401" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D401" s="6"/>
+      <c r="E401" s="7">
+        <v>3127.5</v>
+      </c>
+      <c r="F401" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A402" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D402" s="6"/>
+      <c r="E402" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F402" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A403" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D403" s="6"/>
+      <c r="E403" s="7">
+        <v>1282.5</v>
+      </c>
+      <c r="F403" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A404" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C404" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D404" s="6"/>
+      <c r="E404" s="7">
+        <v>1207.5</v>
+      </c>
+      <c r="F404" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A405" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D405" s="6"/>
+      <c r="E405" s="7">
+        <v>840</v>
+      </c>
+      <c r="F405" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A406" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D406" s="6"/>
+      <c r="E406" s="7">
+        <v>1053.75</v>
+      </c>
+      <c r="F406" s="8">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A407" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D407" s="6"/>
+      <c r="E407" s="7">
+        <v>3358.125</v>
+      </c>
+      <c r="F407" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A408" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B408" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D408" s="6"/>
+      <c r="E408" s="7">
+        <v>2985</v>
+      </c>
+      <c r="F408" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A409" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D409" s="6"/>
+      <c r="E409" s="7">
+        <v>1119.375</v>
+      </c>
+      <c r="F409" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A410" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D410" s="6"/>
+      <c r="E410" s="7">
+        <v>3127.5</v>
+      </c>
+      <c r="F410" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A411" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D411" s="6"/>
+      <c r="E411" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F411" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A412" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D412" s="6"/>
+      <c r="E412" s="7">
+        <v>1282.5</v>
+      </c>
+      <c r="F412" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A413" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D413" s="6"/>
+      <c r="E413" s="7">
+        <v>1207.5</v>
+      </c>
+      <c r="F413" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A414" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C414" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D414" s="6"/>
+      <c r="E414" s="7">
+        <v>840</v>
+      </c>
+      <c r="F414" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A415" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B415" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D415" s="6"/>
+      <c r="E415" s="7">
+        <v>1053.75</v>
+      </c>
+      <c r="F415" s="8">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A416" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B416" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D416" s="6"/>
+      <c r="E416" s="7">
+        <v>3358.125</v>
+      </c>
+      <c r="F416" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A417" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D417" s="6"/>
+      <c r="E417" s="7">
+        <v>2985</v>
+      </c>
+      <c r="F417" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A418" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D418" s="6"/>
+      <c r="E418" s="7">
+        <v>1119.375</v>
+      </c>
+      <c r="F418" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A419" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B419" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D419" s="6"/>
+      <c r="E419" s="7">
+        <v>3127.5</v>
+      </c>
+      <c r="F419" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A420" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B420" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D420" s="6"/>
+      <c r="E420" s="7">
+        <v>2085</v>
+      </c>
+      <c r="F420" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A421" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B421" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D421" s="6"/>
+      <c r="E421" s="7">
+        <v>1282.5</v>
+      </c>
+      <c r="F421" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A422" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B422" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C422" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D422" s="6"/>
+      <c r="E422" s="7">
+        <v>1207.5</v>
+      </c>
+      <c r="F422" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A423" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D423" s="6"/>
+      <c r="E423" s="7">
+        <v>840</v>
+      </c>
+      <c r="F423" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A424" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D424" s="6"/>
+      <c r="E424" s="7">
+        <v>1053.75</v>
+      </c>
+      <c r="F424" s="8">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A425" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D425" s="6"/>
+      <c r="E425" s="7">
+        <v>4477.5</v>
+      </c>
+      <c r="F425" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A426" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D426" s="6"/>
+      <c r="E426" s="7">
+        <v>3980</v>
+      </c>
+      <c r="F426" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A427" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D427" s="6"/>
+      <c r="E427" s="7">
+        <v>1492.5</v>
+      </c>
+      <c r="F427" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A428" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D428" s="6"/>
+      <c r="E428" s="7">
+        <v>4170</v>
+      </c>
+      <c r="F428" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A429" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B429" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D429" s="6"/>
+      <c r="E429" s="7">
+        <v>2780</v>
+      </c>
+      <c r="F429" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A430" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D430" s="6"/>
+      <c r="E430" s="7">
+        <v>1710</v>
+      </c>
+      <c r="F430" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A431" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B431" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D431" s="6"/>
+      <c r="E431" s="7">
+        <v>1610</v>
+      </c>
+      <c r="F431" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A432" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D432" s="6"/>
+      <c r="E432" s="7">
+        <v>1120</v>
+      </c>
+      <c r="F432" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A433" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B433" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D433" s="6"/>
+      <c r="E433" s="7">
+        <v>1405</v>
+      </c>
+      <c r="F433" s="8">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A434" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B434" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C434" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D434" s="6"/>
+      <c r="E434" s="7">
+        <v>4477.5</v>
+      </c>
+      <c r="F434" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A435" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B435" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D435" s="6"/>
+      <c r="E435" s="7">
+        <v>3980</v>
+      </c>
+      <c r="F435" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A436" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B436" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C436" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D436" s="6"/>
+      <c r="E436" s="7">
+        <v>1492.5</v>
+      </c>
+      <c r="F436" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A437" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B437" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D437" s="6"/>
+      <c r="E437" s="7">
+        <v>4170</v>
+      </c>
+      <c r="F437" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A438" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B438" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D438" s="6"/>
+      <c r="E438" s="7">
+        <v>2780</v>
+      </c>
+      <c r="F438" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A439" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B439" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D439" s="6"/>
+      <c r="E439" s="7">
+        <v>1710</v>
+      </c>
+      <c r="F439" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A440" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B440" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D440" s="6"/>
+      <c r="E440" s="7">
+        <v>1610</v>
+      </c>
+      <c r="F440" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A441" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B441" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D441" s="6"/>
+      <c r="E441" s="7">
+        <v>1120</v>
+      </c>
+      <c r="F441" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A442" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D442" s="6"/>
+      <c r="E442" s="7">
+        <v>1405</v>
+      </c>
+      <c r="F442" s="8">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A443" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D443" s="6"/>
+      <c r="E443" s="7">
+        <v>4477.5</v>
+      </c>
+      <c r="F443" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A444" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B444" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D444" s="6"/>
+      <c r="E444" s="7">
+        <v>3980</v>
+      </c>
+      <c r="F444" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A445" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B445" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D445" s="6"/>
+      <c r="E445" s="7">
+        <v>1492.5</v>
+      </c>
+      <c r="F445" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A446" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C446" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D446" s="6"/>
+      <c r="E446" s="7">
+        <v>4170</v>
+      </c>
+      <c r="F446" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A447" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B447" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D447" s="6"/>
+      <c r="E447" s="7">
+        <v>2780</v>
+      </c>
+      <c r="F447" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A448" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C448" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D448" s="6"/>
+      <c r="E448" s="7">
+        <v>1710</v>
+      </c>
+      <c r="F448" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A449" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B449" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D449" s="6"/>
+      <c r="E449" s="7">
+        <v>1610</v>
+      </c>
+      <c r="F449" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A450" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B450" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D450" s="6"/>
+      <c r="E450" s="7">
+        <v>1120</v>
+      </c>
+      <c r="F450" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A451" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B451" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D451" s="6"/>
+      <c r="E451" s="7">
+        <v>1405</v>
+      </c>
+      <c r="F451" s="8">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A452" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B452" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C452" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D452" s="6"/>
+      <c r="E452" s="7">
+        <v>4477.5</v>
+      </c>
+      <c r="F452" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A453" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D453" s="6"/>
+      <c r="E453" s="7">
+        <v>3980</v>
+      </c>
+      <c r="F453" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A454" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B454" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C454" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D454" s="6"/>
+      <c r="E454" s="7">
+        <v>1492.5</v>
+      </c>
+      <c r="F454" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A455" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B455" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C455" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D455" s="6"/>
+      <c r="E455" s="7">
+        <v>4170</v>
+      </c>
+      <c r="F455" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A456" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B456" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C456" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D456" s="6"/>
+      <c r="E456" s="7">
+        <v>2780</v>
+      </c>
+      <c r="F456" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A457" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B457" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D457" s="6"/>
+      <c r="E457" s="7">
+        <v>1710</v>
+      </c>
+      <c r="F457" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A458" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C458" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D458" s="6"/>
+      <c r="E458" s="7">
+        <v>1610</v>
+      </c>
+      <c r="F458" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A459" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B459" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D459" s="6"/>
+      <c r="E459" s="7">
+        <v>1120</v>
+      </c>
+      <c r="F459" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A460" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B460" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C460" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D460" s="6"/>
+      <c r="E460" s="7">
+        <v>1405</v>
+      </c>
+      <c r="F460" s="8">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A461" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B461" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D461" s="6"/>
+      <c r="E461" s="7">
+        <v>4477.5</v>
+      </c>
+      <c r="F461" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A462" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B462" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C462" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D462" s="6"/>
+      <c r="E462" s="7">
+        <v>3980</v>
+      </c>
+      <c r="F462" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A463" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C463" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D463" s="6"/>
+      <c r="E463" s="7">
+        <v>1492.5</v>
+      </c>
+      <c r="F463" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A464" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B464" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C464" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D464" s="6"/>
+      <c r="E464" s="7">
+        <v>4170</v>
+      </c>
+      <c r="F464" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A465" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B465" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C465" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D465" s="6"/>
+      <c r="E465" s="7">
+        <v>2780</v>
+      </c>
+      <c r="F465" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A466" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B466" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C466" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D466" s="6"/>
+      <c r="E466" s="7">
+        <v>1710</v>
+      </c>
+      <c r="F466" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A467" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B467" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C467" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D467" s="6"/>
+      <c r="E467" s="7">
+        <v>1610</v>
+      </c>
+      <c r="F467" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A468" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B468" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C468" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D468" s="6"/>
+      <c r="E468" s="7">
+        <v>1120</v>
+      </c>
+      <c r="F468" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A469" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B469" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C469" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D469" s="6"/>
+      <c r="E469" s="7">
+        <v>1405</v>
+      </c>
+      <c r="F469" s="8">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A470" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B470" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C470" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D470" s="6"/>
+      <c r="E470" s="7">
+        <v>4477.5</v>
+      </c>
+      <c r="F470" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A471" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C471" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D471" s="6"/>
+      <c r="E471" s="7">
+        <v>3980</v>
+      </c>
+      <c r="F471" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A472" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B472" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D472" s="6"/>
+      <c r="E472" s="7">
+        <v>1492.5</v>
+      </c>
+      <c r="F472" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A473" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B473" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D473" s="6"/>
+      <c r="E473" s="7">
+        <v>4170</v>
+      </c>
+      <c r="F473" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A474" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B474" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C474" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D474" s="6"/>
+      <c r="E474" s="7">
+        <v>2780</v>
+      </c>
+      <c r="F474" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A475" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B475" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C475" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D475" s="6"/>
+      <c r="E475" s="7">
+        <v>1710</v>
+      </c>
+      <c r="F475" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A476" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B476" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C476" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D476" s="6"/>
+      <c r="E476" s="7">
+        <v>1610</v>
+      </c>
+      <c r="F476" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A477" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B477" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D477" s="6"/>
+      <c r="E477" s="7">
+        <v>1120</v>
+      </c>
+      <c r="F477" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A478" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B478" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D478" s="6"/>
+      <c r="E478" s="7">
+        <v>1405</v>
+      </c>
+      <c r="F478" s="8">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A479" s="5"/>
+      <c r="B479" s="5"/>
+      <c r="C479" s="5"/>
+    </row>
+    <row r="480" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A480" s="5"/>
+      <c r="B480" s="5"/>
+      <c r="C480" s="5"/>
+    </row>
+    <row r="481" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A481" s="5"/>
+      <c r="B481" s="5"/>
+      <c r="C481" s="5"/>
+    </row>
+    <row r="482" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A482" s="5"/>
+      <c r="B482" s="5"/>
+      <c r="C482" s="5"/>
+    </row>
+    <row r="483" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A483" s="5"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="5"/>
+    </row>
+    <row r="484" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A484" s="5"/>
+      <c r="B484" s="5"/>
+      <c r="C484" s="5"/>
+    </row>
+    <row r="485" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A485" s="5"/>
+      <c r="B485" s="5"/>
+      <c r="C485" s="5"/>
+    </row>
+    <row r="486" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A486" s="5"/>
+      <c r="B486" s="5"/>
+      <c r="C486" s="5"/>
+    </row>
+    <row r="487" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A487" s="5"/>
+      <c r="B487" s="5"/>
+      <c r="C487" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <autoFilter ref="A1:F271" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="12">
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M61:N61"/>
     <mergeCell ref="H1:K1"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H49:K49"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>